--- a/database/event/2410/event_2410_evp_summary.xlsx
+++ b/database/event/2410/event_2410_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.3846</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9766</v>
+        <v>2.9071</v>
       </c>
       <c r="E2" t="n">
         <v>8.411199999999999</v>
@@ -548,7 +548,7 @@
         <v>2.4951</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0836</v>
+        <v>2.0265</v>
       </c>
       <c r="E3" t="n">
         <v>6.2008</v>
@@ -594,7 +594,7 @@
         <v>2.0028</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5894</v>
+        <v>1.539</v>
       </c>
       <c r="E4" t="n">
         <v>4.9773</v>
@@ -640,7 +640,7 @@
         <v>1.8763</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4624</v>
+        <v>1.4138</v>
       </c>
       <c r="E5" t="n">
         <v>4.663</v>
@@ -686,7 +686,7 @@
         <v>1.6941</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2795</v>
+        <v>1.2334</v>
       </c>
       <c r="E6" t="n">
         <v>4.2102</v>
@@ -732,7 +732,7 @@
         <v>1.5846</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1695</v>
+        <v>1.125</v>
       </c>
       <c r="E7" t="n">
         <v>3.938</v>
@@ -778,7 +778,7 @@
         <v>1.2779</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8616</v>
+        <v>0.8214</v>
       </c>
       <c r="E8" t="n">
         <v>3.1759</v>
@@ -824,7 +824,7 @@
         <v>1.1522</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.6969</v>
       </c>
       <c r="E9" t="n">
         <v>2.8634</v>
@@ -870,7 +870,7 @@
         <v>0.9908</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5734</v>
+        <v>0.5371</v>
       </c>
       <c r="E10" t="n">
         <v>2.4623</v>
@@ -916,7 +916,7 @@
         <v>0.9026</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4848</v>
+        <v>0.4497</v>
       </c>
       <c r="E11" t="n">
         <v>2.243</v>
@@ -962,7 +962,7 @@
         <v>0.8921</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4743</v>
+        <v>0.4394</v>
       </c>
       <c r="E12" t="n">
         <v>2.2171</v>
@@ -1008,7 +1008,7 @@
         <v>0.7823</v>
       </c>
       <c r="D13" t="n">
-        <v>0.364</v>
+        <v>0.3306</v>
       </c>
       <c r="E13" t="n">
         <v>1.9441</v>
@@ -1054,7 +1054,7 @@
         <v>0.72</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3015</v>
+        <v>0.269</v>
       </c>
       <c r="E14" t="n">
         <v>1.7894</v>
@@ -1100,7 +1100,7 @@
         <v>0.6897</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2711</v>
+        <v>0.239</v>
       </c>
       <c r="E15" t="n">
         <v>1.7141</v>
@@ -1146,7 +1146,7 @@
         <v>0.5498</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1306</v>
+        <v>0.1004</v>
       </c>
       <c r="E16" t="n">
         <v>1.3663</v>
@@ -1192,7 +1192,7 @@
         <v>0.5002</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0808</v>
+        <v>0.0513</v>
       </c>
       <c r="E17" t="n">
         <v>1.243</v>
@@ -1238,7 +1238,7 @@
         <v>0.4844</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0649</v>
+        <v>0.0356</v>
       </c>
       <c r="E18" t="n">
         <v>1.2037</v>
@@ -1284,7 +1284,7 @@
         <v>0.4721</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0526</v>
+        <v>0.0235</v>
       </c>
       <c r="E19" t="n">
         <v>1.1733</v>
@@ -1330,7 +1330,7 @@
         <v>0.4378</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0181</v>
+        <v>-0.0105</v>
       </c>
       <c r="E20" t="n">
         <v>1.0879</v>
@@ -1376,7 +1376,7 @@
         <v>0.3428</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0772</v>
+        <v>-0.1045</v>
       </c>
       <c r="E21" t="n">
         <v>0.852</v>
@@ -1422,7 +1422,7 @@
         <v>0.3273</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0927</v>
+        <v>-0.1198</v>
       </c>
       <c r="E22" t="n">
         <v>0.8135</v>
@@ -1468,7 +1468,7 @@
         <v>0.2867</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1336</v>
+        <v>-0.1601</v>
       </c>
       <c r="E23" t="n">
         <v>0.7124</v>
@@ -1514,7 +1514,7 @@
         <v>0.2504</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.17</v>
+        <v>-0.196</v>
       </c>
       <c r="E24" t="n">
         <v>0.6223</v>
@@ -1560,7 +1560,7 @@
         <v>0.1969</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2237</v>
+        <v>-0.249</v>
       </c>
       <c r="E25" t="n">
         <v>0.4893</v>
@@ -1606,7 +1606,7 @@
         <v>0.0277</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3935</v>
+        <v>-0.4165</v>
       </c>
       <c r="E26" t="n">
         <v>0.0689</v>
@@ -1652,7 +1652,7 @@
         <v>-0.09370000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5154</v>
+        <v>-0.5367</v>
       </c>
       <c r="E27" t="n">
         <v>-0.2328</v>
@@ -1698,7 +1698,7 @@
         <v>-0.09959999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5213</v>
+        <v>-0.5425</v>
       </c>
       <c r="E28" t="n">
         <v>-0.2475</v>
@@ -1744,7 +1744,7 @@
         <v>-0.1151</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5369</v>
+        <v>-0.5579</v>
       </c>
       <c r="E29" t="n">
         <v>-0.2861</v>
@@ -1790,7 +1790,7 @@
         <v>-0.176</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5981</v>
+        <v>-0.6182</v>
       </c>
       <c r="E30" t="n">
         <v>-0.4375</v>
@@ -1836,7 +1836,7 @@
         <v>-0.3015</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7241</v>
+        <v>-0.7425</v>
       </c>
       <c r="E31" t="n">
         <v>-0.7494</v>
@@ -1882,7 +1882,7 @@
         <v>-0.3521</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7748</v>
+        <v>-0.7925</v>
       </c>
       <c r="E32" t="n">
         <v>-0.875</v>
@@ -1928,7 +1928,7 @@
         <v>-0.3634</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7862</v>
+        <v>-0.8037</v>
       </c>
       <c r="E33" t="n">
         <v>-0.9032</v>
@@ -1974,7 +1974,7 @@
         <v>-0.4288</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8519</v>
+        <v>-0.8685</v>
       </c>
       <c r="E34" t="n">
         <v>-1.0657</v>
@@ -2020,7 +2020,7 @@
         <v>-0.4448</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.868</v>
+        <v>-0.8843</v>
       </c>
       <c r="E35" t="n">
         <v>-1.1055</v>
@@ -2066,7 +2066,7 @@
         <v>-0.4928</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9161</v>
+        <v>-0.9318</v>
       </c>
       <c r="E36" t="n">
         <v>-1.2246</v>
@@ -2112,7 +2112,7 @@
         <v>-0.5207000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9441000000000001</v>
+        <v>-0.9595</v>
       </c>
       <c r="E37" t="n">
         <v>-1.2941</v>
@@ -2158,7 +2158,7 @@
         <v>-0.5208</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9443</v>
+        <v>-0.9596</v>
       </c>
       <c r="E38" t="n">
         <v>-1.2944</v>
@@ -2204,7 +2204,7 @@
         <v>-0.5446</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9681</v>
+        <v>-0.9831</v>
       </c>
       <c r="E39" t="n">
         <v>-1.3534</v>
@@ -2250,7 +2250,7 @@
         <v>-0.6459</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0698</v>
+        <v>-1.0834</v>
       </c>
       <c r="E40" t="n">
         <v>-1.6051</v>
@@ -2296,7 +2296,7 @@
         <v>-0.6822</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1063</v>
+        <v>-1.1194</v>
       </c>
       <c r="E41" t="n">
         <v>-1.6954</v>

--- a/database/event/2410/event_2410_evp_summary.xlsx
+++ b/database/event/2410/event_2410_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.411199999999999</v>
+        <v>7.4521</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3846</v>
+        <v>2.9986</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9071</v>
+        <v>2.7262</v>
       </c>
       <c r="E2" t="n">
-        <v>8.411199999999999</v>
+        <v>7.4521</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2804</v>
+        <v>3.0755</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1308</v>
+        <v>4.3766</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2804</v>
+        <v>3.3935</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2804</v>
+        <v>3.3935</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1308</v>
+        <v>4.3766</v>
       </c>
       <c r="K2" t="n">
         <v>161</v>
@@ -529,7 +529,7 @@
         <v>225</v>
       </c>
       <c r="M2" t="n">
-        <v>8.411200000000001</v>
+        <v>7.770099999999999</v>
       </c>
       <c r="N2" t="n">
         <v>386</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2008</v>
+        <v>5.8458</v>
       </c>
       <c r="C3" t="n">
-        <v>2.4951</v>
+        <v>2.3523</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0265</v>
+        <v>2.0011</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2008</v>
+        <v>5.8458</v>
       </c>
       <c r="F3" t="n">
-        <v>1.384</v>
+        <v>1.5701</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8168</v>
+        <v>4.2757</v>
       </c>
       <c r="H3" t="n">
-        <v>1.384</v>
+        <v>1.5701</v>
       </c>
       <c r="I3" t="n">
-        <v>1.384</v>
+        <v>1.5701</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8168</v>
+        <v>4.2757</v>
       </c>
       <c r="K3" t="n">
         <v>161</v>
@@ -575,7 +575,7 @@
         <v>225</v>
       </c>
       <c r="M3" t="n">
-        <v>6.200799999999999</v>
+        <v>5.8458</v>
       </c>
       <c r="N3" t="n">
         <v>386</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9773</v>
+        <v>4.508</v>
       </c>
       <c r="C4" t="n">
-        <v>2.0028</v>
+        <v>1.814</v>
       </c>
       <c r="D4" t="n">
-        <v>1.539</v>
+        <v>1.3971</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9773</v>
+        <v>4.508</v>
       </c>
       <c r="F4" t="n">
-        <v>4.21</v>
+        <v>3.8101</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7673</v>
+        <v>0.6979</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3775</v>
+        <v>7.938</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5481</v>
+        <v>4.1274</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7673</v>
+        <v>0.6979</v>
       </c>
       <c r="K4" t="n">
         <v>145</v>
@@ -621,7 +621,7 @@
         <v>82</v>
       </c>
       <c r="M4" t="n">
-        <v>4.315399999999999</v>
+        <v>4.825299999999999</v>
       </c>
       <c r="N4" t="n">
         <v>227</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.663</v>
+        <v>4.2617</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8763</v>
+        <v>1.7149</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4138</v>
+        <v>1.2859</v>
       </c>
       <c r="E5" t="n">
-        <v>4.663</v>
+        <v>4.2617</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2141</v>
+        <v>1.3696</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4489</v>
+        <v>2.8921</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2141</v>
+        <v>1.3696</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2141</v>
+        <v>1.3696</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4489</v>
+        <v>2.8921</v>
       </c>
       <c r="K5" t="n">
         <v>142</v>
@@ -667,7 +667,7 @@
         <v>135</v>
       </c>
       <c r="M5" t="n">
-        <v>4.663</v>
+        <v>4.2617</v>
       </c>
       <c r="N5" t="n">
         <v>277</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2102</v>
+        <v>4.2488</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6941</v>
+        <v>1.7097</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2334</v>
+        <v>1.2801</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2102</v>
+        <v>4.2488</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1133</v>
+        <v>2.6807</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3235</v>
+        <v>1.5681</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1133</v>
+        <v>2.6807</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1133</v>
+        <v>2.6807</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3235</v>
+        <v>1.5681</v>
       </c>
       <c r="K6" t="n">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="L6" t="n">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2102</v>
+        <v>4.2488</v>
       </c>
       <c r="N6" t="n">
-        <v>386</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.938</v>
+        <v>3.6973</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5846</v>
+        <v>1.4877</v>
       </c>
       <c r="D7" t="n">
-        <v>1.125</v>
+        <v>1.0311</v>
       </c>
       <c r="E7" t="n">
-        <v>3.938</v>
+        <v>3.6973</v>
       </c>
       <c r="F7" t="n">
-        <v>2.224</v>
+        <v>0.1867</v>
       </c>
       <c r="G7" t="n">
-        <v>1.714</v>
+        <v>3.5106</v>
       </c>
       <c r="H7" t="n">
-        <v>2.224</v>
+        <v>0.1867</v>
       </c>
       <c r="I7" t="n">
-        <v>2.224</v>
+        <v>0.1867</v>
       </c>
       <c r="J7" t="n">
-        <v>1.714</v>
+        <v>3.5106</v>
       </c>
       <c r="K7" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="L7" t="n">
-        <v>135</v>
+        <v>225</v>
       </c>
       <c r="M7" t="n">
-        <v>3.938</v>
+        <v>3.6973</v>
       </c>
       <c r="N7" t="n">
-        <v>277</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1759</v>
+        <v>3.3162</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2779</v>
+        <v>1.3344</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8214</v>
+        <v>0.8591</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1759</v>
+        <v>3.3162</v>
       </c>
       <c r="F8" t="n">
-        <v>2.333</v>
+        <v>2.52</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8429</v>
+        <v>0.7962</v>
       </c>
       <c r="H8" t="n">
-        <v>2.333</v>
+        <v>3.3926</v>
       </c>
       <c r="I8" t="n">
-        <v>1.891</v>
+        <v>1.764</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8429</v>
+        <v>0.7962</v>
       </c>
       <c r="K8" t="n">
         <v>162</v>
@@ -805,7 +805,7 @@
         <v>135</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7339</v>
+        <v>2.5602</v>
       </c>
       <c r="N8" t="n">
         <v>297</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8634</v>
+        <v>3.1611</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1522</v>
+        <v>1.272</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6969</v>
+        <v>0.7891</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8634</v>
+        <v>3.1611</v>
       </c>
       <c r="F9" t="n">
-        <v>1.812</v>
+        <v>2.0863</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0514</v>
+        <v>1.0748</v>
       </c>
       <c r="H9" t="n">
-        <v>1.812</v>
+        <v>2.0863</v>
       </c>
       <c r="I9" t="n">
-        <v>1.812</v>
+        <v>2.0863</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0514</v>
+        <v>1.0748</v>
       </c>
       <c r="K9" t="n">
         <v>142</v>
@@ -851,7 +851,7 @@
         <v>135</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8634</v>
+        <v>3.1611</v>
       </c>
       <c r="N9" t="n">
         <v>277</v>
@@ -860,81 +860,81 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4623</v>
+        <v>3.0327</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9908</v>
+        <v>1.2203</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5371</v>
+        <v>0.7311</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4623</v>
+        <v>3.0327</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3747</v>
+        <v>1.6404</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0876</v>
+        <v>1.3923</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3747</v>
+        <v>1.6404</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9248</v>
+        <v>1.6404</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0876</v>
+        <v>1.3923</v>
       </c>
       <c r="K10" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="L10" t="n">
         <v>135</v>
       </c>
       <c r="M10" t="n">
-        <v>2.0124</v>
+        <v>3.0327</v>
       </c>
       <c r="N10" t="n">
-        <v>297</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.243</v>
+        <v>2.8402</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9026</v>
+        <v>1.1429</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4497</v>
+        <v>0.6442</v>
       </c>
       <c r="E11" t="n">
-        <v>2.243</v>
+        <v>2.8402</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7259</v>
+        <v>2.7469</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5171</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7259</v>
+        <v>4.1919</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5884</v>
+        <v>2.1796</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5171</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>162</v>
@@ -943,7 +943,7 @@
         <v>135</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1055</v>
+        <v>2.2729</v>
       </c>
       <c r="N11" t="n">
         <v>297</v>
@@ -952,173 +952,173 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2171</v>
+        <v>2.7431</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8921</v>
+        <v>1.1038</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4394</v>
+        <v>0.6004</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2171</v>
+        <v>2.7431</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5251</v>
+        <v>1.553</v>
       </c>
       <c r="G12" t="n">
-        <v>1.692</v>
+        <v>1.1901</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5251</v>
+        <v>1.553</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5251</v>
+        <v>0.8075</v>
       </c>
       <c r="J12" t="n">
-        <v>1.692</v>
+        <v>1.1901</v>
       </c>
       <c r="K12" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="L12" t="n">
         <v>135</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2171</v>
+        <v>1.9976</v>
       </c>
       <c r="N12" t="n">
-        <v>277</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9441</v>
+        <v>2.1665</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7823</v>
+        <v>0.8718</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3306</v>
+        <v>0.3401</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9441</v>
+        <v>2.1665</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5704</v>
+        <v>1.7648</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3737</v>
+        <v>0.4017</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5704</v>
+        <v>1.7648</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5704</v>
+        <v>0.9176</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3737</v>
+        <v>0.4017</v>
       </c>
       <c r="K13" t="n">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="L13" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9441</v>
+        <v>1.3193</v>
       </c>
       <c r="N13" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7894</v>
+        <v>2.1543</v>
       </c>
       <c r="C14" t="n">
-        <v>0.72</v>
+        <v>0.8669</v>
       </c>
       <c r="D14" t="n">
-        <v>0.269</v>
+        <v>0.3345</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7894</v>
+        <v>2.1543</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8817</v>
+        <v>2.1338</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.09229999999999999</v>
+        <v>0.0205</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8817</v>
+        <v>2.1338</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8817</v>
+        <v>1.1095</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.09229999999999999</v>
+        <v>0.0205</v>
       </c>
       <c r="K14" t="n">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="L14" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7894</v>
+        <v>1.13</v>
       </c>
       <c r="N14" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7141</v>
+        <v>2.1457</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6897</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.239</v>
+        <v>0.3307</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7141</v>
+        <v>2.1457</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6736</v>
+        <v>2.0571</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0405</v>
+        <v>0.0886</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6736</v>
+        <v>2.0571</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6736</v>
+        <v>2.0571</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0405</v>
+        <v>0.0886</v>
       </c>
       <c r="K15" t="n">
         <v>157</v>
@@ -1127,7 +1127,7 @@
         <v>74</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7141</v>
+        <v>2.1457</v>
       </c>
       <c r="N15" t="n">
         <v>231</v>
@@ -1136,35 +1136,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3663</v>
+        <v>2.0024</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5498</v>
+        <v>0.8057</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1004</v>
+        <v>0.266</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3663</v>
+        <v>2.0024</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2541</v>
+        <v>1.6375</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1122</v>
+        <v>0.3649</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2541</v>
+        <v>1.6375</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2541</v>
+        <v>1.6375</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1122</v>
+        <v>0.3649</v>
       </c>
       <c r="K16" t="n">
         <v>162</v>
@@ -1173,7 +1173,7 @@
         <v>69</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3663</v>
+        <v>2.0024</v>
       </c>
       <c r="N16" t="n">
         <v>231</v>
@@ -1182,170 +1182,170 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.243</v>
+        <v>1.8669</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5002</v>
+        <v>0.7512</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0513</v>
+        <v>0.2048</v>
       </c>
       <c r="E17" t="n">
-        <v>1.243</v>
+        <v>1.8669</v>
       </c>
       <c r="F17" t="n">
-        <v>1.243</v>
+        <v>0.4078</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.4591</v>
       </c>
       <c r="H17" t="n">
-        <v>1.243</v>
+        <v>0.4078</v>
       </c>
       <c r="I17" t="n">
-        <v>1.243</v>
+        <v>0.4078</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.4591</v>
       </c>
       <c r="K17" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="M17" t="n">
-        <v>1.243</v>
+        <v>1.8669</v>
       </c>
       <c r="N17" t="n">
-        <v>154</v>
+        <v>386</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2037</v>
+        <v>1.7172</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4844</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0356</v>
+        <v>0.1372</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2037</v>
+        <v>1.7172</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1381</v>
+        <v>1.5953</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0656</v>
+        <v>0.1219</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1381</v>
+        <v>1.5953</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1381</v>
+        <v>1.5953</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0656</v>
+        <v>0.1219</v>
       </c>
       <c r="K18" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="L18" t="n">
-        <v>225</v>
+        <v>74</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2037</v>
+        <v>1.7172</v>
       </c>
       <c r="N18" t="n">
-        <v>386</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1733</v>
+        <v>1.577</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4721</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0235</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1733</v>
+        <v>1.577</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6691</v>
+        <v>1.349</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5042</v>
+        <v>0.228</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6691</v>
+        <v>1.349</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5423</v>
+        <v>1.349</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5042</v>
+        <v>0.228</v>
       </c>
       <c r="K19" t="n">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="L19" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0465</v>
+        <v>1.577</v>
       </c>
       <c r="N19" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0879</v>
+        <v>1.4105</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4378</v>
+        <v>0.5676</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0105</v>
+        <v>-0.0012</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0879</v>
+        <v>1.4105</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0879</v>
+        <v>1.4105</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0879</v>
+        <v>1.4105</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0879</v>
+        <v>1.4105</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0879</v>
+        <v>1.4105</v>
       </c>
       <c r="N20" t="n">
         <v>154</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.852</v>
+        <v>1.3402</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3428</v>
+        <v>0.5393</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1045</v>
+        <v>-0.033</v>
       </c>
       <c r="E21" t="n">
-        <v>0.852</v>
+        <v>1.3402</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0349</v>
+        <v>0.4758</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8869</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0349</v>
+        <v>0.4758</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0349</v>
+        <v>0.4758</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8869</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>142</v>
@@ -1403,7 +1403,7 @@
         <v>135</v>
       </c>
       <c r="M21" t="n">
-        <v>0.852</v>
+        <v>1.3402</v>
       </c>
       <c r="N21" t="n">
         <v>277</v>
@@ -1412,47 +1412,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8135</v>
+        <v>1.1666</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3273</v>
+        <v>0.4694</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1198</v>
+        <v>-0.1114</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8135</v>
+        <v>1.1666</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0302</v>
+        <v>1.1666</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2167</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0302</v>
+        <v>1.1666</v>
       </c>
       <c r="I22" t="n">
-        <v>0.835</v>
+        <v>1.1666</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2167</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="L22" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6183</v>
+        <v>1.1666</v>
       </c>
       <c r="N22" t="n">
-        <v>227</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7124</v>
+        <v>1.077</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2867</v>
+        <v>0.4334</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1601</v>
+        <v>-0.1518</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7124</v>
+        <v>1.077</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7124</v>
+        <v>1.077</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7124</v>
+        <v>1.077</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7124</v>
+        <v>1.077</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7124</v>
+        <v>1.077</v>
       </c>
       <c r="N23" t="n">
         <v>151</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6223</v>
+        <v>1.0471</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2504</v>
+        <v>0.4213</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.196</v>
+        <v>-0.1653</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6223</v>
+        <v>1.0471</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3921</v>
+        <v>0.6646</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2302</v>
+        <v>0.3825</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3921</v>
+        <v>0.6646</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3921</v>
+        <v>0.6646</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2302</v>
+        <v>0.3825</v>
       </c>
       <c r="K24" t="n">
         <v>157</v>
@@ -1541,7 +1541,7 @@
         <v>74</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6223</v>
+        <v>1.0471</v>
       </c>
       <c r="N24" t="n">
         <v>231</v>
@@ -1550,185 +1550,185 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4893</v>
+        <v>0.9411</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1969</v>
+        <v>0.3787</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.249</v>
+        <v>-0.2132</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4893</v>
+        <v>0.9411</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6801</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1908</v>
+        <v>1.5837</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6801</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6801</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1908</v>
+        <v>1.5837</v>
       </c>
       <c r="K25" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="L25" t="n">
-        <v>74</v>
+        <v>225</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4893000000000001</v>
+        <v>0.9411000000000002</v>
       </c>
       <c r="N25" t="n">
-        <v>231</v>
+        <v>386</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0689</v>
+        <v>0.8276</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0277</v>
+        <v>0.333</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4165</v>
+        <v>-0.2644</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0689</v>
+        <v>0.8276</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0689</v>
+        <v>2.0325</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-1.2049</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0689</v>
+        <v>2.0325</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0689</v>
+        <v>1.0568</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-1.2049</v>
       </c>
       <c r="K26" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0689</v>
+        <v>-0.1481000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>154</v>
+        <v>297</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2328</v>
+        <v>0.7837</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.09370000000000001</v>
+        <v>0.3154</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5367</v>
+        <v>-0.2842</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2328</v>
+        <v>0.7837</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2328</v>
+        <v>0.8602</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.0765</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2328</v>
+        <v>0.8602</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2328</v>
+        <v>0.8602</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.0765</v>
       </c>
       <c r="K27" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2328</v>
+        <v>0.7837</v>
       </c>
       <c r="N27" t="n">
-        <v>151</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2475</v>
+        <v>0.2929</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.09959999999999999</v>
+        <v>0.1179</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5425</v>
+        <v>-0.5058</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2475</v>
+        <v>0.2929</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0221</v>
+        <v>0.2929</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.2696</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.0221</v>
+        <v>0.2929</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8284</v>
+        <v>0.2929</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.2696</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="L28" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4412</v>
+        <v>0.2929</v>
       </c>
       <c r="N28" t="n">
-        <v>297</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2861</v>
+        <v>0.2587</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1151</v>
+        <v>0.1041</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5579</v>
+        <v>-0.5212</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2861</v>
+        <v>0.2587</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1315</v>
+        <v>0.2858</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.1546</v>
+        <v>-0.0271</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1315</v>
+        <v>0.2858</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1315</v>
+        <v>0.2858</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.1546</v>
+        <v>-0.0271</v>
       </c>
       <c r="K29" t="n">
         <v>157</v>
@@ -1771,7 +1771,7 @@
         <v>74</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2861</v>
+        <v>0.2587</v>
       </c>
       <c r="N29" t="n">
         <v>231</v>
@@ -1780,78 +1780,78 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4375</v>
+        <v>0.0236</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.176</v>
+        <v>0.0095</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6182</v>
+        <v>-0.6274</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4375</v>
+        <v>0.0236</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.34</v>
+        <v>0.3877</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9025</v>
+        <v>-0.3641</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.34</v>
+        <v>0.3877</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.34</v>
+        <v>0.2016</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9025</v>
+        <v>-0.3641</v>
       </c>
       <c r="K30" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="L30" t="n">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4375000000000001</v>
+        <v>-0.1625</v>
       </c>
       <c r="N30" t="n">
-        <v>386</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7494</v>
+        <v>-0.0485</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3015</v>
+        <v>-0.0195</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7425</v>
+        <v>-0.6599</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7494</v>
+        <v>-0.0485</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.7494</v>
+        <v>-0.0485</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7494</v>
+        <v>-0.0485</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7494</v>
+        <v>-0.0485</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7494</v>
+        <v>-0.0485</v>
       </c>
       <c r="N31" t="n">
         <v>151</v>
@@ -1872,173 +1872,173 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.875</v>
+        <v>-0.2951</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3521</v>
+        <v>-0.1187</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7925</v>
+        <v>-0.7712</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.875</v>
+        <v>-0.2951</v>
       </c>
       <c r="F32" t="n">
-        <v>0.125</v>
+        <v>0.6076</v>
       </c>
       <c r="G32" t="n">
-        <v>-1</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>0.125</v>
+        <v>0.6076</v>
       </c>
       <c r="I32" t="n">
-        <v>0.125</v>
+        <v>0.3159</v>
       </c>
       <c r="J32" t="n">
-        <v>-1</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="K32" t="n">
         <v>162</v>
       </c>
       <c r="L32" t="n">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.875</v>
+        <v>-0.5868</v>
       </c>
       <c r="N32" t="n">
-        <v>231</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9032</v>
+        <v>-0.3737</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3634</v>
+        <v>-0.1504</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8037</v>
+        <v>-0.8067</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9032</v>
+        <v>-0.3737</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.217</v>
+        <v>-0.3737</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.6862</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.217</v>
+        <v>-0.3737</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1759</v>
+        <v>-0.3737</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.6862</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L33" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8621000000000001</v>
+        <v>-0.3737</v>
       </c>
       <c r="N33" t="n">
-        <v>227</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0657</v>
+        <v>-0.4275</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4288</v>
+        <v>-0.172</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8685</v>
+        <v>-0.831</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0657</v>
+        <v>-0.4275</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0495</v>
+        <v>0.0721</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.0162</v>
+        <v>-0.4996</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.0495</v>
+        <v>0.0721</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0401</v>
+        <v>0.0721</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.0162</v>
+        <v>-0.4996</v>
       </c>
       <c r="K34" t="n">
         <v>162</v>
       </c>
       <c r="L34" t="n">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0563</v>
+        <v>-0.4275</v>
       </c>
       <c r="N34" t="n">
-        <v>297</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1055</v>
+        <v>-0.5715</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4448</v>
+        <v>-0.23</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8843</v>
+        <v>-0.896</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1055</v>
+        <v>-0.5715</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3029</v>
+        <v>0.4285</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.8026</v>
+        <v>-1</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3029</v>
+        <v>0.4285</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3029</v>
+        <v>0.4285</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8026</v>
+        <v>-1</v>
       </c>
       <c r="K35" t="n">
         <v>162</v>
@@ -2047,7 +2047,7 @@
         <v>69</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1055</v>
+        <v>-0.5715</v>
       </c>
       <c r="N35" t="n">
         <v>231</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2246</v>
+        <v>-0.7024</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4928</v>
+        <v>-0.2826</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9318</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2246</v>
+        <v>-0.7024</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.607</v>
+        <v>-0.2738</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.6176</v>
+        <v>-0.4286</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.607</v>
+        <v>-0.2738</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.607</v>
+        <v>-0.2738</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6176</v>
+        <v>-0.4286</v>
       </c>
       <c r="K36" t="n">
         <v>162</v>
@@ -2093,7 +2093,7 @@
         <v>69</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.2246</v>
+        <v>-0.7023999999999999</v>
       </c>
       <c r="N36" t="n">
         <v>231</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2941</v>
+        <v>-0.7439</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.2993</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9595</v>
+        <v>-0.9738</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2941</v>
+        <v>-0.7439</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2941</v>
+        <v>-0.7439</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2941</v>
+        <v>-0.7439</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2941</v>
+        <v>-0.7439</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2941</v>
+        <v>-0.7439</v>
       </c>
       <c r="N37" t="n">
         <v>151</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2944</v>
+        <v>-0.75</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5208</v>
+        <v>-0.3018</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9596</v>
+        <v>-0.9766</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2944</v>
+        <v>-0.75</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2944</v>
+        <v>-0.75</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2944</v>
+        <v>-0.75</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2944</v>
+        <v>-0.75</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2944</v>
+        <v>-0.75</v>
       </c>
       <c r="N38" t="n">
         <v>154</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3534</v>
+        <v>-0.8022</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5446</v>
+        <v>-0.3228</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9831</v>
+        <v>-1.0002</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3534</v>
+        <v>-0.8022</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5322</v>
+        <v>-1.0591</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1788</v>
+        <v>0.2569</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5322</v>
+        <v>-1.0591</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2419</v>
+        <v>-0.5507</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1788</v>
+        <v>0.2569</v>
       </c>
       <c r="K39" t="n">
         <v>145</v>
@@ -2231,7 +2231,7 @@
         <v>82</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0631</v>
+        <v>-0.2938</v>
       </c>
       <c r="N39" t="n">
         <v>227</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6051</v>
+        <v>-0.9843</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6459</v>
+        <v>-0.3961</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0834</v>
+        <v>-1.0824</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6051</v>
+        <v>-0.9843</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.6051</v>
+        <v>-0.9843</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6051</v>
+        <v>-0.9843</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.6051</v>
+        <v>-0.9843</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.6051</v>
+        <v>-0.9843</v>
       </c>
       <c r="N40" t="n">
         <v>151</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.6954</v>
+        <v>-1.0864</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6822</v>
+        <v>-0.4372</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1194</v>
+        <v>-1.1285</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6954</v>
+        <v>-1.0864</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.6954</v>
+        <v>-1.0864</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.6954</v>
+        <v>-1.0864</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.6954</v>
+        <v>-1.0864</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.6954</v>
+        <v>-1.0864</v>
       </c>
       <c r="N41" t="n">
         <v>154</v>
@@ -2429,10 +2429,10 @@
         <v>1.4</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5795</v>
+        <v>0.5105</v>
       </c>
       <c r="J2" t="n">
-        <v>15.6465</v>
+        <v>13.7835</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.38</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5546</v>
+        <v>0.4881</v>
       </c>
       <c r="J3" t="n">
-        <v>14.9742</v>
+        <v>13.1787</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.37</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5421</v>
+        <v>0.4769</v>
       </c>
       <c r="J4" t="n">
-        <v>14.6367</v>
+        <v>12.8763</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0402</v>
+        <v>0.0014</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.0854</v>
+        <v>0.0378</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.91</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.26</v>
+        <v>-0.1453</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.02</v>
+        <v>-3.9231</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.07</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2202</v>
+        <v>0.1666</v>
       </c>
       <c r="J7" t="n">
-        <v>5.9454</v>
+        <v>4.4982</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0.163</v>
+        <v>0.1125</v>
       </c>
       <c r="J8" t="n">
-        <v>4.401</v>
+        <v>3.0375</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.91</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1447</v>
+        <v>-0.1122</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.9069</v>
+        <v>-3.0294</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4952</v>
+        <v>-0.3221</v>
       </c>
       <c r="J10" t="n">
-        <v>-13.3704</v>
+        <v>-8.6967</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.7</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4952</v>
+        <v>-0.3221</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.3704</v>
+        <v>-8.6967</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.82</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1908</v>
+        <v>-0.1707</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.0068</v>
+        <v>-3.5847</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.78</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2544</v>
+        <v>-0.2137</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.3424</v>
+        <v>-4.4877</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.67</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4391</v>
+        <v>-0.3207</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.2211</v>
+        <v>-6.7347</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.64</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4996</v>
+        <v>-0.3471</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.4916</v>
+        <v>-7.2891</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.43</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7936</v>
+        <v>-0.5432</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.6656</v>
+        <v>-11.4072</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.78</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6192</v>
+        <v>1.4176</v>
       </c>
       <c r="J17" t="n">
-        <v>34.0032</v>
+        <v>29.7696</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.66</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3984</v>
+        <v>1.28</v>
       </c>
       <c r="J18" t="n">
-        <v>29.3664</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.56</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2007</v>
+        <v>1.164</v>
       </c>
       <c r="J19" t="n">
-        <v>25.2147</v>
+        <v>24.444</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.26</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5258</v>
+        <v>0.6453</v>
       </c>
       <c r="J20" t="n">
-        <v>11.0418</v>
+        <v>13.5513</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3884</v>
+        <v>0.5008</v>
       </c>
       <c r="J21" t="n">
-        <v>8.1564</v>
+        <v>10.5168</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.98</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0664</v>
+        <v>0.0204</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3944</v>
+        <v>0.4284</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.86</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1566</v>
+        <v>-0.1421</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.2886</v>
+        <v>-2.9841</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.75</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3394</v>
+        <v>-0.2554</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.1274</v>
+        <v>-5.3634</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.63</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5448</v>
+        <v>-0.366</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.4408</v>
+        <v>-7.686</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.43</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8068</v>
+        <v>-0.5525</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.9428</v>
+        <v>-11.6025</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.56</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2593</v>
+        <v>1.1807</v>
       </c>
       <c r="J27" t="n">
-        <v>26.4453</v>
+        <v>24.7947</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.44</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0108</v>
+        <v>1.0324</v>
       </c>
       <c r="J28" t="n">
-        <v>21.2268</v>
+        <v>21.6804</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.37</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8368</v>
+        <v>0.9124</v>
       </c>
       <c r="J29" t="n">
-        <v>17.5728</v>
+        <v>19.1604</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.26</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5693</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>11.9553</v>
+        <v>14.0679</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.23</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4984</v>
+        <v>0.599</v>
       </c>
       <c r="J31" t="n">
-        <v>10.4664</v>
+        <v>12.579</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.12</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2545</v>
+        <v>0.282</v>
       </c>
       <c r="J32" t="n">
-        <v>6.3625</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.11</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2379</v>
+        <v>0.2622</v>
       </c>
       <c r="J33" t="n">
-        <v>5.9475</v>
+        <v>6.555</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.03</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0822</v>
+        <v>0.089</v>
       </c>
       <c r="J34" t="n">
-        <v>2.055</v>
+        <v>2.225</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1618</v>
+        <v>-0.09</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.045</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.89</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2501</v>
+        <v>-0.1473</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.2525</v>
+        <v>-3.6825</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.4</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0658</v>
+        <v>0.7611</v>
       </c>
       <c r="J37" t="n">
-        <v>26.645</v>
+        <v>19.0275</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.33</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.6654</v>
       </c>
       <c r="J38" t="n">
-        <v>22.845</v>
+        <v>16.635</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.04</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0974</v>
+        <v>0.143</v>
       </c>
       <c r="J39" t="n">
-        <v>2.435</v>
+        <v>3.575</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.99</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1415</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.5375</v>
+        <v>-1.9675</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.76</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7986</v>
+        <v>-0.7531</v>
       </c>
       <c r="J41" t="n">
-        <v>-19.965</v>
+        <v>-18.8275</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.46</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6611</v>
+        <v>0.4809</v>
       </c>
       <c r="J42" t="n">
-        <v>19.1719</v>
+        <v>13.9461</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.42</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.4546</v>
       </c>
       <c r="J43" t="n">
-        <v>17.7886</v>
+        <v>13.1834</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.37</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5518</v>
+        <v>0.4214</v>
       </c>
       <c r="J44" t="n">
-        <v>16.0022</v>
+        <v>12.2206</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.06</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0711</v>
+        <v>0.0948</v>
       </c>
       <c r="J45" t="n">
-        <v>2.0619</v>
+        <v>2.7492</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.6</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6673</v>
+        <v>-0.4455</v>
       </c>
       <c r="J46" t="n">
-        <v>-19.3517</v>
+        <v>-12.9195</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.14</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2912</v>
+        <v>0.248</v>
       </c>
       <c r="J47" t="n">
-        <v>8.444800000000001</v>
+        <v>7.192</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.12</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2591</v>
+        <v>0.2181</v>
       </c>
       <c r="J48" t="n">
-        <v>7.5139</v>
+        <v>6.3249</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.08</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1903</v>
+        <v>0.1558</v>
       </c>
       <c r="J49" t="n">
-        <v>5.5187</v>
+        <v>4.5182</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.85</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3106</v>
+        <v>-0.1886</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.007400000000001</v>
+        <v>-5.4694</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3259</v>
+        <v>-0.199</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.4511</v>
+        <v>-5.771</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3157</v>
+        <v>0.3333</v>
       </c>
       <c r="J52" t="n">
-        <v>8.839600000000001</v>
+        <v>9.3324</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.07</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2312</v>
+        <v>0.2287</v>
       </c>
       <c r="J53" t="n">
-        <v>6.4736</v>
+        <v>6.4036</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.91</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1298</v>
+        <v>-0.1087</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.6344</v>
+        <v>-3.0436</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.66</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5423</v>
+        <v>-0.3563</v>
       </c>
       <c r="J55" t="n">
-        <v>-15.1844</v>
+        <v>-9.9764</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.52</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7202</v>
+        <v>-0.4862</v>
       </c>
       <c r="J56" t="n">
-        <v>-20.1656</v>
+        <v>-13.6136</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.69</v>
       </c>
       <c r="I57" t="n">
-        <v>1.5862</v>
+        <v>1.1071</v>
       </c>
       <c r="J57" t="n">
-        <v>44.4136</v>
+        <v>30.9988</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5917</v>
+        <v>0.4951</v>
       </c>
       <c r="J58" t="n">
-        <v>16.5676</v>
+        <v>13.8628</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.12</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2946</v>
+        <v>0.348</v>
       </c>
       <c r="J59" t="n">
-        <v>8.248799999999999</v>
+        <v>9.744</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1226</v>
+        <v>-0.0481</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.4328</v>
+        <v>-1.3468</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.96</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.295</v>
+        <v>-0.2165</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.26</v>
+        <v>-6.062</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.88</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.031</v>
+        <v>-0.0552</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.527</v>
+        <v>-0.9384</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.86</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0643</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.0931</v>
+        <v>-1.3719</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.37</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.8411999999999999</v>
+        <v>-0.5805</v>
       </c>
       <c r="J64" t="n">
-        <v>-14.3004</v>
+        <v>-9.868499999999999</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.34</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.8806</v>
+        <v>-0.6098</v>
       </c>
       <c r="J65" t="n">
-        <v>-14.9702</v>
+        <v>-10.3666</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.33</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8935</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.1895</v>
+        <v>-10.5315</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>2.21</v>
       </c>
       <c r="I67" t="n">
-        <v>1.322</v>
+        <v>0.8728</v>
       </c>
       <c r="J67" t="n">
-        <v>22.474</v>
+        <v>14.8376</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.71</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8357</v>
+        <v>0.5971</v>
       </c>
       <c r="J68" t="n">
-        <v>14.2069</v>
+        <v>10.1507</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.4</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4589</v>
+        <v>0.4161</v>
       </c>
       <c r="J69" t="n">
-        <v>7.8013</v>
+        <v>7.0737</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.33</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3748</v>
+        <v>0.3708</v>
       </c>
       <c r="J70" t="n">
-        <v>6.3716</v>
+        <v>6.3036</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.25</v>
       </c>
       <c r="I71" t="n">
-        <v>0.2754</v>
+        <v>0.3038</v>
       </c>
       <c r="J71" t="n">
-        <v>4.6818</v>
+        <v>5.1646</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.41</v>
       </c>
       <c r="I72" t="n">
-        <v>1.1009</v>
+        <v>0.7821</v>
       </c>
       <c r="J72" t="n">
-        <v>31.9261</v>
+        <v>22.6809</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.32</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9058</v>
+        <v>0.658</v>
       </c>
       <c r="J73" t="n">
-        <v>26.2682</v>
+        <v>19.082</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.08</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2674</v>
+        <v>0.2708</v>
       </c>
       <c r="J74" t="n">
-        <v>7.7546</v>
+        <v>7.8532</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.9</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4336</v>
+        <v>-0.3711</v>
       </c>
       <c r="J75" t="n">
-        <v>-12.5744</v>
+        <v>-10.7619</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.9716</v>
+        <v>-0.9441000000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>-28.1764</v>
+        <v>-27.3789</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.11</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2584</v>
+        <v>0.2766</v>
       </c>
       <c r="J77" t="n">
-        <v>7.4936</v>
+        <v>8.0214</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2417</v>
+        <v>0.2561</v>
       </c>
       <c r="J78" t="n">
-        <v>7.0093</v>
+        <v>7.4269</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.1</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2417</v>
+        <v>0.2561</v>
       </c>
       <c r="J79" t="n">
-        <v>7.0093</v>
+        <v>7.4269</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.76</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.432</v>
+        <v>-0.2743</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.528</v>
+        <v>-7.9547</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.75</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4459</v>
+        <v>-0.2841</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.9311</v>
+        <v>-8.238899999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>1.5711</v>
+        <v>1.1028</v>
       </c>
       <c r="J82" t="n">
-        <v>31.422</v>
+        <v>22.056</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.45</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0446</v>
+        <v>0.776</v>
       </c>
       <c r="J83" t="n">
-        <v>20.892</v>
+        <v>15.52</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.44</v>
       </c>
       <c r="I84" t="n">
-        <v>1.023</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="J84" t="n">
-        <v>20.46</v>
+        <v>15.272</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.11</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2053</v>
+        <v>0.2958</v>
       </c>
       <c r="J85" t="n">
-        <v>4.106</v>
+        <v>5.916</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.03</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.0343</v>
+        <v>0.0489</v>
       </c>
       <c r="J86" t="n">
-        <v>-0.6860000000000001</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.91</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>-1.7</v>
+        <v>-1.826</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.88</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1372</v>
+        <v>-0.1262</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.744</v>
+        <v>-2.524</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.86</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1711</v>
+        <v>-0.1484</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.422</v>
+        <v>-2.968</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.6</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5966</v>
+        <v>-0.3988</v>
       </c>
       <c r="J90" t="n">
-        <v>-11.932</v>
+        <v>-7.976</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.55</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.4455</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.256</v>
+        <v>-8.91</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.34</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4845</v>
+        <v>0.3937</v>
       </c>
       <c r="J92" t="n">
-        <v>12.1125</v>
+        <v>9.842499999999999</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.28</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3977</v>
+        <v>0.3543</v>
       </c>
       <c r="J93" t="n">
-        <v>9.942500000000001</v>
+        <v>8.8575</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.26</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3606</v>
+        <v>0.3399</v>
       </c>
       <c r="J94" t="n">
-        <v>9.015000000000001</v>
+        <v>8.4975</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.24</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3296</v>
+        <v>0.3217</v>
       </c>
       <c r="J95" t="n">
-        <v>8.24</v>
+        <v>8.0425</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.24</v>
       </c>
       <c r="I96" t="n">
-        <v>0.3296</v>
+        <v>0.3217</v>
       </c>
       <c r="J96" t="n">
-        <v>8.24</v>
+        <v>8.0425</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.0847</v>
+        <v>0.0357</v>
       </c>
       <c r="J97" t="n">
-        <v>2.1175</v>
+        <v>0.8925</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.89</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1504</v>
+        <v>-0.1266</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.76</v>
+        <v>-3.165</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.85</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2219</v>
+        <v>-0.1692</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.5475</v>
+        <v>-4.23</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4921</v>
+        <v>-0.3234</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.3025</v>
+        <v>-8.085000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4921</v>
+        <v>-0.3234</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.3025</v>
+        <v>-8.085000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.91</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.0702</v>
+        <v>-0.0834</v>
       </c>
       <c r="J102" t="n">
-        <v>-1.404</v>
+        <v>-1.668</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.78</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.287</v>
+        <v>-0.226</v>
       </c>
       <c r="J103" t="n">
-        <v>-5.74</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.73</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3767</v>
+        <v>-0.2735</v>
       </c>
       <c r="J104" t="n">
-        <v>-7.534</v>
+        <v>-5.47</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4532</v>
+        <v>-0.3097</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.064</v>
+        <v>-6.194</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.53</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6805</v>
+        <v>-0.4592</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.61</v>
+        <v>-9.183999999999999</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.76</v>
       </c>
       <c r="I107" t="n">
-        <v>1.6207</v>
+        <v>1.1384</v>
       </c>
       <c r="J107" t="n">
-        <v>32.414</v>
+        <v>22.768</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.63</v>
       </c>
       <c r="I108" t="n">
-        <v>1.3813</v>
+        <v>0.9857</v>
       </c>
       <c r="J108" t="n">
-        <v>27.626</v>
+        <v>19.714</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.29</v>
       </c>
       <c r="I109" t="n">
-        <v>0.6261</v>
+        <v>0.569</v>
       </c>
       <c r="J109" t="n">
-        <v>12.522</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.23</v>
       </c>
       <c r="I110" t="n">
-        <v>0.487</v>
+        <v>0.4864</v>
       </c>
       <c r="J110" t="n">
-        <v>9.74</v>
+        <v>9.728</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.1</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1628</v>
+        <v>0.2562</v>
       </c>
       <c r="J111" t="n">
-        <v>3.256</v>
+        <v>5.124</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.17</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3538</v>
+        <v>0.3705</v>
       </c>
       <c r="J112" t="n">
-        <v>10.2602</v>
+        <v>10.7445</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1905</v>
+        <v>0.1935</v>
       </c>
       <c r="J113" t="n">
-        <v>5.5245</v>
+        <v>5.6115</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.02</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0876</v>
+        <v>0.0737</v>
       </c>
       <c r="J114" t="n">
-        <v>2.5404</v>
+        <v>2.1373</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.79</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3883</v>
+        <v>-0.2442</v>
       </c>
       <c r="J115" t="n">
-        <v>-11.2607</v>
+        <v>-7.0818</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.75</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.445</v>
+        <v>-0.2836</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.905</v>
+        <v>-8.224399999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.54</v>
       </c>
       <c r="I117" t="n">
-        <v>1.3345</v>
+        <v>0.9374</v>
       </c>
       <c r="J117" t="n">
-        <v>38.7005</v>
+        <v>27.1846</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.16</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4743</v>
+        <v>0.4161</v>
       </c>
       <c r="J118" t="n">
-        <v>13.7547</v>
+        <v>12.0669</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.12</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3384</v>
+        <v>0.3561</v>
       </c>
       <c r="J119" t="n">
-        <v>9.813599999999999</v>
+        <v>10.3269</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.96</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2713</v>
+        <v>-0.1999</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.8677</v>
+        <v>-5.7971</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.89</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4827</v>
+        <v>-0.4152</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.9983</v>
+        <v>-12.0408</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.2806</v>
+        <v>-0.2433</v>
       </c>
       <c r="J122" t="n">
-        <v>-4.4896</v>
+        <v>-3.8928</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.66</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.3262</v>
+        <v>-0.2773</v>
       </c>
       <c r="J123" t="n">
-        <v>-5.2192</v>
+        <v>-4.4368</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.43</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.7217</v>
+        <v>-0.5056</v>
       </c>
       <c r="J124" t="n">
-        <v>-11.5472</v>
+        <v>-8.089600000000001</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.42</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.7377</v>
+        <v>-0.5151</v>
       </c>
       <c r="J125" t="n">
-        <v>-11.8032</v>
+        <v>-8.2416</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.2</v>
       </c>
       <c r="I126" t="n">
-        <v>-1.0429</v>
+        <v>-0.7367</v>
       </c>
       <c r="J126" t="n">
-        <v>-16.6864</v>
+        <v>-11.7872</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>2.27</v>
       </c>
       <c r="I127" t="n">
-        <v>2.0872</v>
+        <v>1.659</v>
       </c>
       <c r="J127" t="n">
-        <v>33.3952</v>
+        <v>26.544</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.82</v>
       </c>
       <c r="I128" t="n">
-        <v>1.646</v>
+        <v>1.1715</v>
       </c>
       <c r="J128" t="n">
-        <v>26.336</v>
+        <v>18.744</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.4</v>
       </c>
       <c r="I129" t="n">
-        <v>0.792</v>
+        <v>0.6894</v>
       </c>
       <c r="J129" t="n">
-        <v>12.672</v>
+        <v>11.0304</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.33</v>
       </c>
       <c r="I130" t="n">
-        <v>0.6464</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="J130" t="n">
-        <v>10.3424</v>
+        <v>9.588800000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.18</v>
       </c>
       <c r="I131" t="n">
-        <v>0.3153</v>
+        <v>0.3905</v>
       </c>
       <c r="J131" t="n">
-        <v>5.0448</v>
+        <v>6.248</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.35</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5557</v>
+        <v>0.4188</v>
       </c>
       <c r="J132" t="n">
-        <v>14.4482</v>
+        <v>10.8888</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.26</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4378</v>
+        <v>0.3551</v>
       </c>
       <c r="J133" t="n">
-        <v>11.3828</v>
+        <v>9.2326</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.13</v>
       </c>
       <c r="I134" t="n">
-        <v>0.243</v>
+        <v>0.2041</v>
       </c>
       <c r="J134" t="n">
-        <v>6.318</v>
+        <v>5.3066</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1825</v>
+        <v>-0.0974</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.745</v>
+        <v>-2.5324</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.76</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4564</v>
+        <v>-0.2882</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.8664</v>
+        <v>-7.4932</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.09</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2074</v>
+        <v>0.1714</v>
       </c>
       <c r="J137" t="n">
-        <v>5.3924</v>
+        <v>4.4564</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1709</v>
+        <v>0.1392</v>
       </c>
       <c r="J138" t="n">
-        <v>4.4434</v>
+        <v>3.6192</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1106</v>
+        <v>0.0877</v>
       </c>
       <c r="J139" t="n">
-        <v>2.8756</v>
+        <v>2.2802</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0004</v>
       </c>
       <c r="J140" t="n">
-        <v>-0.2054</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.84</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3264</v>
+        <v>-0.1993</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.4864</v>
+        <v>-5.1818</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.14</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2942</v>
+        <v>0.3243</v>
       </c>
       <c r="J142" t="n">
-        <v>7.9434</v>
+        <v>8.7561</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.12</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2621</v>
+        <v>0.2871</v>
       </c>
       <c r="J143" t="n">
-        <v>7.0767</v>
+        <v>7.7517</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1346</v>
+        <v>-0.0757</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.6342</v>
+        <v>-2.0439</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1545</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.1715</v>
+        <v>-2.3733</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.84</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3239</v>
+        <v>-0.1981</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.7453</v>
+        <v>-5.3487</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.27</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7487</v>
+        <v>0.5717</v>
       </c>
       <c r="J147" t="n">
-        <v>20.2149</v>
+        <v>15.4359</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.24</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6755</v>
+        <v>0.5295</v>
       </c>
       <c r="J148" t="n">
-        <v>18.2385</v>
+        <v>14.2965</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.19</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5452</v>
+        <v>0.4579</v>
       </c>
       <c r="J149" t="n">
-        <v>14.7204</v>
+        <v>12.3633</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.16</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4572</v>
+        <v>0.4143</v>
       </c>
       <c r="J150" t="n">
-        <v>12.3444</v>
+        <v>11.1861</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.9</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4611</v>
+        <v>-0.3912</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.4497</v>
+        <v>-10.5624</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.58</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7909</v>
+        <v>0.709</v>
       </c>
       <c r="J152" t="n">
-        <v>22.9361</v>
+        <v>20.561</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.54</v>
       </c>
       <c r="I153" t="n">
-        <v>0.7463</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="J153" t="n">
-        <v>21.6427</v>
+        <v>19.3082</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.18</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2632</v>
+        <v>0.2572</v>
       </c>
       <c r="J154" t="n">
-        <v>7.6328</v>
+        <v>7.4588</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.99</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1057</v>
+        <v>-0.0404</v>
       </c>
       <c r="J155" t="n">
-        <v>-3.0653</v>
+        <v>-1.1716</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.74</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4994</v>
+        <v>-0.3186</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.4826</v>
+        <v>-9.2394</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.12</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2934</v>
+        <v>0.3137</v>
       </c>
       <c r="J157" t="n">
-        <v>8.508599999999999</v>
+        <v>9.097300000000001</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.01</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0819</v>
+        <v>0.056</v>
       </c>
       <c r="J158" t="n">
-        <v>2.3751</v>
+        <v>1.624</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.9</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1915</v>
+        <v>-0.1253</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.5535</v>
+        <v>-3.6337</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.78</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3902</v>
+        <v>-0.2485</v>
       </c>
       <c r="J160" t="n">
-        <v>-11.3158</v>
+        <v>-7.2065</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.76</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4192</v>
+        <v>-0.2681</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.1568</v>
+        <v>-7.7749</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.38</v>
       </c>
       <c r="I162" t="n">
-        <v>0.598</v>
+        <v>0.517</v>
       </c>
       <c r="J162" t="n">
-        <v>16.146</v>
+        <v>13.959</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.14</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2663</v>
+        <v>0.2196</v>
       </c>
       <c r="J163" t="n">
-        <v>7.1901</v>
+        <v>5.9292</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.01</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.002</v>
+        <v>0.0195</v>
       </c>
       <c r="J164" t="n">
-        <v>-0.054</v>
+        <v>0.5265</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1398</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.7746</v>
+        <v>-1.9035</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.87</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2957</v>
+        <v>-0.1749</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.9839</v>
+        <v>-4.7223</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.28</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4806</v>
+        <v>0.5682</v>
       </c>
       <c r="J167" t="n">
-        <v>12.9762</v>
+        <v>15.3414</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.09</v>
       </c>
       <c r="I168" t="n">
-        <v>0.194</v>
+        <v>0.2172</v>
       </c>
       <c r="J168" t="n">
-        <v>5.238</v>
+        <v>5.8644</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0376</v>
+        <v>0.0612</v>
       </c>
       <c r="J169" t="n">
-        <v>1.0152</v>
+        <v>1.6524</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.169</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.563</v>
+        <v>-2.4921</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.87</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2882</v>
+        <v>-0.1714</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.7814</v>
+        <v>-4.6278</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.9</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0484</v>
+        <v>-0.0708</v>
       </c>
       <c r="J172" t="n">
-        <v>-0.9196</v>
+        <v>-1.3452</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.79</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2279</v>
+        <v>-0.1978</v>
       </c>
       <c r="J173" t="n">
-        <v>-4.3301</v>
+        <v>-3.7582</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.77</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2594</v>
+        <v>-0.2191</v>
       </c>
       <c r="J174" t="n">
-        <v>-4.9286</v>
+        <v>-4.1629</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.48</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.4927</v>
       </c>
       <c r="J175" t="n">
-        <v>-13.7427</v>
+        <v>-9.3613</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.3</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.949</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="J176" t="n">
-        <v>-18.031</v>
+        <v>-12.5932</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>2.09</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2354</v>
+        <v>1.0937</v>
       </c>
       <c r="J177" t="n">
-        <v>23.4726</v>
+        <v>20.7803</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.6</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7411</v>
+        <v>0.6845</v>
       </c>
       <c r="J178" t="n">
-        <v>14.0809</v>
+        <v>13.0055</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.47</v>
       </c>
       <c r="I179" t="n">
-        <v>0.5747</v>
+        <v>0.555</v>
       </c>
       <c r="J179" t="n">
-        <v>10.9193</v>
+        <v>10.545</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.3</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3564</v>
+        <v>0.3726</v>
       </c>
       <c r="J180" t="n">
-        <v>6.7716</v>
+        <v>7.0794</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.92</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2783</v>
+        <v>-0.1556</v>
       </c>
       <c r="J181" t="n">
-        <v>-5.2877</v>
+        <v>-2.9564</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.29</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5301</v>
+        <v>0.6273</v>
       </c>
       <c r="J182" t="n">
-        <v>14.3127</v>
+        <v>16.9371</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.15</v>
       </c>
       <c r="I183" t="n">
-        <v>0.333</v>
+        <v>0.3664</v>
       </c>
       <c r="J183" t="n">
-        <v>8.991</v>
+        <v>9.892799999999999</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.85</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2888</v>
+        <v>-0.1802</v>
       </c>
       <c r="J184" t="n">
-        <v>-7.7976</v>
+        <v>-4.8654</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.75</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4387</v>
+        <v>-0.2804</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.8449</v>
+        <v>-7.5708</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.63</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.598</v>
+        <v>-0.3943</v>
       </c>
       <c r="J186" t="n">
-        <v>-16.146</v>
+        <v>-10.6461</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.43</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6307</v>
+        <v>0.5535</v>
       </c>
       <c r="J187" t="n">
-        <v>17.0289</v>
+        <v>14.9445</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.22</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3545</v>
+        <v>0.3091</v>
       </c>
       <c r="J188" t="n">
-        <v>9.5715</v>
+        <v>8.345700000000001</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.15</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2326</v>
+        <v>0.2232</v>
       </c>
       <c r="J189" t="n">
-        <v>6.2802</v>
+        <v>6.0264</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.1</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1469</v>
+        <v>0.1563</v>
       </c>
       <c r="J190" t="n">
-        <v>3.9663</v>
+        <v>4.2201</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.92</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2345</v>
+        <v>-0.129</v>
       </c>
       <c r="J191" t="n">
-        <v>-6.3315</v>
+        <v>-3.483</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>0.93</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.065</v>
+        <v>-0.0747</v>
       </c>
       <c r="J192" t="n">
-        <v>-1.43</v>
+        <v>-1.6434</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.85</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2062</v>
+        <v>-0.1654</v>
       </c>
       <c r="J193" t="n">
-        <v>-4.5364</v>
+        <v>-3.6388</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.84</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2235</v>
+        <v>-0.1758</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.917</v>
+        <v>-3.8676</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.72</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4385</v>
+        <v>-0.291</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.647</v>
+        <v>-6.402</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.64</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.553</v>
+        <v>-0.3666</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.166</v>
+        <v>-8.065200000000001</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.67</v>
       </c>
       <c r="I197" t="n">
-        <v>1.4696</v>
+        <v>1.3126</v>
       </c>
       <c r="J197" t="n">
-        <v>32.3312</v>
+        <v>28.8772</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.51</v>
       </c>
       <c r="I198" t="n">
-        <v>1.1589</v>
+        <v>1.1202</v>
       </c>
       <c r="J198" t="n">
-        <v>25.4958</v>
+        <v>24.6444</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.48</v>
       </c>
       <c r="I199" t="n">
-        <v>1.0967</v>
+        <v>1.0836</v>
       </c>
       <c r="J199" t="n">
-        <v>24.1274</v>
+        <v>23.8392</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.2</v>
       </c>
       <c r="I200" t="n">
-        <v>0.4264</v>
+        <v>0.526</v>
       </c>
       <c r="J200" t="n">
-        <v>9.380800000000001</v>
+        <v>11.572</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.175</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="J201" t="n">
-        <v>-3.85</v>
+        <v>-1.9558</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.6</v>
       </c>
       <c r="I202" t="n">
-        <v>1.3738</v>
+        <v>1.2451</v>
       </c>
       <c r="J202" t="n">
-        <v>28.8498</v>
+        <v>26.1471</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.52</v>
       </c>
       <c r="I203" t="n">
-        <v>1.2176</v>
+        <v>1.1464</v>
       </c>
       <c r="J203" t="n">
-        <v>25.5696</v>
+        <v>24.0744</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.16</v>
       </c>
       <c r="I204" t="n">
-        <v>0.358</v>
+        <v>0.4427</v>
       </c>
       <c r="J204" t="n">
-        <v>7.518</v>
+        <v>9.2967</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.1</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1976</v>
+        <v>0.2809</v>
       </c>
       <c r="J205" t="n">
-        <v>4.1496</v>
+        <v>5.8989</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.08</v>
       </c>
       <c r="I206" t="n">
-        <v>0.1406</v>
+        <v>0.2229</v>
       </c>
       <c r="J206" t="n">
-        <v>2.9526</v>
+        <v>4.6809</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.02</v>
       </c>
       <c r="I207" t="n">
-        <v>0.1392</v>
+        <v>0.1121</v>
       </c>
       <c r="J207" t="n">
-        <v>2.9232</v>
+        <v>2.3541</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.92</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1017</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.1357</v>
+        <v>-1.9782</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.86</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2109</v>
+        <v>-0.1603</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.4289</v>
+        <v>-3.3663</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.76</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3936</v>
+        <v>-0.258</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.265599999999999</v>
+        <v>-5.418</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.62</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5903</v>
+        <v>-0.3911</v>
       </c>
       <c r="J211" t="n">
-        <v>-12.3963</v>
+        <v>-8.213100000000001</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.53</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7671</v>
+        <v>0.9547</v>
       </c>
       <c r="J212" t="n">
-        <v>21.4788</v>
+        <v>26.7316</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.29</v>
       </c>
       <c r="I213" t="n">
-        <v>0.4756</v>
+        <v>0.5684</v>
       </c>
       <c r="J213" t="n">
-        <v>13.3168</v>
+        <v>15.9152</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.05</v>
       </c>
       <c r="I214" t="n">
-        <v>0.0793</v>
+        <v>0.1254</v>
       </c>
       <c r="J214" t="n">
-        <v>2.2204</v>
+        <v>3.5112</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3891</v>
+        <v>-0.2396</v>
       </c>
       <c r="J215" t="n">
-        <v>-10.8948</v>
+        <v>-6.7088</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.8</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4031</v>
+        <v>-0.2496</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.2868</v>
+        <v>-6.9888</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.53</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7665</v>
+        <v>0.6818</v>
       </c>
       <c r="J217" t="n">
-        <v>21.462</v>
+        <v>19.0904</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.2</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3493</v>
+        <v>0.2935</v>
       </c>
       <c r="J218" t="n">
-        <v>9.7804</v>
+        <v>8.218</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.04</v>
       </c>
       <c r="I219" t="n">
-        <v>0.0581</v>
+        <v>0.0726</v>
       </c>
       <c r="J219" t="n">
-        <v>1.6268</v>
+        <v>2.0328</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0796</v>
+        <v>-0.0297</v>
       </c>
       <c r="J220" t="n">
-        <v>-2.2288</v>
+        <v>-0.8316</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.73</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4975</v>
+        <v>-0.3181</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.93</v>
+        <v>-8.9068</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.24</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4447</v>
+        <v>0.5162</v>
       </c>
       <c r="J222" t="n">
-        <v>13.341</v>
+        <v>15.486</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.15</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3141</v>
+        <v>0.3491</v>
       </c>
       <c r="J223" t="n">
-        <v>9.423</v>
+        <v>10.473</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.93</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.169</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.07</v>
+        <v>-2.958</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.93</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.169</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.07</v>
+        <v>-2.958</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.68</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5436</v>
+        <v>-0.3536</v>
       </c>
       <c r="J226" t="n">
-        <v>-16.308</v>
+        <v>-10.608</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.36</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5564</v>
+        <v>0.4814</v>
       </c>
       <c r="J227" t="n">
-        <v>16.692</v>
+        <v>14.442</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.36</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5564</v>
+        <v>0.4814</v>
       </c>
       <c r="J228" t="n">
-        <v>16.692</v>
+        <v>14.442</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.25</v>
       </c>
       <c r="I229" t="n">
-        <v>0.4114</v>
+        <v>0.3509</v>
       </c>
       <c r="J229" t="n">
-        <v>12.342</v>
+        <v>10.527</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.85</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3369</v>
+        <v>-0.2017</v>
       </c>
       <c r="J230" t="n">
-        <v>-10.107</v>
+        <v>-6.051</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3943</v>
+        <v>-0.2427</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.829</v>
+        <v>-7.281</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.63</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7851</v>
+        <v>0.7195</v>
       </c>
       <c r="J232" t="n">
-        <v>16.4871</v>
+        <v>15.1095</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.56</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7064</v>
+        <v>0.6489</v>
       </c>
       <c r="J233" t="n">
-        <v>14.8344</v>
+        <v>13.6269</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.53</v>
       </c>
       <c r="I234" t="n">
-        <v>0.6712</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="J234" t="n">
-        <v>14.0952</v>
+        <v>12.9864</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.4</v>
       </c>
       <c r="I235" t="n">
-        <v>0.4946</v>
+        <v>0.4861</v>
       </c>
       <c r="J235" t="n">
-        <v>10.3866</v>
+        <v>10.2081</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.06</v>
       </c>
       <c r="I236" t="n">
-        <v>0.0232</v>
+        <v>0.0655</v>
       </c>
       <c r="J236" t="n">
-        <v>0.4872</v>
+        <v>1.3755</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.85</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1624</v>
+        <v>-0.148</v>
       </c>
       <c r="J237" t="n">
-        <v>-3.4104</v>
+        <v>-3.108</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.8</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2435</v>
+        <v>-0.2018</v>
       </c>
       <c r="J238" t="n">
-        <v>-5.1135</v>
+        <v>-4.2378</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.79</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2597</v>
+        <v>-0.2122</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.4537</v>
+        <v>-4.4562</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.65</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5058</v>
+        <v>-0.3439</v>
       </c>
       <c r="J240" t="n">
-        <v>-10.6218</v>
+        <v>-7.2219</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.45</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7776</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="J241" t="n">
-        <v>-16.3296</v>
+        <v>-11.1447</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.55</v>
       </c>
       <c r="I242" t="n">
-        <v>0.7558</v>
+        <v>0.6753</v>
       </c>
       <c r="J242" t="n">
-        <v>18.895</v>
+        <v>16.8825</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.35</v>
       </c>
       <c r="I243" t="n">
-        <v>0.5172</v>
+        <v>0.4546</v>
       </c>
       <c r="J243" t="n">
-        <v>12.93</v>
+        <v>11.365</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.18</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2607</v>
+        <v>0.2566</v>
       </c>
       <c r="J244" t="n">
-        <v>6.5175</v>
+        <v>6.415</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.04</v>
       </c>
       <c r="I245" t="n">
-        <v>0.026</v>
+        <v>0.0585</v>
       </c>
       <c r="J245" t="n">
-        <v>0.65</v>
+        <v>1.4625</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2091</v>
+        <v>-0.1099</v>
       </c>
       <c r="J246" t="n">
-        <v>-5.2275</v>
+        <v>-2.7475</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.03</v>
       </c>
       <c r="I247" t="n">
-        <v>0.155</v>
+        <v>0.1332</v>
       </c>
       <c r="J247" t="n">
-        <v>3.875</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.91</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1278</v>
+        <v>-0.1082</v>
       </c>
       <c r="J248" t="n">
-        <v>-3.195</v>
+        <v>-2.705</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.8</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3372</v>
+        <v>-0.2209</v>
       </c>
       <c r="J249" t="n">
-        <v>-8.43</v>
+        <v>-5.5225</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.79</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3533</v>
+        <v>-0.2308</v>
       </c>
       <c r="J250" t="n">
-        <v>-8.8325</v>
+        <v>-5.77</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.73</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4439</v>
+        <v>-0.2891</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.0975</v>
+        <v>-7.2275</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.65</v>
       </c>
       <c r="I252" t="n">
-        <v>0.8539</v>
+        <v>0.7723</v>
       </c>
       <c r="J252" t="n">
-        <v>23.0553</v>
+        <v>20.8521</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.23</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3218</v>
+        <v>0.3131</v>
       </c>
       <c r="J253" t="n">
-        <v>8.688599999999999</v>
+        <v>8.4537</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.22</v>
       </c>
       <c r="I254" t="n">
-        <v>0.3064</v>
+        <v>0.3013</v>
       </c>
       <c r="J254" t="n">
-        <v>8.2728</v>
+        <v>8.1351</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.11</v>
       </c>
       <c r="I255" t="n">
-        <v>0.138</v>
+        <v>0.1598</v>
       </c>
       <c r="J255" t="n">
-        <v>3.726</v>
+        <v>4.3146</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.06</v>
       </c>
       <c r="I256" t="n">
-        <v>0.0541</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J256" t="n">
-        <v>1.4607</v>
+        <v>2.322</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.8</v>
       </c>
       <c r="I257" t="n">
-        <v>1.1096</v>
+        <v>1.2791</v>
       </c>
       <c r="J257" t="n">
-        <v>29.9592</v>
+        <v>34.5357</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.85</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2909</v>
+        <v>-0.1809</v>
       </c>
       <c r="J258" t="n">
-        <v>-7.8543</v>
+        <v>-4.8843</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.73</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.4679</v>
+        <v>-0.3005</v>
       </c>
       <c r="J259" t="n">
-        <v>-12.6333</v>
+        <v>-8.1135</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.68</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.3482</v>
       </c>
       <c r="J260" t="n">
-        <v>-14.4396</v>
+        <v>-9.401400000000001</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.64</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5864</v>
+        <v>-0.3857</v>
       </c>
       <c r="J261" t="n">
-        <v>-15.8328</v>
+        <v>-10.4139</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.73</v>
       </c>
       <c r="I262" t="n">
-        <v>0.9297</v>
+        <v>0.848</v>
       </c>
       <c r="J262" t="n">
-        <v>23.2425</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.44</v>
       </c>
       <c r="I263" t="n">
-        <v>0.6072</v>
+        <v>0.5431</v>
       </c>
       <c r="J263" t="n">
-        <v>15.18</v>
+        <v>13.5775</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.41</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5703</v>
+        <v>0.5105</v>
       </c>
       <c r="J264" t="n">
-        <v>14.2575</v>
+        <v>12.7625</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.97</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1653</v>
+        <v>-0.0781</v>
       </c>
       <c r="J265" t="n">
-        <v>-4.1325</v>
+        <v>-1.9525</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.88</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3176</v>
+        <v>-0.185</v>
       </c>
       <c r="J266" t="n">
-        <v>-7.94</v>
+        <v>-4.625</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.15</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3681</v>
+        <v>0.4059</v>
       </c>
       <c r="J267" t="n">
-        <v>9.202500000000001</v>
+        <v>10.1475</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.91</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.123</v>
+        <v>-0.1067</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.075</v>
+        <v>-2.6675</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.83</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2797</v>
+        <v>-0.1903</v>
       </c>
       <c r="J269" t="n">
-        <v>-6.9925</v>
+        <v>-4.7575</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.82</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2982</v>
+        <v>-0.2001</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.455</v>
+        <v>-5.0025</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.5</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.7421</v>
+        <v>-0.5028</v>
       </c>
       <c r="J271" t="n">
-        <v>-18.5525</v>
+        <v>-12.57</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.24</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4082</v>
+        <v>0.3442</v>
       </c>
       <c r="J272" t="n">
-        <v>11.4296</v>
+        <v>9.637600000000001</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.2</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3508</v>
+        <v>0.2942</v>
       </c>
       <c r="J273" t="n">
-        <v>9.8224</v>
+        <v>8.2376</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.05</v>
       </c>
       <c r="I274" t="n">
-        <v>0.0801</v>
+        <v>0.0895</v>
       </c>
       <c r="J274" t="n">
-        <v>2.2428</v>
+        <v>2.506</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.99</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.0784</v>
+        <v>-0.0293</v>
       </c>
       <c r="J275" t="n">
-        <v>-2.1952</v>
+        <v>-0.8204</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.99</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.0784</v>
+        <v>-0.0293</v>
       </c>
       <c r="J276" t="n">
-        <v>-2.1952</v>
+        <v>-0.8204</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.25</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4626</v>
+        <v>0.5387</v>
       </c>
       <c r="J277" t="n">
-        <v>12.9528</v>
+        <v>15.0836</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.14</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3029</v>
+        <v>0.3334</v>
       </c>
       <c r="J278" t="n">
-        <v>8.481199999999999</v>
+        <v>9.3352</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.02</v>
       </c>
       <c r="I279" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0707</v>
       </c>
       <c r="J279" t="n">
-        <v>2.2736</v>
+        <v>1.9796</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.84</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3173</v>
+        <v>-0.1953</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.884399999999999</v>
+        <v>-5.4684</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.62</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.4081</v>
       </c>
       <c r="J281" t="n">
-        <v>-17.2872</v>
+        <v>-11.4268</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.43</v>
       </c>
       <c r="I282" t="n">
-        <v>0.6624</v>
+        <v>0.5785</v>
       </c>
       <c r="J282" t="n">
-        <v>18.5472</v>
+        <v>16.198</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.07</v>
       </c>
       <c r="I283" t="n">
-        <v>0.1453</v>
+        <v>0.1231</v>
       </c>
       <c r="J283" t="n">
-        <v>4.0684</v>
+        <v>3.4468</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.01</v>
       </c>
       <c r="I284" t="n">
-        <v>0.0025</v>
+        <v>0.021</v>
       </c>
       <c r="J284" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.96</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1362</v>
+        <v>-0.0693</v>
       </c>
       <c r="J285" t="n">
-        <v>-3.8136</v>
+        <v>-1.9404</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.83</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3533</v>
+        <v>-0.2154</v>
       </c>
       <c r="J286" t="n">
-        <v>-9.8924</v>
+        <v>-6.0312</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.39</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6192</v>
+        <v>0.753</v>
       </c>
       <c r="J287" t="n">
-        <v>17.3376</v>
+        <v>21.084</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.17</v>
       </c>
       <c r="I288" t="n">
-        <v>0.3238</v>
+        <v>0.3707</v>
       </c>
       <c r="J288" t="n">
-        <v>9.0664</v>
+        <v>10.3796</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1702</v>
+        <v>-0.0927</v>
       </c>
       <c r="J289" t="n">
-        <v>-4.7656</v>
+        <v>-2.5956</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.92</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2065</v>
+        <v>-0.1164</v>
       </c>
       <c r="J290" t="n">
-        <v>-5.782</v>
+        <v>-3.2592</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.8</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3932</v>
+        <v>-0.244</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.0096</v>
+        <v>-6.832</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.29</v>
       </c>
       <c r="I292" t="n">
-        <v>0.6395</v>
+        <v>0.8088</v>
       </c>
       <c r="J292" t="n">
-        <v>14.7085</v>
+        <v>18.6024</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.59</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.5825</v>
+        <v>-0.3952</v>
       </c>
       <c r="J293" t="n">
-        <v>-13.3975</v>
+        <v>-9.089600000000001</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.57</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.6111</v>
+        <v>-0.4139</v>
       </c>
       <c r="J294" t="n">
-        <v>-14.0553</v>
+        <v>-9.5197</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.48</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.7326</v>
+        <v>-0.4982</v>
       </c>
       <c r="J295" t="n">
-        <v>-16.8498</v>
+        <v>-11.4586</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.47</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="J296" t="n">
-        <v>-17.1465</v>
+        <v>-11.6748</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.87</v>
       </c>
       <c r="I297" t="n">
-        <v>1.04</v>
+        <v>0.9573</v>
       </c>
       <c r="J297" t="n">
-        <v>23.92</v>
+        <v>22.0179</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.52</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6664</v>
+        <v>0.6109</v>
       </c>
       <c r="J298" t="n">
-        <v>15.3272</v>
+        <v>14.0507</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.31</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3836</v>
+        <v>0.3903</v>
       </c>
       <c r="J299" t="n">
-        <v>8.822800000000001</v>
+        <v>8.976900000000001</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.27</v>
       </c>
       <c r="I300" t="n">
-        <v>0.3311</v>
+        <v>0.3445</v>
       </c>
       <c r="J300" t="n">
-        <v>7.6153</v>
+        <v>7.9235</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>1.09</v>
       </c>
       <c r="I301" t="n">
-        <v>0.0762</v>
+        <v>0.1134</v>
       </c>
       <c r="J301" t="n">
-        <v>1.7526</v>
+        <v>2.6082</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.32</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.639</v>
       </c>
       <c r="J302" t="n">
-        <v>16.044</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.18</v>
       </c>
       <c r="I303" t="n">
-        <v>0.3424</v>
+        <v>0.3918</v>
       </c>
       <c r="J303" t="n">
-        <v>10.272</v>
+        <v>11.754</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.02</v>
       </c>
       <c r="I304" t="n">
-        <v>0.041</v>
+        <v>0.062</v>
       </c>
       <c r="J304" t="n">
-        <v>1.23</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.83</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3476</v>
+        <v>-0.2125</v>
       </c>
       <c r="J305" t="n">
-        <v>-10.428</v>
+        <v>-6.375</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.82</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3623</v>
+        <v>-0.2227</v>
       </c>
       <c r="J306" t="n">
-        <v>-10.869</v>
+        <v>-6.681</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.2</v>
       </c>
       <c r="I307" t="n">
-        <v>0.3669</v>
+        <v>0.3023</v>
       </c>
       <c r="J307" t="n">
-        <v>11.007</v>
+        <v>9.069000000000001</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.12</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2428</v>
+        <v>0.1959</v>
       </c>
       <c r="J308" t="n">
-        <v>7.284</v>
+        <v>5.877</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.11</v>
       </c>
       <c r="I309" t="n">
-        <v>0.2259</v>
+        <v>0.182</v>
       </c>
       <c r="J309" t="n">
-        <v>6.777</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.93</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1898</v>
+        <v>-0.1052</v>
       </c>
       <c r="J310" t="n">
-        <v>-5.694</v>
+        <v>-3.156</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.88</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2743</v>
+        <v>-0.1615</v>
       </c>
       <c r="J311" t="n">
-        <v>-8.228999999999999</v>
+        <v>-4.845</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.15</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3937</v>
+        <v>0.4406</v>
       </c>
       <c r="J312" t="n">
-        <v>9.842499999999999</v>
+        <v>11.015</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.88</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.1467</v>
+        <v>-0.1302</v>
       </c>
       <c r="J313" t="n">
-        <v>-3.6675</v>
+        <v>-3.255</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.76</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.3662</v>
+        <v>-0.251</v>
       </c>
       <c r="J314" t="n">
-        <v>-9.154999999999999</v>
+        <v>-6.275</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.73</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.416</v>
+        <v>-0.2793</v>
       </c>
       <c r="J315" t="n">
-        <v>-10.4</v>
+        <v>-6.9825</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.38</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.8745000000000001</v>
+        <v>-0.6048</v>
       </c>
       <c r="J316" t="n">
-        <v>-21.8625</v>
+        <v>-15.12</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.55</v>
       </c>
       <c r="I317" t="n">
-        <v>0.728</v>
+        <v>0.6558</v>
       </c>
       <c r="J317" t="n">
-        <v>18.2</v>
+        <v>16.395</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.43</v>
       </c>
       <c r="I318" t="n">
-        <v>0.5866</v>
+        <v>0.5285</v>
       </c>
       <c r="J318" t="n">
-        <v>14.665</v>
+        <v>13.2125</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.38</v>
       </c>
       <c r="I319" t="n">
-        <v>0.5231</v>
+        <v>0.4745</v>
       </c>
       <c r="J319" t="n">
-        <v>13.0775</v>
+        <v>11.8625</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.21</v>
       </c>
       <c r="I320" t="n">
-        <v>0.2728</v>
+        <v>0.2831</v>
       </c>
       <c r="J320" t="n">
-        <v>6.82</v>
+        <v>7.0775</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>1</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.0293</v>
       </c>
       <c r="J321" t="n">
-        <v>-2.295</v>
+        <v>-0.7325</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>0.98</v>
       </c>
       <c r="I322" t="n">
-        <v>0.0072</v>
+        <v>-0.0207</v>
       </c>
       <c r="J322" t="n">
-        <v>0.1944</v>
+        <v>-0.5589</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>0.93</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.0969</v>
+        <v>-0.0868</v>
       </c>
       <c r="J323" t="n">
-        <v>-2.6163</v>
+        <v>-2.3436</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.9</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.1538</v>
+        <v>-0.1212</v>
       </c>
       <c r="J324" t="n">
-        <v>-4.1526</v>
+        <v>-3.2724</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.77</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3896</v>
+        <v>-0.2521</v>
       </c>
       <c r="J325" t="n">
-        <v>-10.5192</v>
+        <v>-6.8067</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.75</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.4193</v>
+        <v>-0.2716</v>
       </c>
       <c r="J326" t="n">
-        <v>-11.3211</v>
+        <v>-7.3332</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.66</v>
       </c>
       <c r="I327" t="n">
-        <v>0.8624000000000001</v>
+        <v>0.781</v>
       </c>
       <c r="J327" t="n">
-        <v>23.2848</v>
+        <v>21.087</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.46</v>
       </c>
       <c r="I328" t="n">
-        <v>0.6381</v>
+        <v>0.5685</v>
       </c>
       <c r="J328" t="n">
-        <v>17.2287</v>
+        <v>15.3495</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.1</v>
       </c>
       <c r="I329" t="n">
-        <v>0.1201</v>
+        <v>0.1448</v>
       </c>
       <c r="J329" t="n">
-        <v>3.2427</v>
+        <v>3.9096</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.07</v>
       </c>
       <c r="I330" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1006</v>
       </c>
       <c r="J330" t="n">
-        <v>1.89</v>
+        <v>2.7162</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>1.02</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.0258</v>
+        <v>0.0162</v>
       </c>
       <c r="J331" t="n">
-        <v>-0.6966</v>
+        <v>0.4374</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.11</v>
       </c>
       <c r="I332" t="n">
-        <v>0.2606</v>
+        <v>0.2784</v>
       </c>
       <c r="J332" t="n">
-        <v>6.7756</v>
+        <v>7.2384</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.1</v>
       </c>
       <c r="I333" t="n">
-        <v>0.2439</v>
+        <v>0.2579</v>
       </c>
       <c r="J333" t="n">
-        <v>6.3414</v>
+        <v>6.7054</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.09</v>
       </c>
       <c r="I334" t="n">
-        <v>0.2269</v>
+        <v>0.237</v>
       </c>
       <c r="J334" t="n">
-        <v>5.8994</v>
+        <v>6.162</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.96</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.0861</v>
+        <v>-0.06</v>
       </c>
       <c r="J335" t="n">
-        <v>-2.2386</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.53</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.7237</v>
+        <v>-0.4884</v>
       </c>
       <c r="J336" t="n">
-        <v>-18.8162</v>
+        <v>-12.6984</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.5</v>
       </c>
       <c r="I337" t="n">
-        <v>0.6917</v>
+        <v>0.6161</v>
       </c>
       <c r="J337" t="n">
-        <v>17.9842</v>
+        <v>16.0186</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.24</v>
       </c>
       <c r="I338" t="n">
-        <v>0.3503</v>
+        <v>0.3257</v>
       </c>
       <c r="J338" t="n">
-        <v>9.107799999999999</v>
+        <v>8.4682</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.2</v>
       </c>
       <c r="I339" t="n">
-        <v>0.2818</v>
+        <v>0.2787</v>
       </c>
       <c r="J339" t="n">
-        <v>7.3268</v>
+        <v>7.2462</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.14</v>
       </c>
       <c r="I340" t="n">
-        <v>0.1894</v>
+        <v>0.2025</v>
       </c>
       <c r="J340" t="n">
-        <v>4.9244</v>
+        <v>5.265</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>1.11</v>
       </c>
       <c r="I341" t="n">
-        <v>0.142</v>
+        <v>0.1617</v>
       </c>
       <c r="J341" t="n">
-        <v>3.692</v>
+        <v>4.2042</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.21</v>
       </c>
       <c r="I342" t="n">
-        <v>0.4184</v>
+        <v>0.478</v>
       </c>
       <c r="J342" t="n">
-        <v>12.1336</v>
+        <v>13.862</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.09</v>
       </c>
       <c r="I343" t="n">
-        <v>0.233</v>
+        <v>0.2418</v>
       </c>
       <c r="J343" t="n">
-        <v>6.757</v>
+        <v>7.0122</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.05</v>
       </c>
       <c r="I344" t="n">
-        <v>0.1597</v>
+        <v>0.1532</v>
       </c>
       <c r="J344" t="n">
-        <v>4.6313</v>
+        <v>4.4428</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.92</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1682</v>
+        <v>-0.1058</v>
       </c>
       <c r="J345" t="n">
-        <v>-4.8778</v>
+        <v>-3.0682</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.44</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.8257</v>
+        <v>-0.5674</v>
       </c>
       <c r="J346" t="n">
-        <v>-23.9453</v>
+        <v>-16.4546</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.45</v>
       </c>
       <c r="I347" t="n">
-        <v>0.651</v>
+        <v>0.5734</v>
       </c>
       <c r="J347" t="n">
-        <v>18.879</v>
+        <v>16.6286</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.29</v>
       </c>
       <c r="I348" t="n">
-        <v>0.4496</v>
+        <v>0.3909</v>
       </c>
       <c r="J348" t="n">
-        <v>13.0384</v>
+        <v>11.3361</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.12</v>
       </c>
       <c r="I349" t="n">
-        <v>0.1766</v>
+        <v>0.1826</v>
       </c>
       <c r="J349" t="n">
-        <v>5.1214</v>
+        <v>5.2954</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>1.01</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.0318</v>
+        <v>0.0062</v>
       </c>
       <c r="J350" t="n">
-        <v>-0.9222</v>
+        <v>0.1798</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>1.01</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.0318</v>
+        <v>0.0062</v>
       </c>
       <c r="J351" t="n">
-        <v>-0.9222</v>
+        <v>0.1798</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.04</v>
       </c>
       <c r="I352" t="n">
-        <v>0.1973</v>
+        <v>0.1814</v>
       </c>
       <c r="J352" t="n">
-        <v>4.9325</v>
+        <v>4.535</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>0.92</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.0852</v>
+        <v>-0.0877</v>
       </c>
       <c r="J353" t="n">
-        <v>-2.13</v>
+        <v>-2.1925</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>0.84</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.2258</v>
+        <v>-0.1764</v>
       </c>
       <c r="J354" t="n">
-        <v>-5.645</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>0.65</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.5404</v>
+        <v>-0.3578</v>
       </c>
       <c r="J355" t="n">
-        <v>-13.51</v>
+        <v>-8.945</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>0.55</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.6722</v>
+        <v>-0.4512</v>
       </c>
       <c r="J356" t="n">
-        <v>-16.805</v>
+        <v>-11.28</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.69</v>
       </c>
       <c r="I357" t="n">
-        <v>0.876</v>
+        <v>0.7974</v>
       </c>
       <c r="J357" t="n">
-        <v>21.9</v>
+        <v>19.935</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>1.39</v>
       </c>
       <c r="I358" t="n">
-        <v>0.53</v>
+        <v>0.4834</v>
       </c>
       <c r="J358" t="n">
-        <v>13.25</v>
+        <v>12.085</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>1.38</v>
       </c>
       <c r="I359" t="n">
-        <v>0.5167</v>
+        <v>0.4726</v>
       </c>
       <c r="J359" t="n">
-        <v>12.9175</v>
+        <v>11.815</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>1.15</v>
       </c>
       <c r="I360" t="n">
-        <v>0.1819</v>
+        <v>0.2051</v>
       </c>
       <c r="J360" t="n">
-        <v>4.5475</v>
+        <v>5.1275</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>1.05</v>
       </c>
       <c r="I361" t="n">
-        <v>0.0214</v>
+        <v>0.0608</v>
       </c>
       <c r="J361" t="n">
-        <v>0.535</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.32</v>
       </c>
       <c r="I362" t="n">
-        <v>0.6411</v>
+        <v>0.7953</v>
       </c>
       <c r="J362" t="n">
-        <v>14.1042</v>
+        <v>17.4966</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.01</v>
       </c>
       <c r="I363" t="n">
-        <v>0.1484</v>
+        <v>0.1186</v>
       </c>
       <c r="J363" t="n">
-        <v>3.2648</v>
+        <v>2.6092</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.4355</v>
       </c>
       <c r="J364" t="n">
-        <v>-14.2714</v>
+        <v>-9.581</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>0.55</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.6617</v>
+        <v>-0.4449</v>
       </c>
       <c r="J365" t="n">
-        <v>-14.5574</v>
+        <v>-9.787800000000001</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.34</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.9176</v>
+        <v>-0.6387</v>
       </c>
       <c r="J366" t="n">
-        <v>-20.1872</v>
+        <v>-14.0514</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.77</v>
       </c>
       <c r="I367" t="n">
-        <v>0.9346</v>
+        <v>0.8593</v>
       </c>
       <c r="J367" t="n">
-        <v>20.5612</v>
+        <v>18.9046</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>1.63</v>
       </c>
       <c r="I368" t="n">
-        <v>0.7862</v>
+        <v>0.72</v>
       </c>
       <c r="J368" t="n">
-        <v>17.2964</v>
+        <v>15.84</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>1.45</v>
       </c>
       <c r="I369" t="n">
-        <v>0.5718</v>
+        <v>0.5374</v>
       </c>
       <c r="J369" t="n">
-        <v>12.5796</v>
+        <v>11.8228</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>1.41</v>
       </c>
       <c r="I370" t="n">
-        <v>0.5097</v>
+        <v>0.4969</v>
       </c>
       <c r="J370" t="n">
-        <v>11.2134</v>
+        <v>10.9318</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.9</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.305</v>
+        <v>-0.1749</v>
       </c>
       <c r="J371" t="n">
-        <v>-6.71</v>
+        <v>-3.8478</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.24</v>
       </c>
       <c r="I372" t="n">
-        <v>0.4489</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="J372" t="n">
-        <v>12.5692</v>
+        <v>14.5796</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>1.15</v>
       </c>
       <c r="I373" t="n">
-        <v>0.3185</v>
+        <v>0.3528</v>
       </c>
       <c r="J373" t="n">
-        <v>8.917999999999999</v>
+        <v>9.878399999999999</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>1.02</v>
       </c>
       <c r="I374" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0707</v>
       </c>
       <c r="J374" t="n">
-        <v>2.2736</v>
+        <v>1.9796</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>0.84</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.3173</v>
+        <v>-0.1953</v>
       </c>
       <c r="J375" t="n">
-        <v>-8.884399999999999</v>
+        <v>-5.4684</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>0.62</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.4081</v>
       </c>
       <c r="J376" t="n">
-        <v>-17.2872</v>
+        <v>-11.4268</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>1.56</v>
       </c>
       <c r="I377" t="n">
-        <v>1.3483</v>
+        <v>1.2222</v>
       </c>
       <c r="J377" t="n">
-        <v>37.7524</v>
+        <v>34.2216</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>1.43</v>
       </c>
       <c r="I378" t="n">
-        <v>1.0871</v>
+        <v>1.0543</v>
       </c>
       <c r="J378" t="n">
-        <v>30.4388</v>
+        <v>29.5204</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>1.09</v>
       </c>
       <c r="I379" t="n">
-        <v>0.2148</v>
+        <v>0.2778</v>
       </c>
       <c r="J379" t="n">
-        <v>6.0144</v>
+        <v>7.7784</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>0.93</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.3851</v>
+        <v>-0.3099</v>
       </c>
       <c r="J380" t="n">
-        <v>-10.7828</v>
+        <v>-8.677199999999999</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>0.91</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.4433</v>
+        <v>-0.3702</v>
       </c>
       <c r="J381" t="n">
-        <v>-12.4124</v>
+        <v>-10.3656</v>
       </c>
     </row>
     <row r="382">
@@ -17629,10 +17629,10 @@
         <v>1.25</v>
       </c>
       <c r="I382" t="n">
-        <v>0.7484</v>
+        <v>0.718</v>
       </c>
       <c r="J382" t="n">
-        <v>18.71</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="383">
@@ -17669,10 +17669,10 @@
         <v>1.18</v>
       </c>
       <c r="I383" t="n">
-        <v>0.5734</v>
+        <v>0.5419</v>
       </c>
       <c r="J383" t="n">
-        <v>14.335</v>
+        <v>13.5475</v>
       </c>
     </row>
     <row r="384">
@@ -17709,10 +17709,10 @@
         <v>1.06</v>
       </c>
       <c r="I384" t="n">
-        <v>0.1955</v>
+        <v>0.214</v>
       </c>
       <c r="J384" t="n">
-        <v>4.8875</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="385">
@@ -17749,10 +17749,10 @@
         <v>0.98</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.167</v>
+        <v>-0.1108</v>
       </c>
       <c r="J385" t="n">
-        <v>-4.175</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="386">
@@ -17789,10 +17789,10 @@
         <v>0.88</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.4864</v>
+        <v>-0.426</v>
       </c>
       <c r="J386" t="n">
-        <v>-12.16</v>
+        <v>-10.65</v>
       </c>
     </row>
     <row r="387">
@@ -17829,10 +17829,10 @@
         <v>1.72</v>
       </c>
       <c r="I387" t="n">
-        <v>0.9903999999999999</v>
+        <v>1.1652</v>
       </c>
       <c r="J387" t="n">
-        <v>24.76</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="388">
@@ -17869,10 +17869,10 @@
         <v>1.14</v>
       </c>
       <c r="I388" t="n">
-        <v>0.2779</v>
+        <v>0.3149</v>
       </c>
       <c r="J388" t="n">
-        <v>6.9475</v>
+        <v>7.8725</v>
       </c>
     </row>
     <row r="389">
@@ -17909,10 +17909,10 @@
         <v>0.91</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.2232</v>
+        <v>-0.1277</v>
       </c>
       <c r="J389" t="n">
-        <v>-5.58</v>
+        <v>-3.1925</v>
       </c>
     </row>
     <row r="390">
@@ -17949,10 +17949,10 @@
         <v>0.88</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.2728</v>
+        <v>-0.1608</v>
       </c>
       <c r="J390" t="n">
-        <v>-6.82</v>
+        <v>-4.02</v>
       </c>
     </row>
     <row r="391">
@@ -17989,10 +17989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.699</v>
+        <v>-0.4696</v>
       </c>
       <c r="J391" t="n">
-        <v>-17.475</v>
+        <v>-11.74</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2410/event_2410_evp_summary.xlsx
+++ b/database/event/2410/event_2410_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.4521</v>
+        <v>7.3508</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9986</v>
+        <v>2.9579</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7262</v>
+        <v>2.722</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4521</v>
+        <v>7.3508</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0755</v>
+        <v>2.7653</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3766</v>
+        <v>4.5855</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3935</v>
+        <v>3.3274</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3935</v>
+        <v>3.3274</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3766</v>
+        <v>4.5855</v>
       </c>
       <c r="K2" t="n">
         <v>161</v>
@@ -529,7 +529,7 @@
         <v>225</v>
       </c>
       <c r="M2" t="n">
-        <v>7.770099999999999</v>
+        <v>7.9129</v>
       </c>
       <c r="N2" t="n">
         <v>386</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8458</v>
+        <v>6.1007</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3523</v>
+        <v>2.4548</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0011</v>
+        <v>2.153</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8458</v>
+        <v>6.1007</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5701</v>
+        <v>1.5614</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2757</v>
+        <v>4.5393</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5701</v>
+        <v>1.5614</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5701</v>
+        <v>1.5614</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2757</v>
+        <v>4.5393</v>
       </c>
       <c r="K3" t="n">
         <v>161</v>
@@ -575,7 +575,7 @@
         <v>225</v>
       </c>
       <c r="M3" t="n">
-        <v>5.8458</v>
+        <v>6.1007</v>
       </c>
       <c r="N3" t="n">
         <v>386</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.508</v>
+        <v>4.5823</v>
       </c>
       <c r="C4" t="n">
-        <v>1.814</v>
+        <v>1.8439</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3971</v>
+        <v>1.4618</v>
       </c>
       <c r="E4" t="n">
-        <v>4.508</v>
+        <v>4.5823</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8101</v>
+        <v>1.356</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6979</v>
+        <v>3.2263</v>
       </c>
       <c r="H4" t="n">
-        <v>7.938</v>
+        <v>1.356</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1274</v>
+        <v>1.356</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6979</v>
+        <v>3.2263</v>
       </c>
       <c r="K4" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="L4" t="n">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="M4" t="n">
-        <v>4.825299999999999</v>
+        <v>4.5823</v>
       </c>
       <c r="N4" t="n">
-        <v>227</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2617</v>
+        <v>4.5023</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7149</v>
+        <v>1.8117</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2859</v>
+        <v>1.4253</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2617</v>
+        <v>4.5023</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3696</v>
+        <v>3.7573</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8921</v>
+        <v>0.745</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3696</v>
+        <v>7.5027</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3696</v>
+        <v>4.0514</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8921</v>
+        <v>0.745</v>
       </c>
       <c r="K5" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L5" t="n">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2617</v>
+        <v>4.7964</v>
       </c>
       <c r="N5" t="n">
-        <v>277</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2488</v>
+        <v>4.164</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7097</v>
+        <v>1.6755</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2801</v>
+        <v>1.2713</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2488</v>
+        <v>4.164</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6807</v>
+        <v>2.4317</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5681</v>
+        <v>1.7323</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6807</v>
+        <v>2.5972</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6807</v>
+        <v>2.5972</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5681</v>
+        <v>1.7323</v>
       </c>
       <c r="K6" t="n">
         <v>142</v>
@@ -713,7 +713,7 @@
         <v>135</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2488</v>
+        <v>4.329499999999999</v>
       </c>
       <c r="N6" t="n">
         <v>277</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6973</v>
+        <v>4.0627</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4877</v>
+        <v>1.6348</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0311</v>
+        <v>1.2252</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6973</v>
+        <v>4.0627</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1867</v>
+        <v>0.1705</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5106</v>
+        <v>3.8922</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1867</v>
+        <v>0.1705</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1867</v>
+        <v>0.1705</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5106</v>
+        <v>3.8922</v>
       </c>
       <c r="K7" t="n">
         <v>161</v>
@@ -759,7 +759,7 @@
         <v>225</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6973</v>
+        <v>4.0627</v>
       </c>
       <c r="N7" t="n">
         <v>386</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3162</v>
+        <v>3.3152</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3344</v>
+        <v>1.334</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8591</v>
+        <v>0.8849</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3162</v>
+        <v>3.3152</v>
       </c>
       <c r="F8" t="n">
-        <v>2.52</v>
+        <v>2.4719</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7962</v>
+        <v>0.8433</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3926</v>
+        <v>3.2615</v>
       </c>
       <c r="I8" t="n">
-        <v>1.764</v>
+        <v>1.7612</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7962</v>
+        <v>0.8433</v>
       </c>
       <c r="K8" t="n">
         <v>162</v>
@@ -805,7 +805,7 @@
         <v>135</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5602</v>
+        <v>2.6045</v>
       </c>
       <c r="N8" t="n">
         <v>297</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1611</v>
+        <v>3.2405</v>
       </c>
       <c r="C9" t="n">
-        <v>1.272</v>
+        <v>1.3039</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7891</v>
+        <v>0.8509</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1611</v>
+        <v>3.2405</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0863</v>
+        <v>2.0215</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0748</v>
+        <v>1.219</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0863</v>
+        <v>2.0215</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0863</v>
+        <v>2.0215</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0748</v>
+        <v>1.219</v>
       </c>
       <c r="K9" t="n">
         <v>142</v>
@@ -851,7 +851,7 @@
         <v>135</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1611</v>
+        <v>3.2405</v>
       </c>
       <c r="N9" t="n">
         <v>277</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0327</v>
+        <v>3.1551</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2203</v>
+        <v>1.2696</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7311</v>
+        <v>0.8121</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0327</v>
+        <v>3.1551</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6404</v>
+        <v>1.5637</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3923</v>
+        <v>1.5914</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6404</v>
+        <v>1.5637</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6404</v>
+        <v>1.5637</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3923</v>
+        <v>1.5914</v>
       </c>
       <c r="K10" t="n">
         <v>142</v>
@@ -897,7 +897,7 @@
         <v>135</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0327</v>
+        <v>3.1551</v>
       </c>
       <c r="N10" t="n">
         <v>277</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8402</v>
+        <v>2.8541</v>
       </c>
       <c r="C11" t="n">
-        <v>1.1429</v>
+        <v>1.1485</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6442</v>
+        <v>0.675</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8402</v>
+        <v>2.8541</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7469</v>
+        <v>2.6632</v>
       </c>
       <c r="G11" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.1909</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1919</v>
+        <v>3.8928</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1796</v>
+        <v>2.1021</v>
       </c>
       <c r="J11" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.1909</v>
       </c>
       <c r="K11" t="n">
         <v>162</v>
@@ -943,7 +943,7 @@
         <v>135</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2729</v>
+        <v>2.293</v>
       </c>
       <c r="N11" t="n">
         <v>297</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7431</v>
+        <v>2.7227</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1038</v>
+        <v>1.0956</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6004</v>
+        <v>0.6152</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7431</v>
+        <v>2.7227</v>
       </c>
       <c r="F12" t="n">
-        <v>1.553</v>
+        <v>1.4817</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1901</v>
+        <v>1.241</v>
       </c>
       <c r="H12" t="n">
-        <v>1.553</v>
+        <v>1.4817</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8075</v>
+        <v>0.8001</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1901</v>
+        <v>1.241</v>
       </c>
       <c r="K12" t="n">
         <v>162</v>
@@ -989,7 +989,7 @@
         <v>135</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9976</v>
+        <v>2.0411</v>
       </c>
       <c r="N12" t="n">
         <v>297</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1665</v>
+        <v>2.1905</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8718</v>
+        <v>0.8814</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3401</v>
+        <v>0.373</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1665</v>
+        <v>2.1905</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7648</v>
+        <v>1.7391</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4017</v>
+        <v>0.4514</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7648</v>
+        <v>1.7391</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9176</v>
+        <v>0.9391</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4017</v>
+        <v>0.4514</v>
       </c>
       <c r="K13" t="n">
         <v>145</v>
@@ -1035,7 +1035,7 @@
         <v>82</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3193</v>
+        <v>1.3905</v>
       </c>
       <c r="N13" t="n">
         <v>227</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1543</v>
+        <v>2.169</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8669</v>
+        <v>0.8728</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3345</v>
+        <v>0.3632</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1543</v>
+        <v>2.169</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1338</v>
+        <v>2.0563</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0205</v>
+        <v>0.1127</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1338</v>
+        <v>2.0563</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1095</v>
+        <v>2.0563</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0205</v>
+        <v>0.1127</v>
       </c>
       <c r="K14" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="L14" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="M14" t="n">
-        <v>1.13</v>
+        <v>2.169</v>
       </c>
       <c r="N14" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1457</v>
+        <v>2.0527</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3307</v>
+        <v>0.3102</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1457</v>
+        <v>2.0527</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0571</v>
+        <v>2.0241</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0886</v>
+        <v>0.0286</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0571</v>
+        <v>2.0241</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0571</v>
+        <v>1.093</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0886</v>
+        <v>0.0286</v>
       </c>
       <c r="K15" t="n">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="L15" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1457</v>
+        <v>1.1216</v>
       </c>
       <c r="N15" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0024</v>
+        <v>1.95</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8057</v>
+        <v>0.7847</v>
       </c>
       <c r="D16" t="n">
-        <v>0.266</v>
+        <v>0.2635</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0024</v>
+        <v>1.95</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6375</v>
+        <v>1.5861</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3649</v>
+        <v>0.3639</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6375</v>
+        <v>1.5861</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6375</v>
+        <v>1.5861</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3649</v>
+        <v>0.3639</v>
       </c>
       <c r="K16" t="n">
         <v>162</v>
@@ -1173,7 +1173,7 @@
         <v>69</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0024</v>
+        <v>1.95</v>
       </c>
       <c r="N16" t="n">
         <v>231</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8669</v>
+        <v>1.8832</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7512</v>
+        <v>0.7578</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2048</v>
+        <v>0.2331</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8669</v>
+        <v>1.8832</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4078</v>
+        <v>0.401</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4591</v>
+        <v>1.4822</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4078</v>
+        <v>0.401</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4078</v>
+        <v>0.401</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4591</v>
+        <v>1.4822</v>
       </c>
       <c r="K17" t="n">
         <v>161</v>
@@ -1219,7 +1219,7 @@
         <v>225</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8669</v>
+        <v>1.8832</v>
       </c>
       <c r="N17" t="n">
         <v>386</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7172</v>
+        <v>1.7429</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.7013</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1372</v>
+        <v>0.1692</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7172</v>
+        <v>1.7429</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5953</v>
+        <v>1.6161</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1219</v>
+        <v>0.1268</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5953</v>
+        <v>1.6161</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5953</v>
+        <v>1.6161</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1219</v>
+        <v>0.1268</v>
       </c>
       <c r="K18" t="n">
         <v>157</v>
@@ -1265,7 +1265,7 @@
         <v>74</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7172</v>
+        <v>1.7429</v>
       </c>
       <c r="N18" t="n">
         <v>231</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.577</v>
+        <v>1.6239</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.6534</v>
       </c>
       <c r="D19" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.115</v>
       </c>
       <c r="E19" t="n">
-        <v>1.577</v>
+        <v>1.6239</v>
       </c>
       <c r="F19" t="n">
-        <v>1.349</v>
+        <v>1.3537</v>
       </c>
       <c r="G19" t="n">
-        <v>0.228</v>
+        <v>0.2702</v>
       </c>
       <c r="H19" t="n">
-        <v>1.349</v>
+        <v>1.3537</v>
       </c>
       <c r="I19" t="n">
-        <v>1.349</v>
+        <v>1.3537</v>
       </c>
       <c r="J19" t="n">
-        <v>0.228</v>
+        <v>0.2702</v>
       </c>
       <c r="K19" t="n">
         <v>162</v>
@@ -1311,7 +1311,7 @@
         <v>69</v>
       </c>
       <c r="M19" t="n">
-        <v>1.577</v>
+        <v>1.6239</v>
       </c>
       <c r="N19" t="n">
         <v>231</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4105</v>
+        <v>1.4991</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5676</v>
+        <v>0.6032</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0012</v>
+        <v>0.0582</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4105</v>
+        <v>1.4991</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4105</v>
+        <v>0.4907</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1.0084</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4105</v>
+        <v>0.4907</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4105</v>
+        <v>0.4907</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.0084</v>
       </c>
       <c r="K20" t="n">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4105</v>
+        <v>1.4991</v>
       </c>
       <c r="N20" t="n">
-        <v>154</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3402</v>
+        <v>1.3637</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5393</v>
+        <v>0.5487</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.033</v>
+        <v>-0.0034</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3402</v>
+        <v>1.3637</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4758</v>
+        <v>1.3637</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8643999999999999</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4758</v>
+        <v>1.3637</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4758</v>
+        <v>1.3637</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8643999999999999</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="L21" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3402</v>
+        <v>1.3637</v>
       </c>
       <c r="N21" t="n">
-        <v>277</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1666</v>
+        <v>1.1577</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4694</v>
+        <v>0.4658</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1114</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1666</v>
+        <v>1.1577</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1666</v>
+        <v>1.1577</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1666</v>
+        <v>1.1577</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1666</v>
+        <v>1.1577</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1666</v>
+        <v>1.1577</v>
       </c>
       <c r="N22" t="n">
         <v>154</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.077</v>
+        <v>1.0933</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4334</v>
+        <v>0.4399</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1518</v>
+        <v>-0.1265</v>
       </c>
       <c r="E23" t="n">
-        <v>1.077</v>
+        <v>1.0933</v>
       </c>
       <c r="F23" t="n">
-        <v>1.077</v>
+        <v>0.6897</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.4036</v>
       </c>
       <c r="H23" t="n">
-        <v>1.077</v>
+        <v>0.6897</v>
       </c>
       <c r="I23" t="n">
-        <v>1.077</v>
+        <v>0.6897</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.4036</v>
       </c>
       <c r="K23" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M23" t="n">
-        <v>1.077</v>
+        <v>1.0933</v>
       </c>
       <c r="N23" t="n">
-        <v>151</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0471</v>
+        <v>0.9918</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4213</v>
+        <v>0.3991</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1653</v>
+        <v>-0.1727</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0471</v>
+        <v>0.9918</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6646</v>
+        <v>0.9918</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3825</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6646</v>
+        <v>0.9918</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6646</v>
+        <v>0.9918</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3825</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="L24" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0471</v>
+        <v>0.9918</v>
       </c>
       <c r="N24" t="n">
-        <v>231</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9411</v>
+        <v>0.9779</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3787</v>
+        <v>0.3935</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2132</v>
+        <v>-0.179</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9411</v>
+        <v>0.9779</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.6838</v>
       </c>
       <c r="G25" t="n">
-        <v>1.5837</v>
+        <v>1.6617</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.6838</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.6838</v>
       </c>
       <c r="J25" t="n">
-        <v>1.5837</v>
+        <v>1.6617</v>
       </c>
       <c r="K25" t="n">
         <v>161</v>
@@ -1587,7 +1587,7 @@
         <v>225</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9411000000000002</v>
+        <v>0.9779</v>
       </c>
       <c r="N25" t="n">
         <v>386</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8276</v>
+        <v>0.8084</v>
       </c>
       <c r="C26" t="n">
-        <v>0.333</v>
+        <v>0.3253</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2644</v>
+        <v>-0.2562</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8276</v>
+        <v>0.8084</v>
       </c>
       <c r="F26" t="n">
-        <v>2.0325</v>
+        <v>1.9173</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.2049</v>
+        <v>-1.1089</v>
       </c>
       <c r="H26" t="n">
-        <v>2.0325</v>
+        <v>1.9173</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0568</v>
+        <v>1.0353</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.2049</v>
+        <v>-1.1089</v>
       </c>
       <c r="K26" t="n">
         <v>162</v>
@@ -1633,7 +1633,7 @@
         <v>135</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1481000000000001</v>
+        <v>-0.07359999999999989</v>
       </c>
       <c r="N26" t="n">
         <v>297</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7837</v>
+        <v>0.7861</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3154</v>
+        <v>0.3163</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2842</v>
+        <v>-0.2664</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7837</v>
+        <v>0.7861</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8602</v>
+        <v>0.8462</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0765</v>
+        <v>-0.0601</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8602</v>
+        <v>0.8462</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8602</v>
+        <v>0.8462</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.0765</v>
+        <v>-0.0601</v>
       </c>
       <c r="K27" t="n">
         <v>157</v>
@@ -1679,7 +1679,7 @@
         <v>74</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7837</v>
+        <v>0.7860999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>231</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2929</v>
+        <v>0.2514</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1179</v>
+        <v>0.1012</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5058</v>
+        <v>-0.5098</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2929</v>
+        <v>0.2514</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2929</v>
+        <v>0.2514</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2929</v>
+        <v>0.2514</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2929</v>
+        <v>0.2514</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2929</v>
+        <v>0.2514</v>
       </c>
       <c r="N28" t="n">
         <v>154</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2587</v>
+        <v>0.2455</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1041</v>
+        <v>0.0988</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5212</v>
+        <v>-0.5124</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2587</v>
+        <v>0.2455</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2858</v>
+        <v>0.2839</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0271</v>
+        <v>-0.0384</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2858</v>
+        <v>0.2839</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2858</v>
+        <v>0.2839</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0271</v>
+        <v>-0.0384</v>
       </c>
       <c r="K29" t="n">
         <v>157</v>
@@ -1771,7 +1771,7 @@
         <v>74</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2587</v>
+        <v>0.2455</v>
       </c>
       <c r="N29" t="n">
         <v>231</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0236</v>
+        <v>-0.0861</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0095</v>
+        <v>-0.0346</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6274</v>
+        <v>-0.6634</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0236</v>
+        <v>-0.0861</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3877</v>
+        <v>-0.0861</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3641</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3877</v>
+        <v>-0.0861</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2016</v>
+        <v>-0.0861</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.3641</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L30" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1625</v>
+        <v>-0.0861</v>
       </c>
       <c r="N30" t="n">
-        <v>227</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0485</v>
+        <v>-0.1167</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0195</v>
+        <v>-0.047</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6599</v>
+        <v>-0.6773</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0485</v>
+        <v>-0.1167</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0485</v>
+        <v>0.2687</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.3854</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0485</v>
+        <v>0.2687</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0485</v>
+        <v>0.1451</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.3854</v>
       </c>
       <c r="K31" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0485</v>
+        <v>-0.2403</v>
       </c>
       <c r="N31" t="n">
-        <v>151</v>
+        <v>227</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2951</v>
+        <v>-0.2527</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1187</v>
+        <v>-0.1017</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7712</v>
+        <v>-0.7392</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2951</v>
+        <v>-0.2527</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6076</v>
+        <v>0.61</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-0.8627</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6076</v>
+        <v>0.61</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3159</v>
+        <v>0.3294</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-0.8627</v>
       </c>
       <c r="K32" t="n">
         <v>162</v>
@@ -1909,7 +1909,7 @@
         <v>135</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5868</v>
+        <v>-0.5333</v>
       </c>
       <c r="N32" t="n">
         <v>297</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3737</v>
+        <v>-0.3918</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1504</v>
+        <v>-0.1577</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8067</v>
+        <v>-0.8026</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3737</v>
+        <v>-0.3918</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3737</v>
+        <v>-0.3918</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3737</v>
+        <v>-0.3918</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3737</v>
+        <v>-0.3918</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3737</v>
+        <v>-0.3918</v>
       </c>
       <c r="N33" t="n">
         <v>151</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4275</v>
+        <v>-0.4349</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.172</v>
+        <v>-0.175</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.831</v>
+        <v>-0.8222</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4275</v>
+        <v>-0.4349</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0721</v>
+        <v>0.079</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.4996</v>
+        <v>-0.5139</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0721</v>
+        <v>0.079</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0721</v>
+        <v>0.079</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.4996</v>
+        <v>-0.5139</v>
       </c>
       <c r="K34" t="n">
         <v>162</v>
@@ -2001,7 +2001,7 @@
         <v>69</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4275</v>
+        <v>-0.4349</v>
       </c>
       <c r="N34" t="n">
         <v>231</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5715</v>
+        <v>-0.592</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.23</v>
+        <v>-0.2382</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.896</v>
+        <v>-0.8937</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5715</v>
+        <v>-0.592</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4285</v>
+        <v>0.408</v>
       </c>
       <c r="G35" t="n">
         <v>-1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4285</v>
+        <v>0.408</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4285</v>
+        <v>0.408</v>
       </c>
       <c r="J35" t="n">
         <v>-1</v>
@@ -2047,7 +2047,7 @@
         <v>69</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5715</v>
+        <v>-0.5920000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>231</v>
@@ -2056,185 +2056,185 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7024</v>
+        <v>-0.6947</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2826</v>
+        <v>-0.2795</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.9404</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7024</v>
+        <v>-0.6947</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.2738</v>
+        <v>-0.6947</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.4286</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2738</v>
+        <v>-0.6947</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2738</v>
+        <v>-0.6947</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.4286</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="L36" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7023999999999999</v>
+        <v>-0.6947</v>
       </c>
       <c r="N36" t="n">
-        <v>231</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7439</v>
+        <v>-0.7322</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2993</v>
+        <v>-0.2946</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9738</v>
+        <v>-0.9575</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7439</v>
+        <v>-0.7322</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7439</v>
+        <v>-1.0552</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.323</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7439</v>
+        <v>-1.0552</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7439</v>
+        <v>-0.5698</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.323</v>
       </c>
       <c r="K37" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7439</v>
+        <v>-0.2468</v>
       </c>
       <c r="N37" t="n">
-        <v>151</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.75</v>
+        <v>-0.7614</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3018</v>
+        <v>-0.3064</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9766</v>
+        <v>-0.9708</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.75</v>
+        <v>-0.7614</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.75</v>
+        <v>-0.2793</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.4821</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.75</v>
+        <v>-0.2793</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.75</v>
+        <v>-0.2793</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.4821</v>
       </c>
       <c r="K38" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.75</v>
+        <v>-0.7614</v>
       </c>
       <c r="N38" t="n">
-        <v>154</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.8022</v>
+        <v>-0.7945</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3228</v>
+        <v>-0.3197</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0002</v>
+        <v>-0.9859</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.8022</v>
+        <v>-0.7945</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0591</v>
+        <v>-0.7945</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2569</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0591</v>
+        <v>-0.7945</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5507</v>
+        <v>-0.7945</v>
       </c>
       <c r="J39" t="n">
-        <v>0.2569</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L39" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.2938</v>
+        <v>-0.7945</v>
       </c>
       <c r="N39" t="n">
-        <v>227</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.9843</v>
+        <v>-1.0081</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3961</v>
+        <v>-0.4056</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0824</v>
+        <v>-1.0831</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.9843</v>
+        <v>-1.0081</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9843</v>
+        <v>-1.0081</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9843</v>
+        <v>-1.0081</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9843</v>
+        <v>-1.0081</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.9843</v>
+        <v>-1.0081</v>
       </c>
       <c r="N40" t="n">
         <v>151</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.0864</v>
+        <v>-1.146</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4372</v>
+        <v>-0.4611</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1285</v>
+        <v>-1.1459</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.0864</v>
+        <v>-1.146</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.0864</v>
+        <v>-1.146</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.0864</v>
+        <v>-1.146</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.0864</v>
+        <v>-1.146</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.0864</v>
+        <v>-1.146</v>
       </c>
       <c r="N41" t="n">
         <v>154</v>
@@ -2429,10 +2429,10 @@
         <v>1.4</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5105</v>
+        <v>0.5195</v>
       </c>
       <c r="J2" t="n">
-        <v>13.7835</v>
+        <v>14.0265</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.38</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4881</v>
+        <v>0.4983</v>
       </c>
       <c r="J3" t="n">
-        <v>13.1787</v>
+        <v>13.4541</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.37</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4769</v>
+        <v>0.4877</v>
       </c>
       <c r="J4" t="n">
-        <v>12.8763</v>
+        <v>13.1679</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0014</v>
+        <v>0.0131</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0378</v>
+        <v>0.3537</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.91</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1453</v>
+        <v>-0.1528</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.9231</v>
+        <v>-4.1256</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.07</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1666</v>
+        <v>0.1695</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4982</v>
+        <v>4.5765</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1125</v>
+        <v>0.1152</v>
       </c>
       <c r="J8" t="n">
-        <v>3.0375</v>
+        <v>3.1104</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.91</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1122</v>
+        <v>-0.1271</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.0294</v>
+        <v>-3.4317</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3221</v>
+        <v>-0.3366</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.6967</v>
+        <v>-9.088200000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.7</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3221</v>
+        <v>-0.3366</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.6967</v>
+        <v>-9.088200000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.82</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1707</v>
+        <v>-0.1952</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.5847</v>
+        <v>-4.0992</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.78</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2137</v>
+        <v>-0.2371</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.4877</v>
+        <v>-4.9791</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.67</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3207</v>
+        <v>-0.3409</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.7347</v>
+        <v>-7.1589</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.64</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3471</v>
+        <v>-0.3666</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.2891</v>
+        <v>-7.6986</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.43</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5432</v>
+        <v>-0.5511</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.4072</v>
+        <v>-11.5731</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.78</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4176</v>
+        <v>1.5415</v>
       </c>
       <c r="J17" t="n">
-        <v>29.7696</v>
+        <v>32.3715</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.66</v>
       </c>
       <c r="I18" t="n">
-        <v>1.28</v>
+        <v>1.3549</v>
       </c>
       <c r="J18" t="n">
-        <v>26.88</v>
+        <v>28.4529</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.56</v>
       </c>
       <c r="I19" t="n">
-        <v>1.164</v>
+        <v>1.1863</v>
       </c>
       <c r="J19" t="n">
-        <v>24.444</v>
+        <v>24.9123</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.26</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6453</v>
+        <v>0.633</v>
       </c>
       <c r="J20" t="n">
-        <v>13.5513</v>
+        <v>13.293</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5008</v>
+        <v>0.5042</v>
       </c>
       <c r="J21" t="n">
-        <v>10.5168</v>
+        <v>10.5882</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.98</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0204</v>
+        <v>-0.0061</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4284</v>
+        <v>-0.1281</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.86</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1421</v>
+        <v>-0.1637</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.9841</v>
+        <v>-3.4377</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.75</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2554</v>
+        <v>-0.2755</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.3634</v>
+        <v>-5.7855</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.63</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.366</v>
+        <v>-0.3828</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.686</v>
+        <v>-8.0388</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.43</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5525</v>
+        <v>-0.5585</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.6025</v>
+        <v>-11.7285</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.56</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1807</v>
+        <v>1.206</v>
       </c>
       <c r="J27" t="n">
-        <v>24.7947</v>
+        <v>25.326</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.44</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0324</v>
+        <v>0.9919</v>
       </c>
       <c r="J28" t="n">
-        <v>21.6804</v>
+        <v>20.8299</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.37</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9124</v>
+        <v>0.8646</v>
       </c>
       <c r="J29" t="n">
-        <v>19.1604</v>
+        <v>18.1566</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.26</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="J30" t="n">
-        <v>14.0679</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.23</v>
       </c>
       <c r="I31" t="n">
-        <v>0.599</v>
+        <v>0.587</v>
       </c>
       <c r="J31" t="n">
-        <v>12.579</v>
+        <v>12.327</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.12</v>
       </c>
       <c r="I32" t="n">
-        <v>0.282</v>
+        <v>0.2876</v>
       </c>
       <c r="J32" t="n">
-        <v>7.05</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.11</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2622</v>
+        <v>0.2687</v>
       </c>
       <c r="J33" t="n">
-        <v>6.555</v>
+        <v>6.7175</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.03</v>
       </c>
       <c r="I34" t="n">
-        <v>0.089</v>
+        <v>0.098</v>
       </c>
       <c r="J34" t="n">
-        <v>2.225</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.09</v>
+        <v>-0.1005</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.25</v>
+        <v>-2.5125</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.89</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1473</v>
+        <v>-0.1598</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.6825</v>
+        <v>-3.995</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.4</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7611</v>
+        <v>0.8373</v>
       </c>
       <c r="J37" t="n">
-        <v>19.0275</v>
+        <v>20.9325</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.33</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6654</v>
+        <v>0.7333</v>
       </c>
       <c r="J38" t="n">
-        <v>16.635</v>
+        <v>18.3325</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.04</v>
       </c>
       <c r="I39" t="n">
-        <v>0.143</v>
+        <v>0.1543</v>
       </c>
       <c r="J39" t="n">
-        <v>3.575</v>
+        <v>3.8575</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.99</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0761</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.9675</v>
+        <v>-1.9025</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.76</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7531</v>
+        <v>-0.6987</v>
       </c>
       <c r="J41" t="n">
-        <v>-18.8275</v>
+        <v>-17.4675</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.46</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4809</v>
+        <v>0.5482</v>
       </c>
       <c r="J42" t="n">
-        <v>13.9461</v>
+        <v>15.8978</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.42</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4546</v>
+        <v>0.5173</v>
       </c>
       <c r="J43" t="n">
-        <v>13.1834</v>
+        <v>15.0017</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.37</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4214</v>
+        <v>0.4779</v>
       </c>
       <c r="J44" t="n">
-        <v>12.2206</v>
+        <v>13.8591</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.06</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0948</v>
+        <v>0.1112</v>
       </c>
       <c r="J45" t="n">
-        <v>2.7492</v>
+        <v>3.2248</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.6</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4455</v>
+        <v>-0.4501</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.9195</v>
+        <v>-13.0529</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.14</v>
       </c>
       <c r="I47" t="n">
-        <v>0.248</v>
+        <v>0.256</v>
       </c>
       <c r="J47" t="n">
-        <v>7.192</v>
+        <v>7.424</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.12</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2181</v>
+        <v>0.227</v>
       </c>
       <c r="J48" t="n">
-        <v>6.3249</v>
+        <v>6.583</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.08</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1558</v>
+        <v>0.1656</v>
       </c>
       <c r="J49" t="n">
-        <v>4.5182</v>
+        <v>4.8024</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.85</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1886</v>
+        <v>-0.202</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.4694</v>
+        <v>-5.858</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.199</v>
+        <v>-0.2124</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.771</v>
+        <v>-6.1596</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3333</v>
+        <v>0.3282</v>
       </c>
       <c r="J52" t="n">
-        <v>9.3324</v>
+        <v>9.1896</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.07</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2287</v>
+        <v>0.2245</v>
       </c>
       <c r="J53" t="n">
-        <v>6.4036</v>
+        <v>6.286</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.91</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1087</v>
+        <v>-0.1245</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.0436</v>
+        <v>-3.486</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.66</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3563</v>
+        <v>-0.3702</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.9764</v>
+        <v>-10.3656</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.52</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4862</v>
+        <v>-0.4939</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.6136</v>
+        <v>-13.8292</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.69</v>
       </c>
       <c r="I57" t="n">
-        <v>1.1071</v>
+        <v>1.2115</v>
       </c>
       <c r="J57" t="n">
-        <v>30.9988</v>
+        <v>33.922</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4951</v>
+        <v>0.5488</v>
       </c>
       <c r="J58" t="n">
-        <v>13.8628</v>
+        <v>15.3664</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.12</v>
       </c>
       <c r="I59" t="n">
-        <v>0.348</v>
+        <v>0.3615</v>
       </c>
       <c r="J59" t="n">
-        <v>9.744</v>
+        <v>10.122</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0481</v>
+        <v>-0.0332</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.3468</v>
+        <v>-0.9296</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.96</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2165</v>
+        <v>-0.205</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.062</v>
+        <v>-5.74</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.88</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.0552</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.9384</v>
+        <v>-1.5351</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.86</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.1152</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.3719</v>
+        <v>-1.9584</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.37</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.5805</v>
+        <v>-0.5883</v>
       </c>
       <c r="J64" t="n">
-        <v>-9.868499999999999</v>
+        <v>-10.0011</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.34</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.6098</v>
+        <v>-0.6151</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.3666</v>
+        <v>-10.4567</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.33</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.6241</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.5315</v>
+        <v>-10.6097</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>2.21</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8728</v>
+        <v>1.0077</v>
       </c>
       <c r="J67" t="n">
-        <v>14.8376</v>
+        <v>17.1309</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.71</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5971</v>
+        <v>0.6917</v>
       </c>
       <c r="J68" t="n">
-        <v>10.1507</v>
+        <v>11.7589</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.4</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4161</v>
+        <v>0.4777</v>
       </c>
       <c r="J69" t="n">
-        <v>7.0737</v>
+        <v>8.120900000000001</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.33</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3708</v>
+        <v>0.4173</v>
       </c>
       <c r="J70" t="n">
-        <v>6.3036</v>
+        <v>7.0941</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.25</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3038</v>
+        <v>0.3291</v>
       </c>
       <c r="J71" t="n">
-        <v>5.1646</v>
+        <v>5.5947</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.41</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7821</v>
+        <v>0.8585</v>
       </c>
       <c r="J72" t="n">
-        <v>22.6809</v>
+        <v>24.8965</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.32</v>
       </c>
       <c r="I73" t="n">
-        <v>0.658</v>
+        <v>0.7238</v>
       </c>
       <c r="J73" t="n">
-        <v>19.082</v>
+        <v>20.9902</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.08</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2708</v>
+        <v>0.2745</v>
       </c>
       <c r="J74" t="n">
-        <v>7.8532</v>
+        <v>7.9605</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.9</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3711</v>
+        <v>-0.3575</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.7619</v>
+        <v>-10.3675</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.9441000000000001</v>
+        <v>-0.8666</v>
       </c>
       <c r="J76" t="n">
-        <v>-27.3789</v>
+        <v>-25.1314</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.11</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2766</v>
+        <v>0.2791</v>
       </c>
       <c r="J77" t="n">
-        <v>8.0214</v>
+        <v>8.0939</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2561</v>
+        <v>0.2595</v>
       </c>
       <c r="J78" t="n">
-        <v>7.4269</v>
+        <v>7.5255</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.1</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2561</v>
+        <v>0.2595</v>
       </c>
       <c r="J79" t="n">
-        <v>7.4269</v>
+        <v>7.5255</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.76</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2743</v>
+        <v>-0.2881</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.9547</v>
+        <v>-8.354900000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.75</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2841</v>
+        <v>-0.2976</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.238899999999999</v>
+        <v>-8.6304</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1028</v>
+        <v>1.2139</v>
       </c>
       <c r="J82" t="n">
-        <v>22.056</v>
+        <v>24.278</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.45</v>
       </c>
       <c r="I83" t="n">
-        <v>0.776</v>
+        <v>0.8637</v>
       </c>
       <c r="J83" t="n">
-        <v>15.52</v>
+        <v>17.274</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.44</v>
       </c>
       <c r="I84" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="J84" t="n">
-        <v>15.272</v>
+        <v>17.006</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.11</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2958</v>
+        <v>0.3119</v>
       </c>
       <c r="J85" t="n">
-        <v>5.916</v>
+        <v>6.238</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.03</v>
       </c>
       <c r="I86" t="n">
-        <v>0.0489</v>
+        <v>0.0793</v>
       </c>
       <c r="J86" t="n">
-        <v>0.978</v>
+        <v>1.586</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.91</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1109</v>
       </c>
       <c r="J87" t="n">
-        <v>-1.826</v>
+        <v>-2.218</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.88</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1262</v>
+        <v>-0.1463</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.524</v>
+        <v>-2.926</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.86</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1484</v>
+        <v>-0.1686</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.968</v>
+        <v>-3.372</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.6</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3988</v>
+        <v>-0.4133</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.976</v>
+        <v>-8.266</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.55</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4455</v>
+        <v>-0.4575</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.91</v>
+        <v>-9.15</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.34</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3937</v>
+        <v>0.4452</v>
       </c>
       <c r="J92" t="n">
-        <v>9.842499999999999</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.28</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3543</v>
+        <v>0.3852</v>
       </c>
       <c r="J93" t="n">
-        <v>8.8575</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.26</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3399</v>
+        <v>0.3636</v>
       </c>
       <c r="J94" t="n">
-        <v>8.4975</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.24</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3217</v>
+        <v>0.3412</v>
       </c>
       <c r="J95" t="n">
-        <v>8.0425</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.24</v>
       </c>
       <c r="I96" t="n">
-        <v>0.3217</v>
+        <v>0.3412</v>
       </c>
       <c r="J96" t="n">
-        <v>8.0425</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.0357</v>
+        <v>0.0265</v>
       </c>
       <c r="J97" t="n">
-        <v>0.8925</v>
+        <v>0.6625</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.89</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1266</v>
+        <v>-0.1439</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.165</v>
+        <v>-3.5975</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.85</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1692</v>
+        <v>-0.1871</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.23</v>
+        <v>-4.6775</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3234</v>
+        <v>-0.3394</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.085000000000001</v>
+        <v>-8.484999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3234</v>
+        <v>-0.3394</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.085000000000001</v>
+        <v>-8.484999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.91</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.0834</v>
+        <v>-0.1048</v>
       </c>
       <c r="J102" t="n">
-        <v>-1.668</v>
+        <v>-2.096</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.78</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.226</v>
+        <v>-0.2467</v>
       </c>
       <c r="J103" t="n">
-        <v>-4.52</v>
+        <v>-4.934</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.73</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2735</v>
+        <v>-0.2933</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.47</v>
+        <v>-5.866</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3097</v>
+        <v>-0.3288</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.194</v>
+        <v>-6.576</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.53</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4592</v>
+        <v>-0.4712</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.183999999999999</v>
+        <v>-9.423999999999999</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.76</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1384</v>
+        <v>1.2536</v>
       </c>
       <c r="J107" t="n">
-        <v>22.768</v>
+        <v>25.072</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.63</v>
       </c>
       <c r="I108" t="n">
-        <v>0.9857</v>
+        <v>1.0913</v>
       </c>
       <c r="J108" t="n">
-        <v>19.714</v>
+        <v>21.826</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.29</v>
       </c>
       <c r="I109" t="n">
-        <v>0.569</v>
+        <v>0.6371</v>
       </c>
       <c r="J109" t="n">
-        <v>11.38</v>
+        <v>12.742</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.23</v>
       </c>
       <c r="I110" t="n">
-        <v>0.4864</v>
+        <v>0.5451</v>
       </c>
       <c r="J110" t="n">
-        <v>9.728</v>
+        <v>10.902</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.1</v>
       </c>
       <c r="I111" t="n">
-        <v>0.2562</v>
+        <v>0.278</v>
       </c>
       <c r="J111" t="n">
-        <v>5.124</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.17</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3705</v>
+        <v>0.3912</v>
       </c>
       <c r="J112" t="n">
-        <v>10.7445</v>
+        <v>11.3448</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1935</v>
+        <v>0.1987</v>
       </c>
       <c r="J113" t="n">
-        <v>5.6115</v>
+        <v>5.7623</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.02</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0737</v>
+        <v>0.0789</v>
       </c>
       <c r="J114" t="n">
-        <v>2.1373</v>
+        <v>2.2881</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.79</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2442</v>
+        <v>-0.2586</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.0818</v>
+        <v>-7.4994</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.75</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2836</v>
+        <v>-0.2972</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.224399999999999</v>
+        <v>-8.6188</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.54</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9374</v>
+        <v>1.0281</v>
       </c>
       <c r="J117" t="n">
-        <v>27.1846</v>
+        <v>29.8149</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.16</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4161</v>
+        <v>0.4568</v>
       </c>
       <c r="J118" t="n">
-        <v>12.0669</v>
+        <v>13.2472</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.12</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3561</v>
+        <v>0.3705</v>
       </c>
       <c r="J119" t="n">
-        <v>10.3269</v>
+        <v>10.7445</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.96</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1999</v>
+        <v>-0.1934</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.7971</v>
+        <v>-5.6086</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.89</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4152</v>
+        <v>-0.3946</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.0408</v>
+        <v>-11.4434</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.2433</v>
+        <v>-0.277</v>
       </c>
       <c r="J122" t="n">
-        <v>-3.8928</v>
+        <v>-4.432</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.66</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.2773</v>
+        <v>-0.3088</v>
       </c>
       <c r="J123" t="n">
-        <v>-4.4368</v>
+        <v>-4.9408</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.43</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.5056</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="J124" t="n">
-        <v>-8.089600000000001</v>
+        <v>-8.347200000000001</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.42</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5151</v>
+        <v>-0.5305</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.2416</v>
+        <v>-8.488</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.2</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7367</v>
+        <v>-0.7318</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.7872</v>
+        <v>-11.7088</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>2.27</v>
       </c>
       <c r="I127" t="n">
-        <v>1.659</v>
+        <v>1.805</v>
       </c>
       <c r="J127" t="n">
-        <v>26.544</v>
+        <v>28.88</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.82</v>
       </c>
       <c r="I128" t="n">
-        <v>1.1715</v>
+        <v>1.2949</v>
       </c>
       <c r="J128" t="n">
-        <v>18.744</v>
+        <v>20.7184</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.4</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6894</v>
+        <v>0.7749</v>
       </c>
       <c r="J129" t="n">
-        <v>11.0304</v>
+        <v>12.3984</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.33</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="J130" t="n">
-        <v>9.588800000000001</v>
+        <v>10.8144</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.18</v>
       </c>
       <c r="I131" t="n">
-        <v>0.3905</v>
+        <v>0.4408</v>
       </c>
       <c r="J131" t="n">
-        <v>6.248</v>
+        <v>7.0528</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.35</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4188</v>
+        <v>0.4723</v>
       </c>
       <c r="J132" t="n">
-        <v>10.8888</v>
+        <v>12.2798</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.26</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3551</v>
+        <v>0.3814</v>
       </c>
       <c r="J133" t="n">
-        <v>9.2326</v>
+        <v>9.916399999999999</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.13</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2041</v>
+        <v>0.2195</v>
       </c>
       <c r="J134" t="n">
-        <v>5.3066</v>
+        <v>5.707</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0974</v>
+        <v>-0.1062</v>
       </c>
       <c r="J135" t="n">
-        <v>-2.5324</v>
+        <v>-2.7612</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.76</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2882</v>
+        <v>-0.299</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.4932</v>
+        <v>-7.774</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.09</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1714</v>
+        <v>0.1812</v>
       </c>
       <c r="J137" t="n">
-        <v>4.4564</v>
+        <v>4.7112</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1392</v>
+        <v>0.1491</v>
       </c>
       <c r="J138" t="n">
-        <v>3.6192</v>
+        <v>3.8766</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0877</v>
+        <v>0.0968</v>
       </c>
       <c r="J139" t="n">
-        <v>2.2802</v>
+        <v>2.5168</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0004</v>
+        <v>-0.0003</v>
       </c>
       <c r="J140" t="n">
-        <v>-0.0104</v>
+        <v>-0.0078</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.84</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1993</v>
+        <v>-0.2126</v>
       </c>
       <c r="J141" t="n">
-        <v>-5.1818</v>
+        <v>-5.5276</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.14</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3243</v>
+        <v>0.3284</v>
       </c>
       <c r="J142" t="n">
-        <v>8.7561</v>
+        <v>8.8668</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.12</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2871</v>
+        <v>0.2913</v>
       </c>
       <c r="J143" t="n">
-        <v>7.7517</v>
+        <v>7.8651</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0757</v>
+        <v>-0.0859</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.0439</v>
+        <v>-2.3193</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.0989</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.3733</v>
+        <v>-2.6703</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.84</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1981</v>
+        <v>-0.2117</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.3487</v>
+        <v>-5.7159</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.27</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5717</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="J147" t="n">
-        <v>15.4359</v>
+        <v>17.0802</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.24</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5295</v>
+        <v>0.5858</v>
       </c>
       <c r="J148" t="n">
-        <v>14.2965</v>
+        <v>15.8166</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.19</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4579</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="J149" t="n">
-        <v>12.3633</v>
+        <v>13.6485</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.16</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4143</v>
+        <v>0.4551</v>
       </c>
       <c r="J150" t="n">
-        <v>11.1861</v>
+        <v>12.2877</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.9</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3912</v>
+        <v>-0.3715</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.5624</v>
+        <v>-10.0305</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.58</v>
       </c>
       <c r="I152" t="n">
-        <v>0.709</v>
+        <v>0.7046</v>
       </c>
       <c r="J152" t="n">
-        <v>20.561</v>
+        <v>20.4334</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.54</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6646</v>
       </c>
       <c r="J153" t="n">
-        <v>19.3082</v>
+        <v>19.2734</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.18</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2572</v>
+        <v>0.275</v>
       </c>
       <c r="J154" t="n">
-        <v>7.4588</v>
+        <v>7.975</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.99</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0404</v>
+        <v>-0.0406</v>
       </c>
       <c r="J155" t="n">
-        <v>-1.1716</v>
+        <v>-1.1774</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.74</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3186</v>
+        <v>-0.3267</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.2394</v>
+        <v>-9.474299999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.12</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3137</v>
+        <v>0.3107</v>
       </c>
       <c r="J157" t="n">
-        <v>9.097300000000001</v>
+        <v>9.010300000000001</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.01</v>
       </c>
       <c r="I158" t="n">
-        <v>0.056</v>
+        <v>0.0565</v>
       </c>
       <c r="J158" t="n">
-        <v>1.624</v>
+        <v>1.6385</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.9</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1253</v>
+        <v>-0.1401</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.6337</v>
+        <v>-4.0629</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.78</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2485</v>
+        <v>-0.2639</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.2065</v>
+        <v>-7.6531</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.76</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2681</v>
+        <v>-0.2832</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.7749</v>
+        <v>-8.2128</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.38</v>
       </c>
       <c r="I162" t="n">
-        <v>0.517</v>
+        <v>0.5204</v>
       </c>
       <c r="J162" t="n">
-        <v>13.959</v>
+        <v>14.0508</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.14</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2196</v>
+        <v>0.2344</v>
       </c>
       <c r="J163" t="n">
-        <v>5.9292</v>
+        <v>6.3288</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.01</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0195</v>
+        <v>0.0268</v>
       </c>
       <c r="J164" t="n">
-        <v>0.5265</v>
+        <v>0.7236</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0781</v>
       </c>
       <c r="J165" t="n">
-        <v>-1.9035</v>
+        <v>-2.1087</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.87</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1749</v>
+        <v>-0.1865</v>
       </c>
       <c r="J166" t="n">
-        <v>-4.7223</v>
+        <v>-5.0355</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.28</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5682</v>
+        <v>0.5553</v>
       </c>
       <c r="J167" t="n">
-        <v>15.3414</v>
+        <v>14.9931</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.09</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2172</v>
+        <v>0.2265</v>
       </c>
       <c r="J168" t="n">
-        <v>5.8644</v>
+        <v>6.1155</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0612</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J169" t="n">
-        <v>1.6524</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.1022</v>
       </c>
       <c r="J170" t="n">
-        <v>-2.4921</v>
+        <v>-2.7594</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.87</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1714</v>
+        <v>-0.1837</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.6278</v>
+        <v>-4.9599</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.9</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0708</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="J172" t="n">
-        <v>-1.3452</v>
+        <v>-1.8544</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.79</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1978</v>
+        <v>-0.2227</v>
       </c>
       <c r="J173" t="n">
-        <v>-3.7582</v>
+        <v>-4.2313</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.77</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2191</v>
+        <v>-0.2434</v>
       </c>
       <c r="J174" t="n">
-        <v>-4.1629</v>
+        <v>-4.6246</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.48</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4927</v>
+        <v>-0.5047</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.3613</v>
+        <v>-9.5893</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.3</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.6619</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.5932</v>
+        <v>-12.5761</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>2.09</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0937</v>
+        <v>1.093</v>
       </c>
       <c r="J177" t="n">
-        <v>20.7803</v>
+        <v>20.767</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.6</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6845</v>
+        <v>0.6894</v>
       </c>
       <c r="J178" t="n">
-        <v>13.0055</v>
+        <v>13.0986</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.47</v>
       </c>
       <c r="I179" t="n">
-        <v>0.555</v>
+        <v>0.5674</v>
       </c>
       <c r="J179" t="n">
-        <v>10.545</v>
+        <v>10.7806</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.3</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3726</v>
+        <v>0.3933</v>
       </c>
       <c r="J180" t="n">
-        <v>7.0794</v>
+        <v>7.4727</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.92</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1556</v>
+        <v>-0.158</v>
       </c>
       <c r="J181" t="n">
-        <v>-2.9564</v>
+        <v>-3.002</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.29</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6273</v>
+        <v>0.6019</v>
       </c>
       <c r="J182" t="n">
-        <v>16.9371</v>
+        <v>16.2513</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.15</v>
       </c>
       <c r="I183" t="n">
-        <v>0.3664</v>
+        <v>0.3619</v>
       </c>
       <c r="J183" t="n">
-        <v>9.892799999999999</v>
+        <v>9.7713</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.85</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1802</v>
+        <v>-0.1955</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.8654</v>
+        <v>-5.2785</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.75</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2804</v>
+        <v>-0.2947</v>
       </c>
       <c r="J185" t="n">
-        <v>-7.5708</v>
+        <v>-7.9569</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.63</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3943</v>
+        <v>-0.405</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.6461</v>
+        <v>-10.935</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.43</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5535</v>
+        <v>0.5583</v>
       </c>
       <c r="J187" t="n">
-        <v>14.9445</v>
+        <v>15.0741</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.22</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3091</v>
+        <v>0.3251</v>
       </c>
       <c r="J188" t="n">
-        <v>8.345700000000001</v>
+        <v>8.777699999999999</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.15</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2232</v>
+        <v>0.2404</v>
       </c>
       <c r="J189" t="n">
-        <v>6.0264</v>
+        <v>6.4908</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.1</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1563</v>
+        <v>0.1733</v>
       </c>
       <c r="J190" t="n">
-        <v>4.2201</v>
+        <v>4.6791</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.92</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.129</v>
+        <v>-0.1371</v>
       </c>
       <c r="J191" t="n">
-        <v>-3.483</v>
+        <v>-3.7017</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>0.93</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0747</v>
+        <v>-0.0921</v>
       </c>
       <c r="J192" t="n">
-        <v>-1.6434</v>
+        <v>-2.0262</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.85</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1654</v>
+        <v>-0.1842</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.6388</v>
+        <v>-4.0524</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.84</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1758</v>
+        <v>-0.1946</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.8676</v>
+        <v>-4.2812</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.72</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.291</v>
+        <v>-0.3087</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.402</v>
+        <v>-6.7914</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.64</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3666</v>
+        <v>-0.3817</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.065200000000001</v>
+        <v>-8.397399999999999</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.67</v>
       </c>
       <c r="I197" t="n">
-        <v>1.3126</v>
+        <v>1.2942</v>
       </c>
       <c r="J197" t="n">
-        <v>28.8772</v>
+        <v>28.4724</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.51</v>
       </c>
       <c r="I198" t="n">
-        <v>1.1202</v>
+        <v>1.0881</v>
       </c>
       <c r="J198" t="n">
-        <v>24.6444</v>
+        <v>23.9382</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.48</v>
       </c>
       <c r="I199" t="n">
-        <v>1.0836</v>
+        <v>1.0473</v>
       </c>
       <c r="J199" t="n">
-        <v>23.8392</v>
+        <v>23.0406</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.2</v>
       </c>
       <c r="I200" t="n">
-        <v>0.526</v>
+        <v>0.5218</v>
       </c>
       <c r="J200" t="n">
-        <v>11.572</v>
+        <v>11.4796</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.0618</v>
       </c>
       <c r="J201" t="n">
-        <v>-1.9558</v>
+        <v>-1.3596</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.6</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2451</v>
+        <v>1.2192</v>
       </c>
       <c r="J202" t="n">
-        <v>26.1471</v>
+        <v>25.6032</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.52</v>
       </c>
       <c r="I203" t="n">
-        <v>1.1464</v>
+        <v>1.1135</v>
       </c>
       <c r="J203" t="n">
-        <v>24.0744</v>
+        <v>23.3835</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.16</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4427</v>
+        <v>0.4431</v>
       </c>
       <c r="J204" t="n">
-        <v>9.2967</v>
+        <v>9.305099999999999</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.1</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2809</v>
+        <v>0.2952</v>
       </c>
       <c r="J205" t="n">
-        <v>5.8989</v>
+        <v>6.1992</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.08</v>
       </c>
       <c r="I206" t="n">
-        <v>0.2229</v>
+        <v>0.2414</v>
       </c>
       <c r="J206" t="n">
-        <v>4.6809</v>
+        <v>5.0694</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.02</v>
       </c>
       <c r="I207" t="n">
-        <v>0.1121</v>
+        <v>0.1068</v>
       </c>
       <c r="J207" t="n">
-        <v>2.3541</v>
+        <v>2.2428</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.92</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.1102</v>
       </c>
       <c r="J208" t="n">
-        <v>-1.9782</v>
+        <v>-2.3142</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.86</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1603</v>
+        <v>-0.1777</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.3663</v>
+        <v>-3.7317</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.76</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.258</v>
+        <v>-0.2753</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.418</v>
+        <v>-5.7813</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.62</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3911</v>
+        <v>-0.4041</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.213100000000001</v>
+        <v>-8.4861</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.53</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9547</v>
+        <v>0.9091</v>
       </c>
       <c r="J212" t="n">
-        <v>26.7316</v>
+        <v>25.4548</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.29</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5684</v>
+        <v>0.5586</v>
       </c>
       <c r="J213" t="n">
-        <v>15.9152</v>
+        <v>15.6408</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.05</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1254</v>
+        <v>0.138</v>
       </c>
       <c r="J214" t="n">
-        <v>3.5112</v>
+        <v>3.864</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2396</v>
+        <v>-0.2508</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.7088</v>
+        <v>-7.0224</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.8</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2496</v>
+        <v>-0.2607</v>
       </c>
       <c r="J216" t="n">
-        <v>-6.9888</v>
+        <v>-7.2996</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.53</v>
       </c>
       <c r="I217" t="n">
-        <v>0.6818</v>
+        <v>0.6752</v>
       </c>
       <c r="J217" t="n">
-        <v>19.0904</v>
+        <v>18.9056</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.2</v>
       </c>
       <c r="I218" t="n">
-        <v>0.2935</v>
+        <v>0.308</v>
       </c>
       <c r="J218" t="n">
-        <v>8.218</v>
+        <v>8.624000000000001</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.04</v>
       </c>
       <c r="I219" t="n">
-        <v>0.0726</v>
+        <v>0.0852</v>
       </c>
       <c r="J219" t="n">
-        <v>2.0328</v>
+        <v>2.3856</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0297</v>
+        <v>-0.0322</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.8316</v>
+        <v>-0.9016</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.73</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3181</v>
+        <v>-0.3281</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.9068</v>
+        <v>-9.1868</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.24</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5162</v>
+        <v>0.5043</v>
       </c>
       <c r="J222" t="n">
-        <v>15.486</v>
+        <v>15.129</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.15</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3491</v>
+        <v>0.3492</v>
       </c>
       <c r="J223" t="n">
-        <v>10.473</v>
+        <v>10.476</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.93</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.1104</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.958</v>
+        <v>-3.312</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.93</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.1104</v>
       </c>
       <c r="J225" t="n">
-        <v>-2.958</v>
+        <v>-3.312</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.68</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3536</v>
+        <v>-0.3647</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.608</v>
+        <v>-10.941</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.36</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4814</v>
+        <v>0.489</v>
       </c>
       <c r="J227" t="n">
-        <v>14.442</v>
+        <v>14.67</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.36</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4814</v>
+        <v>0.489</v>
       </c>
       <c r="J228" t="n">
-        <v>14.442</v>
+        <v>14.67</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.25</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3509</v>
+        <v>0.3645</v>
       </c>
       <c r="J229" t="n">
-        <v>10.527</v>
+        <v>10.935</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.85</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2017</v>
+        <v>-0.2122</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.051</v>
+        <v>-6.366</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2427</v>
+        <v>-0.2532</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.281</v>
+        <v>-7.596</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.63</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7195</v>
+        <v>0.7211</v>
       </c>
       <c r="J232" t="n">
-        <v>15.1095</v>
+        <v>15.1431</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.56</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6489</v>
+        <v>0.6553</v>
       </c>
       <c r="J233" t="n">
-        <v>13.6269</v>
+        <v>13.7613</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.53</v>
       </c>
       <c r="I234" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.6267</v>
       </c>
       <c r="J234" t="n">
-        <v>12.9864</v>
+        <v>13.1607</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.4</v>
       </c>
       <c r="I235" t="n">
-        <v>0.4861</v>
+        <v>0.5012</v>
       </c>
       <c r="J235" t="n">
-        <v>10.2081</v>
+        <v>10.5252</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.06</v>
       </c>
       <c r="I236" t="n">
-        <v>0.0655</v>
+        <v>0.0888</v>
       </c>
       <c r="J236" t="n">
-        <v>1.3755</v>
+        <v>1.8648</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.85</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.148</v>
+        <v>-0.1706</v>
       </c>
       <c r="J237" t="n">
-        <v>-3.108</v>
+        <v>-3.5826</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.8</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2018</v>
+        <v>-0.2237</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.2378</v>
+        <v>-4.6977</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.79</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2122</v>
+        <v>-0.2339</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.4562</v>
+        <v>-4.9119</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.65</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3439</v>
+        <v>-0.3623</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.2219</v>
+        <v>-7.6083</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.45</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.5386</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.1447</v>
+        <v>-11.3106</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.55</v>
       </c>
       <c r="I242" t="n">
-        <v>0.6753</v>
+        <v>0.6737</v>
       </c>
       <c r="J242" t="n">
-        <v>16.8825</v>
+        <v>16.8425</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.35</v>
       </c>
       <c r="I243" t="n">
-        <v>0.4546</v>
+        <v>0.4664</v>
       </c>
       <c r="J243" t="n">
-        <v>11.365</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.18</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2566</v>
+        <v>0.2746</v>
       </c>
       <c r="J244" t="n">
-        <v>6.415</v>
+        <v>6.865</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.04</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0585</v>
+        <v>0.0745</v>
       </c>
       <c r="J245" t="n">
-        <v>1.4625</v>
+        <v>1.8625</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1099</v>
+        <v>-0.116</v>
       </c>
       <c r="J246" t="n">
-        <v>-2.7475</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.03</v>
       </c>
       <c r="I247" t="n">
-        <v>0.1332</v>
+        <v>0.13</v>
       </c>
       <c r="J247" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.91</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1082</v>
+        <v>-0.1241</v>
       </c>
       <c r="J248" t="n">
-        <v>-2.705</v>
+        <v>-3.1025</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.8</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2209</v>
+        <v>-0.2384</v>
       </c>
       <c r="J249" t="n">
-        <v>-5.5225</v>
+        <v>-5.96</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.79</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2308</v>
+        <v>-0.2481</v>
       </c>
       <c r="J250" t="n">
-        <v>-5.77</v>
+        <v>-6.2025</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.73</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2891</v>
+        <v>-0.3053</v>
       </c>
       <c r="J251" t="n">
-        <v>-7.2275</v>
+        <v>-7.6325</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.65</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7723</v>
+        <v>0.7648</v>
       </c>
       <c r="J252" t="n">
-        <v>20.8521</v>
+        <v>20.6496</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.23</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3131</v>
+        <v>0.3309</v>
       </c>
       <c r="J253" t="n">
-        <v>8.4537</v>
+        <v>8.9343</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.22</v>
       </c>
       <c r="I254" t="n">
-        <v>0.3013</v>
+        <v>0.3194</v>
       </c>
       <c r="J254" t="n">
-        <v>8.1351</v>
+        <v>8.623799999999999</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.11</v>
       </c>
       <c r="I255" t="n">
-        <v>0.1598</v>
+        <v>0.1795</v>
       </c>
       <c r="J255" t="n">
-        <v>4.3146</v>
+        <v>4.8465</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.06</v>
       </c>
       <c r="I256" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.1045</v>
       </c>
       <c r="J256" t="n">
-        <v>2.322</v>
+        <v>2.8215</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.8</v>
       </c>
       <c r="I257" t="n">
-        <v>1.2791</v>
+        <v>1.2586</v>
       </c>
       <c r="J257" t="n">
-        <v>34.5357</v>
+        <v>33.9822</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.85</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1809</v>
+        <v>-0.196</v>
       </c>
       <c r="J258" t="n">
-        <v>-4.8843</v>
+        <v>-5.292</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.73</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3005</v>
+        <v>-0.3142</v>
       </c>
       <c r="J259" t="n">
-        <v>-8.1135</v>
+        <v>-8.4834</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.68</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3482</v>
+        <v>-0.3605</v>
       </c>
       <c r="J260" t="n">
-        <v>-9.401400000000001</v>
+        <v>-9.733499999999999</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.64</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3857</v>
+        <v>-0.3966</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.4139</v>
+        <v>-10.7082</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.73</v>
       </c>
       <c r="I262" t="n">
-        <v>0.848</v>
+        <v>0.8355</v>
       </c>
       <c r="J262" t="n">
-        <v>21.2</v>
+        <v>20.8875</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.44</v>
       </c>
       <c r="I263" t="n">
-        <v>0.5431</v>
+        <v>0.5523</v>
       </c>
       <c r="J263" t="n">
-        <v>13.5775</v>
+        <v>13.8075</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.41</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5105</v>
+        <v>0.5216</v>
       </c>
       <c r="J264" t="n">
-        <v>12.7625</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.97</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0781</v>
+        <v>-0.08</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.9525</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.88</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.185</v>
+        <v>-0.1919</v>
       </c>
       <c r="J266" t="n">
-        <v>-4.625</v>
+        <v>-4.7975</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.15</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4059</v>
+        <v>0.391</v>
       </c>
       <c r="J267" t="n">
-        <v>10.1475</v>
+        <v>9.775</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.91</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1067</v>
+        <v>-0.123</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.6675</v>
+        <v>-3.075</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.83</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1903</v>
+        <v>-0.2081</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.7575</v>
+        <v>-5.2025</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.82</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2001</v>
+        <v>-0.2179</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.0025</v>
+        <v>-5.4475</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.5</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5028</v>
+        <v>-0.5098</v>
       </c>
       <c r="J271" t="n">
-        <v>-12.57</v>
+        <v>-12.745</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.24</v>
       </c>
       <c r="I272" t="n">
-        <v>0.3442</v>
+        <v>0.3569</v>
       </c>
       <c r="J272" t="n">
-        <v>9.637600000000001</v>
+        <v>9.9932</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.2</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2942</v>
+        <v>0.3084</v>
       </c>
       <c r="J273" t="n">
-        <v>8.2376</v>
+        <v>8.635199999999999</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.05</v>
       </c>
       <c r="I274" t="n">
-        <v>0.0895</v>
+        <v>0.1027</v>
       </c>
       <c r="J274" t="n">
-        <v>2.506</v>
+        <v>2.8756</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.99</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.0293</v>
+        <v>-0.0319</v>
       </c>
       <c r="J275" t="n">
-        <v>-0.8204</v>
+        <v>-0.8932</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.99</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.0293</v>
+        <v>-0.0319</v>
       </c>
       <c r="J276" t="n">
-        <v>-0.8204</v>
+        <v>-0.8932</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.25</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5387</v>
+        <v>0.5241</v>
       </c>
       <c r="J277" t="n">
-        <v>15.0836</v>
+        <v>14.6748</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.14</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3334</v>
+        <v>0.3336</v>
       </c>
       <c r="J278" t="n">
-        <v>9.3352</v>
+        <v>9.3408</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.02</v>
       </c>
       <c r="I279" t="n">
-        <v>0.0707</v>
+        <v>0.0767</v>
       </c>
       <c r="J279" t="n">
-        <v>1.9796</v>
+        <v>2.1476</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.84</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1953</v>
+        <v>-0.2095</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.4684</v>
+        <v>-5.866</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.62</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4081</v>
+        <v>-0.4174</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.4268</v>
+        <v>-11.6872</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.43</v>
       </c>
       <c r="I282" t="n">
-        <v>0.5785</v>
+        <v>0.5775</v>
       </c>
       <c r="J282" t="n">
-        <v>16.198</v>
+        <v>16.17</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.07</v>
       </c>
       <c r="I283" t="n">
-        <v>0.1231</v>
+        <v>0.1367</v>
       </c>
       <c r="J283" t="n">
-        <v>3.4468</v>
+        <v>3.8276</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.01</v>
       </c>
       <c r="I284" t="n">
-        <v>0.021</v>
+        <v>0.0279</v>
       </c>
       <c r="J284" t="n">
-        <v>0.588</v>
+        <v>0.7812</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.96</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.0693</v>
+        <v>-0.0772</v>
       </c>
       <c r="J285" t="n">
-        <v>-1.9404</v>
+        <v>-2.1616</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.83</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2154</v>
+        <v>-0.2275</v>
       </c>
       <c r="J286" t="n">
-        <v>-6.0312</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.39</v>
       </c>
       <c r="I287" t="n">
-        <v>0.753</v>
+        <v>0.7229</v>
       </c>
       <c r="J287" t="n">
-        <v>21.084</v>
+        <v>20.2412</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.17</v>
       </c>
       <c r="I288" t="n">
-        <v>0.3707</v>
+        <v>0.3729</v>
       </c>
       <c r="J288" t="n">
-        <v>10.3796</v>
+        <v>10.4412</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0927</v>
+        <v>-0.1026</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.5956</v>
+        <v>-2.8728</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.92</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1164</v>
+        <v>-0.1273</v>
       </c>
       <c r="J290" t="n">
-        <v>-3.2592</v>
+        <v>-3.5644</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.8</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.244</v>
+        <v>-0.2563</v>
       </c>
       <c r="J291" t="n">
-        <v>-6.832</v>
+        <v>-7.1764</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.29</v>
       </c>
       <c r="I292" t="n">
-        <v>0.8088</v>
+        <v>0.7369</v>
       </c>
       <c r="J292" t="n">
-        <v>18.6024</v>
+        <v>16.9487</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.59</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.3952</v>
+        <v>-0.4121</v>
       </c>
       <c r="J293" t="n">
-        <v>-9.089600000000001</v>
+        <v>-9.478300000000001</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.57</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.4139</v>
+        <v>-0.4298</v>
       </c>
       <c r="J294" t="n">
-        <v>-9.5197</v>
+        <v>-9.885400000000001</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.48</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4982</v>
+        <v>-0.509</v>
       </c>
       <c r="J295" t="n">
-        <v>-11.4586</v>
+        <v>-11.707</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.47</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.5177</v>
       </c>
       <c r="J296" t="n">
-        <v>-11.6748</v>
+        <v>-11.9071</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.87</v>
       </c>
       <c r="I297" t="n">
-        <v>0.9573</v>
+        <v>0.9419</v>
       </c>
       <c r="J297" t="n">
-        <v>22.0179</v>
+        <v>21.6637</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.52</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6109</v>
+        <v>0.6192</v>
       </c>
       <c r="J298" t="n">
-        <v>14.0507</v>
+        <v>14.2416</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.31</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3903</v>
+        <v>0.409</v>
       </c>
       <c r="J299" t="n">
-        <v>8.976900000000001</v>
+        <v>9.407</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.27</v>
       </c>
       <c r="I300" t="n">
-        <v>0.3445</v>
+        <v>0.3648</v>
       </c>
       <c r="J300" t="n">
-        <v>7.9235</v>
+        <v>8.3904</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>1.09</v>
       </c>
       <c r="I301" t="n">
-        <v>0.1134</v>
+        <v>0.1371</v>
       </c>
       <c r="J301" t="n">
-        <v>2.6082</v>
+        <v>3.1533</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.32</v>
       </c>
       <c r="I302" t="n">
-        <v>0.639</v>
+        <v>0.6194</v>
       </c>
       <c r="J302" t="n">
-        <v>19.17</v>
+        <v>18.582</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.18</v>
       </c>
       <c r="I303" t="n">
-        <v>0.3918</v>
+        <v>0.3921</v>
       </c>
       <c r="J303" t="n">
-        <v>11.754</v>
+        <v>11.763</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.02</v>
       </c>
       <c r="I304" t="n">
-        <v>0.062</v>
+        <v>0.0706</v>
       </c>
       <c r="J304" t="n">
-        <v>1.86</v>
+        <v>2.118</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.83</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2125</v>
+        <v>-0.2252</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.375</v>
+        <v>-6.756</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.82</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2227</v>
+        <v>-0.2354</v>
       </c>
       <c r="J306" t="n">
-        <v>-6.681</v>
+        <v>-7.062</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.2</v>
       </c>
       <c r="I307" t="n">
-        <v>0.3023</v>
+        <v>0.3146</v>
       </c>
       <c r="J307" t="n">
-        <v>9.069000000000001</v>
+        <v>9.438000000000001</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.12</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1959</v>
+        <v>0.21</v>
       </c>
       <c r="J308" t="n">
-        <v>5.877</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.11</v>
       </c>
       <c r="I309" t="n">
-        <v>0.182</v>
+        <v>0.1961</v>
       </c>
       <c r="J309" t="n">
-        <v>5.46</v>
+        <v>5.883</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.93</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1052</v>
+        <v>-0.1155</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.156</v>
+        <v>-3.465</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.88</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.1615</v>
+        <v>-0.1735</v>
       </c>
       <c r="J311" t="n">
-        <v>-4.845</v>
+        <v>-5.205</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.15</v>
       </c>
       <c r="I312" t="n">
-        <v>0.4406</v>
+        <v>0.4166</v>
       </c>
       <c r="J312" t="n">
-        <v>11.015</v>
+        <v>10.415</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.88</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.1302</v>
+        <v>-0.1494</v>
       </c>
       <c r="J313" t="n">
-        <v>-3.255</v>
+        <v>-3.735</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.76</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.251</v>
+        <v>-0.27</v>
       </c>
       <c r="J314" t="n">
-        <v>-6.275</v>
+        <v>-6.75</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.73</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2793</v>
+        <v>-0.2977</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.9825</v>
+        <v>-7.4425</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.38</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6048</v>
+        <v>-0.6063</v>
       </c>
       <c r="J316" t="n">
-        <v>-15.12</v>
+        <v>-15.1575</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.55</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6558</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="J317" t="n">
-        <v>16.395</v>
+        <v>16.47</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.43</v>
       </c>
       <c r="I318" t="n">
-        <v>0.5285</v>
+        <v>0.5392</v>
       </c>
       <c r="J318" t="n">
-        <v>13.2125</v>
+        <v>13.48</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.38</v>
       </c>
       <c r="I319" t="n">
-        <v>0.4745</v>
+        <v>0.488</v>
       </c>
       <c r="J319" t="n">
-        <v>11.8625</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.21</v>
       </c>
       <c r="I320" t="n">
-        <v>0.2831</v>
+        <v>0.303</v>
       </c>
       <c r="J320" t="n">
-        <v>7.0775</v>
+        <v>7.575</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>1</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.0293</v>
+        <v>-0.0227</v>
       </c>
       <c r="J321" t="n">
-        <v>-0.7325</v>
+        <v>-0.5675</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>0.98</v>
       </c>
       <c r="I322" t="n">
-        <v>-0.0207</v>
+        <v>-0.031</v>
       </c>
       <c r="J322" t="n">
-        <v>-0.5589</v>
+        <v>-0.837</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>0.93</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.0868</v>
+        <v>-0.1015</v>
       </c>
       <c r="J323" t="n">
-        <v>-2.3436</v>
+        <v>-2.7405</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.9</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.1212</v>
+        <v>-0.137</v>
       </c>
       <c r="J324" t="n">
-        <v>-3.2724</v>
+        <v>-3.699</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.77</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2521</v>
+        <v>-0.2688</v>
       </c>
       <c r="J325" t="n">
-        <v>-6.8067</v>
+        <v>-7.2576</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.75</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2716</v>
+        <v>-0.2879</v>
       </c>
       <c r="J326" t="n">
-        <v>-7.3332</v>
+        <v>-7.7733</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.66</v>
       </c>
       <c r="I327" t="n">
-        <v>0.781</v>
+        <v>0.7731</v>
       </c>
       <c r="J327" t="n">
-        <v>21.087</v>
+        <v>20.8737</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.46</v>
       </c>
       <c r="I328" t="n">
-        <v>0.5685</v>
+        <v>0.5756</v>
       </c>
       <c r="J328" t="n">
-        <v>15.3495</v>
+        <v>15.5412</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.1</v>
       </c>
       <c r="I329" t="n">
-        <v>0.1448</v>
+        <v>0.1646</v>
       </c>
       <c r="J329" t="n">
-        <v>3.9096</v>
+        <v>4.4442</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.07</v>
       </c>
       <c r="I330" t="n">
-        <v>0.1006</v>
+        <v>0.1197</v>
       </c>
       <c r="J330" t="n">
-        <v>2.7162</v>
+        <v>3.2319</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>1.02</v>
       </c>
       <c r="I331" t="n">
-        <v>0.0162</v>
+        <v>0.0313</v>
       </c>
       <c r="J331" t="n">
-        <v>0.4374</v>
+        <v>0.8451</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.11</v>
       </c>
       <c r="I332" t="n">
-        <v>0.2784</v>
+        <v>0.2805</v>
       </c>
       <c r="J332" t="n">
-        <v>7.2384</v>
+        <v>7.293</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.1</v>
       </c>
       <c r="I333" t="n">
-        <v>0.2579</v>
+        <v>0.2608</v>
       </c>
       <c r="J333" t="n">
-        <v>6.7054</v>
+        <v>6.7808</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.09</v>
       </c>
       <c r="I334" t="n">
-        <v>0.237</v>
+        <v>0.2408</v>
       </c>
       <c r="J334" t="n">
-        <v>6.162</v>
+        <v>6.2608</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.96</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.06</v>
+        <v>-0.0701</v>
       </c>
       <c r="J335" t="n">
-        <v>-1.56</v>
+        <v>-1.8226</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.53</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.4884</v>
+        <v>-0.4943</v>
       </c>
       <c r="J336" t="n">
-        <v>-12.6984</v>
+        <v>-12.8518</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.5</v>
       </c>
       <c r="I337" t="n">
-        <v>0.6161</v>
+        <v>0.6194</v>
       </c>
       <c r="J337" t="n">
-        <v>16.0186</v>
+        <v>16.1044</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.24</v>
       </c>
       <c r="I338" t="n">
-        <v>0.3257</v>
+        <v>0.343</v>
       </c>
       <c r="J338" t="n">
-        <v>8.4682</v>
+        <v>8.917999999999999</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.2</v>
       </c>
       <c r="I339" t="n">
-        <v>0.2787</v>
+        <v>0.2969</v>
       </c>
       <c r="J339" t="n">
-        <v>7.2462</v>
+        <v>7.7194</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.14</v>
       </c>
       <c r="I340" t="n">
-        <v>0.2025</v>
+        <v>0.2217</v>
       </c>
       <c r="J340" t="n">
-        <v>5.265</v>
+        <v>5.7642</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>1.11</v>
       </c>
       <c r="I341" t="n">
-        <v>0.1617</v>
+        <v>0.181</v>
       </c>
       <c r="J341" t="n">
-        <v>4.2042</v>
+        <v>4.706</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.21</v>
       </c>
       <c r="I342" t="n">
-        <v>0.478</v>
+        <v>0.4661</v>
       </c>
       <c r="J342" t="n">
-        <v>13.862</v>
+        <v>13.5169</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.09</v>
       </c>
       <c r="I343" t="n">
-        <v>0.2418</v>
+        <v>0.2443</v>
       </c>
       <c r="J343" t="n">
-        <v>7.0122</v>
+        <v>7.0847</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.05</v>
       </c>
       <c r="I344" t="n">
-        <v>0.1532</v>
+        <v>0.1579</v>
       </c>
       <c r="J344" t="n">
-        <v>4.4428</v>
+        <v>4.5791</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.92</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1058</v>
+        <v>-0.1191</v>
       </c>
       <c r="J345" t="n">
-        <v>-3.0682</v>
+        <v>-3.4539</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.44</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5674</v>
+        <v>-0.569</v>
       </c>
       <c r="J346" t="n">
-        <v>-16.4546</v>
+        <v>-16.501</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.45</v>
       </c>
       <c r="I347" t="n">
-        <v>0.5734</v>
+        <v>0.5774</v>
       </c>
       <c r="J347" t="n">
-        <v>16.6286</v>
+        <v>16.7446</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.29</v>
       </c>
       <c r="I348" t="n">
-        <v>0.3909</v>
+        <v>0.4045</v>
       </c>
       <c r="J348" t="n">
-        <v>11.3361</v>
+        <v>11.7305</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.12</v>
       </c>
       <c r="I349" t="n">
-        <v>0.1826</v>
+        <v>0.2001</v>
       </c>
       <c r="J349" t="n">
-        <v>5.2954</v>
+        <v>5.8029</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>1.01</v>
       </c>
       <c r="I350" t="n">
-        <v>0.0062</v>
+        <v>0.0167</v>
       </c>
       <c r="J350" t="n">
-        <v>0.1798</v>
+        <v>0.4843</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>1.01</v>
       </c>
       <c r="I351" t="n">
-        <v>0.0062</v>
+        <v>0.0167</v>
       </c>
       <c r="J351" t="n">
-        <v>0.1798</v>
+        <v>0.4843</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.04</v>
       </c>
       <c r="I352" t="n">
-        <v>0.1814</v>
+        <v>0.1723</v>
       </c>
       <c r="J352" t="n">
-        <v>4.535</v>
+        <v>4.3075</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>0.92</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.0877</v>
+        <v>-0.1052</v>
       </c>
       <c r="J353" t="n">
-        <v>-2.1925</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>0.84</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.1764</v>
+        <v>-0.195</v>
       </c>
       <c r="J354" t="n">
-        <v>-4.41</v>
+        <v>-4.875</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>0.65</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.3578</v>
+        <v>-0.3731</v>
       </c>
       <c r="J355" t="n">
-        <v>-8.945</v>
+        <v>-9.327500000000001</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>0.55</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.4512</v>
+        <v>-0.462</v>
       </c>
       <c r="J356" t="n">
-        <v>-11.28</v>
+        <v>-11.55</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.69</v>
       </c>
       <c r="I357" t="n">
-        <v>0.7974</v>
+        <v>0.7904</v>
       </c>
       <c r="J357" t="n">
-        <v>19.935</v>
+        <v>19.76</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>1.39</v>
       </c>
       <c r="I358" t="n">
-        <v>0.4834</v>
+        <v>0.4969</v>
       </c>
       <c r="J358" t="n">
-        <v>12.085</v>
+        <v>12.4225</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>1.38</v>
       </c>
       <c r="I359" t="n">
-        <v>0.4726</v>
+        <v>0.4867</v>
       </c>
       <c r="J359" t="n">
-        <v>11.815</v>
+        <v>12.1675</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>1.15</v>
       </c>
       <c r="I360" t="n">
-        <v>0.2051</v>
+        <v>0.2268</v>
       </c>
       <c r="J360" t="n">
-        <v>5.1275</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>1.05</v>
       </c>
       <c r="I361" t="n">
-        <v>0.0608</v>
+        <v>0.081</v>
       </c>
       <c r="J361" t="n">
-        <v>1.52</v>
+        <v>2.025</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.32</v>
       </c>
       <c r="I362" t="n">
-        <v>0.7953</v>
+        <v>0.7353</v>
       </c>
       <c r="J362" t="n">
-        <v>17.4966</v>
+        <v>16.1766</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.01</v>
       </c>
       <c r="I363" t="n">
-        <v>0.1186</v>
+        <v>0.1024</v>
       </c>
       <c r="J363" t="n">
-        <v>2.6092</v>
+        <v>2.2528</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.4355</v>
+        <v>-0.4482</v>
       </c>
       <c r="J364" t="n">
-        <v>-9.581</v>
+        <v>-9.8604</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>0.55</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.4449</v>
+        <v>-0.457</v>
       </c>
       <c r="J365" t="n">
-        <v>-9.787800000000001</v>
+        <v>-10.054</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.34</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.6387</v>
+        <v>-0.638</v>
       </c>
       <c r="J366" t="n">
-        <v>-14.0514</v>
+        <v>-14.036</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.77</v>
       </c>
       <c r="I367" t="n">
-        <v>0.8593</v>
+        <v>0.8502</v>
       </c>
       <c r="J367" t="n">
-        <v>18.9046</v>
+        <v>18.7044</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>1.63</v>
       </c>
       <c r="I368" t="n">
-        <v>0.72</v>
+        <v>0.7215</v>
       </c>
       <c r="J368" t="n">
-        <v>15.84</v>
+        <v>15.873</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>1.45</v>
       </c>
       <c r="I369" t="n">
-        <v>0.5374</v>
+        <v>0.5501</v>
       </c>
       <c r="J369" t="n">
-        <v>11.8228</v>
+        <v>12.1022</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>1.41</v>
       </c>
       <c r="I370" t="n">
-        <v>0.4969</v>
+        <v>0.5114</v>
       </c>
       <c r="J370" t="n">
-        <v>10.9318</v>
+        <v>11.2508</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.9</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.1749</v>
+        <v>-0.1788</v>
       </c>
       <c r="J371" t="n">
-        <v>-3.8478</v>
+        <v>-3.9336</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.24</v>
       </c>
       <c r="I372" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J372" t="n">
-        <v>14.5796</v>
+        <v>14.2128</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>1.15</v>
       </c>
       <c r="I373" t="n">
-        <v>0.3528</v>
+        <v>0.3519</v>
       </c>
       <c r="J373" t="n">
-        <v>9.878399999999999</v>
+        <v>9.853199999999999</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>1.02</v>
       </c>
       <c r="I374" t="n">
-        <v>0.0707</v>
+        <v>0.0767</v>
       </c>
       <c r="J374" t="n">
-        <v>1.9796</v>
+        <v>2.1476</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>0.84</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1953</v>
+        <v>-0.2095</v>
       </c>
       <c r="J375" t="n">
-        <v>-5.4684</v>
+        <v>-5.866</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>0.62</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.4081</v>
+        <v>-0.4174</v>
       </c>
       <c r="J376" t="n">
-        <v>-11.4268</v>
+        <v>-11.6872</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>1.56</v>
       </c>
       <c r="I377" t="n">
-        <v>1.2222</v>
+        <v>1.1898</v>
       </c>
       <c r="J377" t="n">
-        <v>34.2216</v>
+        <v>33.3144</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>1.43</v>
       </c>
       <c r="I378" t="n">
-        <v>1.0543</v>
+        <v>1.0046</v>
       </c>
       <c r="J378" t="n">
-        <v>29.5204</v>
+        <v>28.1288</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>1.09</v>
       </c>
       <c r="I379" t="n">
-        <v>0.2778</v>
+        <v>0.2864</v>
       </c>
       <c r="J379" t="n">
-        <v>7.7784</v>
+        <v>8.0192</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>0.93</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.3099</v>
+        <v>-0.2943</v>
       </c>
       <c r="J380" t="n">
-        <v>-8.677199999999999</v>
+        <v>-8.240399999999999</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>0.91</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3702</v>
+        <v>-0.3503</v>
       </c>
       <c r="J381" t="n">
-        <v>-10.3656</v>
+        <v>-9.808400000000001</v>
       </c>
     </row>
     <row r="382">
@@ -17629,10 +17629,10 @@
         <v>1.25</v>
       </c>
       <c r="I382" t="n">
-        <v>0.718</v>
+        <v>0.6785</v>
       </c>
       <c r="J382" t="n">
-        <v>17.95</v>
+        <v>16.9625</v>
       </c>
     </row>
     <row r="383">
@@ -17669,10 +17669,10 @@
         <v>1.18</v>
       </c>
       <c r="I383" t="n">
-        <v>0.5419</v>
+        <v>0.5221</v>
       </c>
       <c r="J383" t="n">
-        <v>13.5475</v>
+        <v>13.0525</v>
       </c>
     </row>
     <row r="384">
@@ -17709,10 +17709,10 @@
         <v>1.06</v>
       </c>
       <c r="I384" t="n">
-        <v>0.214</v>
+        <v>0.2202</v>
       </c>
       <c r="J384" t="n">
-        <v>5.35</v>
+        <v>5.505</v>
       </c>
     </row>
     <row r="385">
@@ -17749,10 +17749,10 @@
         <v>0.98</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.1108</v>
+        <v>-0.1113</v>
       </c>
       <c r="J385" t="n">
-        <v>-2.77</v>
+        <v>-2.7825</v>
       </c>
     </row>
     <row r="386">
@@ -17789,10 +17789,10 @@
         <v>0.88</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.426</v>
+        <v>-0.4081</v>
       </c>
       <c r="J386" t="n">
-        <v>-10.65</v>
+        <v>-10.2025</v>
       </c>
     </row>
     <row r="387">
@@ -17829,10 +17829,10 @@
         <v>1.72</v>
       </c>
       <c r="I387" t="n">
-        <v>1.1652</v>
+        <v>1.1406</v>
       </c>
       <c r="J387" t="n">
-        <v>29.13</v>
+        <v>28.515</v>
       </c>
     </row>
     <row r="388">
@@ -17869,10 +17869,10 @@
         <v>1.14</v>
       </c>
       <c r="I388" t="n">
-        <v>0.3149</v>
+        <v>0.3202</v>
       </c>
       <c r="J388" t="n">
-        <v>7.8725</v>
+        <v>8.005000000000001</v>
       </c>
     </row>
     <row r="389">
@@ -17909,10 +17909,10 @@
         <v>0.91</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.1277</v>
+        <v>-0.139</v>
       </c>
       <c r="J389" t="n">
-        <v>-3.1925</v>
+        <v>-3.475</v>
       </c>
     </row>
     <row r="390">
@@ -17949,10 +17949,10 @@
         <v>0.88</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.1608</v>
+        <v>-0.173</v>
       </c>
       <c r="J390" t="n">
-        <v>-4.02</v>
+        <v>-4.325</v>
       </c>
     </row>
     <row r="391">
@@ -17989,10 +17989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.4696</v>
+        <v>-0.4751</v>
       </c>
       <c r="J391" t="n">
-        <v>-11.74</v>
+        <v>-11.8775</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2410/event_2410_evp_summary.xlsx
+++ b/database/event/2410/event_2410_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.3508</v>
+        <v>7.1804</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9579</v>
+        <v>2.8893</v>
       </c>
       <c r="D2" t="n">
-        <v>2.722</v>
+        <v>2.6652</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3508</v>
+        <v>7.1804</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7653</v>
+        <v>2.5882</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5855</v>
+        <v>4.5922</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3274</v>
+        <v>2.9813</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3274</v>
+        <v>2.9813</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5855</v>
+        <v>4.5922</v>
       </c>
       <c r="K2" t="n">
         <v>161</v>
@@ -529,7 +529,7 @@
         <v>225</v>
       </c>
       <c r="M2" t="n">
-        <v>7.9129</v>
+        <v>7.5735</v>
       </c>
       <c r="N2" t="n">
         <v>386</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.1007</v>
+        <v>5.7659</v>
       </c>
       <c r="C3" t="n">
-        <v>2.4548</v>
+        <v>2.3201</v>
       </c>
       <c r="D3" t="n">
-        <v>2.153</v>
+        <v>2.0209</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1007</v>
+        <v>5.7659</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5614</v>
+        <v>1.3163</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5393</v>
+        <v>4.4496</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5614</v>
+        <v>1.3163</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5614</v>
+        <v>1.3163</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5393</v>
+        <v>4.4496</v>
       </c>
       <c r="K3" t="n">
         <v>161</v>
@@ -575,7 +575,7 @@
         <v>225</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1007</v>
+        <v>5.7659</v>
       </c>
       <c r="N3" t="n">
         <v>386</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.5823</v>
+        <v>4.4239</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8439</v>
+        <v>1.7801</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4618</v>
+        <v>1.4095</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5823</v>
+        <v>4.4239</v>
       </c>
       <c r="F4" t="n">
-        <v>1.356</v>
+        <v>1.2799</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2263</v>
+        <v>3.144</v>
       </c>
       <c r="H4" t="n">
-        <v>1.356</v>
+        <v>1.2799</v>
       </c>
       <c r="I4" t="n">
-        <v>1.356</v>
+        <v>1.2799</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2263</v>
+        <v>3.144</v>
       </c>
       <c r="K4" t="n">
         <v>142</v>
@@ -621,7 +621,7 @@
         <v>135</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5823</v>
+        <v>4.4239</v>
       </c>
       <c r="N4" t="n">
         <v>277</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5023</v>
+        <v>4.1906</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8117</v>
+        <v>1.6862</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4253</v>
+        <v>1.3032</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5023</v>
+        <v>4.1906</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7573</v>
+        <v>3.5207</v>
       </c>
       <c r="G5" t="n">
-        <v>0.745</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>7.5027</v>
+        <v>6.7754</v>
       </c>
       <c r="I5" t="n">
-        <v>4.0514</v>
+        <v>3.8042</v>
       </c>
       <c r="J5" t="n">
-        <v>0.745</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="K5" t="n">
         <v>145</v>
@@ -667,7 +667,7 @@
         <v>82</v>
       </c>
       <c r="M5" t="n">
-        <v>4.7964</v>
+        <v>4.4741</v>
       </c>
       <c r="N5" t="n">
         <v>227</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.164</v>
+        <v>4.0661</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6755</v>
+        <v>1.6361</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2713</v>
+        <v>1.2465</v>
       </c>
       <c r="E6" t="n">
-        <v>4.164</v>
+        <v>4.0661</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4317</v>
+        <v>0.1336</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7323</v>
+        <v>3.9325</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5972</v>
+        <v>0.1336</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5972</v>
+        <v>0.1336</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7323</v>
+        <v>3.9325</v>
       </c>
       <c r="K6" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="L6" t="n">
-        <v>135</v>
+        <v>225</v>
       </c>
       <c r="M6" t="n">
-        <v>4.329499999999999</v>
+        <v>4.0661</v>
       </c>
       <c r="N6" t="n">
-        <v>277</v>
+        <v>386</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0627</v>
+        <v>4.0278</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6348</v>
+        <v>1.6207</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2252</v>
+        <v>1.2291</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0627</v>
+        <v>4.0278</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1705</v>
+        <v>2.3914</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8922</v>
+        <v>1.6364</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1705</v>
+        <v>2.5303</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1705</v>
+        <v>2.5303</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8922</v>
+        <v>1.6364</v>
       </c>
       <c r="K7" t="n">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="L7" t="n">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="M7" t="n">
-        <v>4.0627</v>
+        <v>4.166700000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>386</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3152</v>
+        <v>3.2112</v>
       </c>
       <c r="C8" t="n">
-        <v>1.334</v>
+        <v>1.2921</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8849</v>
+        <v>0.8571</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3152</v>
+        <v>3.2112</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4719</v>
+        <v>2.4697</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8433</v>
+        <v>0.7415</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2615</v>
+        <v>2.8295</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7612</v>
+        <v>1.5887</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8433</v>
+        <v>0.7415</v>
       </c>
       <c r="K8" t="n">
         <v>162</v>
@@ -805,7 +805,7 @@
         <v>135</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6045</v>
+        <v>2.3302</v>
       </c>
       <c r="N8" t="n">
         <v>297</v>
@@ -814,35 +814,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2405</v>
+        <v>3.1745</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3039</v>
+        <v>1.2774</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8509</v>
+        <v>0.8403</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2405</v>
+        <v>3.1745</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0215</v>
+        <v>1.6116</v>
       </c>
       <c r="G9" t="n">
-        <v>1.219</v>
+        <v>1.5629</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0215</v>
+        <v>1.6116</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0215</v>
+        <v>1.6116</v>
       </c>
       <c r="J9" t="n">
-        <v>1.219</v>
+        <v>1.5629</v>
       </c>
       <c r="K9" t="n">
         <v>142</v>
@@ -851,7 +851,7 @@
         <v>135</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2405</v>
+        <v>3.1745</v>
       </c>
       <c r="N9" t="n">
         <v>277</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1551</v>
+        <v>3.0579</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2696</v>
+        <v>1.2305</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8121</v>
+        <v>0.7872</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1551</v>
+        <v>3.0579</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5637</v>
+        <v>1.9071</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5914</v>
+        <v>1.1509</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5637</v>
+        <v>1.9071</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5637</v>
+        <v>1.9071</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5914</v>
+        <v>1.1509</v>
       </c>
       <c r="K10" t="n">
         <v>142</v>
@@ -897,7 +897,7 @@
         <v>135</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1551</v>
+        <v>3.058</v>
       </c>
       <c r="N10" t="n">
         <v>277</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8541</v>
+        <v>2.8514</v>
       </c>
       <c r="C11" t="n">
-        <v>1.1485</v>
+        <v>1.1474</v>
       </c>
       <c r="D11" t="n">
-        <v>0.675</v>
+        <v>0.6932</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8541</v>
+        <v>2.8514</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6632</v>
+        <v>2.6519</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1909</v>
+        <v>0.1995</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8928</v>
+        <v>3.5138</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1021</v>
+        <v>1.9729</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1909</v>
+        <v>0.1995</v>
       </c>
       <c r="K11" t="n">
         <v>162</v>
@@ -943,7 +943,7 @@
         <v>135</v>
       </c>
       <c r="M11" t="n">
-        <v>2.293</v>
+        <v>2.1724</v>
       </c>
       <c r="N11" t="n">
         <v>297</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7227</v>
+        <v>2.4812</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0956</v>
+        <v>0.9984</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6152</v>
+        <v>0.5245</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7227</v>
+        <v>2.4812</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4817</v>
+        <v>1.2932</v>
       </c>
       <c r="G12" t="n">
-        <v>1.241</v>
+        <v>1.188</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4817</v>
+        <v>1.2932</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8001</v>
+        <v>0.7261</v>
       </c>
       <c r="J12" t="n">
-        <v>1.241</v>
+        <v>1.188</v>
       </c>
       <c r="K12" t="n">
         <v>162</v>
@@ -989,7 +989,7 @@
         <v>135</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0411</v>
+        <v>1.9141</v>
       </c>
       <c r="N12" t="n">
         <v>297</v>
@@ -998,47 +998,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1905</v>
+        <v>1.823</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8814</v>
+        <v>0.7336</v>
       </c>
       <c r="D13" t="n">
-        <v>0.373</v>
+        <v>0.2247</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1905</v>
+        <v>1.823</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7391</v>
+        <v>0.2956</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4514</v>
+        <v>1.5274</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7391</v>
+        <v>0.2956</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9391</v>
+        <v>0.2956</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4514</v>
+        <v>1.5274</v>
       </c>
       <c r="K13" t="n">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="L13" t="n">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3905</v>
+        <v>1.823</v>
       </c>
       <c r="N13" t="n">
-        <v>227</v>
+        <v>386</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.169</v>
+        <v>1.7881</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8728</v>
+        <v>0.7195</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3632</v>
+        <v>0.2088</v>
       </c>
       <c r="E14" t="n">
-        <v>2.169</v>
+        <v>1.7881</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0563</v>
+        <v>1.7707</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1127</v>
+        <v>0.0174</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0563</v>
+        <v>1.7707</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0563</v>
+        <v>1.7707</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1127</v>
+        <v>0.0174</v>
       </c>
       <c r="K14" t="n">
         <v>157</v>
@@ -1081,7 +1081,7 @@
         <v>74</v>
       </c>
       <c r="M14" t="n">
-        <v>2.169</v>
+        <v>1.7881</v>
       </c>
       <c r="N14" t="n">
         <v>231</v>
@@ -1090,139 +1090,139 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0527</v>
+        <v>1.6783</v>
       </c>
       <c r="C15" t="n">
-        <v>0.826</v>
+        <v>0.6753</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3102</v>
+        <v>0.1588</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0527</v>
+        <v>1.6783</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0241</v>
+        <v>1.4157</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0286</v>
+        <v>0.2626</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0241</v>
+        <v>1.4157</v>
       </c>
       <c r="I15" t="n">
-        <v>1.093</v>
+        <v>1.4157</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0286</v>
+        <v>0.2626</v>
       </c>
       <c r="K15" t="n">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="L15" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1216</v>
+        <v>1.6783</v>
       </c>
       <c r="N15" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.95</v>
+        <v>1.6712</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7847</v>
+        <v>0.6725</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2635</v>
+        <v>0.1555</v>
       </c>
       <c r="E16" t="n">
-        <v>1.95</v>
+        <v>1.6712</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5861</v>
+        <v>1.7052</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3639</v>
+        <v>-0.034</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5861</v>
+        <v>1.7052</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5861</v>
+        <v>0.9574</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3639</v>
+        <v>-0.034</v>
       </c>
       <c r="K16" t="n">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="L16" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="M16" t="n">
-        <v>1.95</v>
+        <v>0.9234</v>
       </c>
       <c r="N16" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8832</v>
+        <v>1.6004</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7578</v>
+        <v>0.644</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2331</v>
+        <v>0.1233</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8832</v>
+        <v>1.6004</v>
       </c>
       <c r="F17" t="n">
-        <v>0.401</v>
+        <v>1.2125</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4822</v>
+        <v>0.3879</v>
       </c>
       <c r="H17" t="n">
-        <v>0.401</v>
+        <v>1.2125</v>
       </c>
       <c r="I17" t="n">
-        <v>0.401</v>
+        <v>0.6808</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4822</v>
+        <v>0.3879</v>
       </c>
       <c r="K17" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="L17" t="n">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8832</v>
+        <v>1.0687</v>
       </c>
       <c r="N17" t="n">
-        <v>386</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7429</v>
+        <v>1.452</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7013</v>
+        <v>0.5843</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1692</v>
+        <v>0.0557</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7429</v>
+        <v>1.452</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6161</v>
+        <v>1.3884</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1268</v>
+        <v>0.0636</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6161</v>
+        <v>1.3884</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6161</v>
+        <v>1.3884</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1268</v>
+        <v>0.0636</v>
       </c>
       <c r="K18" t="n">
         <v>157</v>
@@ -1265,7 +1265,7 @@
         <v>74</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7429</v>
+        <v>1.452</v>
       </c>
       <c r="N18" t="n">
         <v>231</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6239</v>
+        <v>1.3155</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6534</v>
+        <v>0.5293</v>
       </c>
       <c r="D19" t="n">
-        <v>0.115</v>
+        <v>-0.0065</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6239</v>
+        <v>1.3155</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3537</v>
+        <v>0.3749</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2702</v>
+        <v>0.9406</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3537</v>
+        <v>0.3749</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3537</v>
+        <v>0.3749</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2702</v>
+        <v>0.9406</v>
       </c>
       <c r="K19" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="L19" t="n">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6239</v>
+        <v>1.3155</v>
       </c>
       <c r="N19" t="n">
-        <v>231</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4991</v>
+        <v>1.2622</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6032</v>
+        <v>0.5079</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0582</v>
+        <v>-0.0308</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4991</v>
+        <v>1.2622</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4907</v>
+        <v>1.1042</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0084</v>
+        <v>0.158</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4907</v>
+        <v>1.1042</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4907</v>
+        <v>1.1042</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0084</v>
+        <v>0.158</v>
       </c>
       <c r="K20" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="L20" t="n">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4991</v>
+        <v>1.2622</v>
       </c>
       <c r="N20" t="n">
-        <v>277</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3637</v>
+        <v>1.1756</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5487</v>
+        <v>0.473</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0034</v>
+        <v>-0.0702</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3637</v>
+        <v>1.1756</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3637</v>
+        <v>1.1756</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3637</v>
+        <v>1.1756</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3637</v>
+        <v>1.1756</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3637</v>
+        <v>1.1756</v>
       </c>
       <c r="N21" t="n">
         <v>154</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1577</v>
+        <v>1.0021</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4658</v>
+        <v>0.4032</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.1493</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1577</v>
+        <v>1.0021</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1577</v>
+        <v>-0.6622</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1.6643</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1577</v>
+        <v>-0.6622</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1577</v>
+        <v>-0.6622</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1.6643</v>
       </c>
       <c r="K22" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1577</v>
+        <v>1.0021</v>
       </c>
       <c r="N22" t="n">
-        <v>154</v>
+        <v>386</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0933</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4399</v>
+        <v>0.3693</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1265</v>
+        <v>-0.1877</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0933</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6897</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4036</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6897</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6897</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4036</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="L23" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0933</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>231</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9918</v>
+        <v>0.871</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3991</v>
+        <v>0.3505</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1727</v>
+        <v>-0.209</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9918</v>
+        <v>0.871</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9918</v>
+        <v>0.871</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9918</v>
+        <v>0.871</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9918</v>
+        <v>0.871</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9918</v>
+        <v>0.871</v>
       </c>
       <c r="N24" t="n">
         <v>151</v>
@@ -1550,47 +1550,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9779</v>
+        <v>0.8</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3935</v>
+        <v>0.3219</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.179</v>
+        <v>-0.2413</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9779</v>
+        <v>0.8</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6838</v>
+        <v>0.4946</v>
       </c>
       <c r="G25" t="n">
-        <v>1.6617</v>
+        <v>0.3055</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6838</v>
+        <v>0.4946</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6838</v>
+        <v>0.4946</v>
       </c>
       <c r="J25" t="n">
-        <v>1.6617</v>
+        <v>0.3055</v>
       </c>
       <c r="K25" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="L25" t="n">
-        <v>225</v>
+        <v>74</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9779</v>
+        <v>0.8001</v>
       </c>
       <c r="N25" t="n">
-        <v>386</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26">
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8084</v>
+        <v>0.74</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3253</v>
+        <v>0.2978</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2562</v>
+        <v>-0.2687</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8084</v>
+        <v>0.74</v>
       </c>
       <c r="F26" t="n">
-        <v>1.9173</v>
+        <v>1.8318</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.1089</v>
+        <v>-1.0918</v>
       </c>
       <c r="H26" t="n">
-        <v>1.9173</v>
+        <v>1.8318</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0353</v>
+        <v>1.0285</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.1089</v>
+        <v>-1.0918</v>
       </c>
       <c r="K26" t="n">
         <v>162</v>
@@ -1633,7 +1633,7 @@
         <v>135</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.07359999999999989</v>
+        <v>-0.06330000000000013</v>
       </c>
       <c r="N26" t="n">
         <v>297</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7861</v>
+        <v>0.6389</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3163</v>
+        <v>0.2571</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2664</v>
+        <v>-0.3147</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7861</v>
+        <v>0.6389</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8462</v>
+        <v>0.7234</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0601</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8462</v>
+        <v>0.7234</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8462</v>
+        <v>0.7234</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.0601</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>157</v>
@@ -1679,7 +1679,7 @@
         <v>74</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7860999999999999</v>
+        <v>0.6389</v>
       </c>
       <c r="N27" t="n">
         <v>231</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2514</v>
+        <v>0.1816</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1012</v>
+        <v>0.0731</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5098</v>
+        <v>-0.5231</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2514</v>
+        <v>0.1816</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2514</v>
+        <v>0.1816</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2514</v>
+        <v>0.1816</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2514</v>
+        <v>0.1816</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2514</v>
+        <v>0.1816</v>
       </c>
       <c r="N28" t="n">
         <v>154</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2455</v>
+        <v>0.1107</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0988</v>
+        <v>0.0445</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5124</v>
+        <v>-0.5554</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2455</v>
+        <v>0.1107</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2839</v>
+        <v>0.1727</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0384</v>
+        <v>-0.062</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2839</v>
+        <v>0.1727</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2839</v>
+        <v>0.1727</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0384</v>
+        <v>-0.062</v>
       </c>
       <c r="K29" t="n">
         <v>157</v>
@@ -1771,7 +1771,7 @@
         <v>74</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2455</v>
+        <v>0.1107</v>
       </c>
       <c r="N29" t="n">
         <v>231</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0861</v>
+        <v>-0.1602</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0346</v>
+        <v>-0.0645</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6634</v>
+        <v>-0.6788</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0861</v>
+        <v>-0.1602</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0861</v>
+        <v>-0.1602</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0861</v>
+        <v>-0.1602</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0861</v>
+        <v>-0.1602</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0861</v>
+        <v>-0.1602</v>
       </c>
       <c r="N30" t="n">
         <v>151</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1167</v>
+        <v>-0.1864</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.047</v>
+        <v>-0.075</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6773</v>
+        <v>-0.6907</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1167</v>
+        <v>-0.1864</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2687</v>
+        <v>0.2187</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.3854</v>
+        <v>-0.4051</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2687</v>
+        <v>0.2187</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1451</v>
+        <v>0.1228</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.3854</v>
+        <v>-0.4051</v>
       </c>
       <c r="K31" t="n">
         <v>145</v>
@@ -1863,7 +1863,7 @@
         <v>82</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2403</v>
+        <v>-0.2823</v>
       </c>
       <c r="N31" t="n">
         <v>227</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2527</v>
+        <v>-0.4214</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1017</v>
+        <v>-0.1696</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7392</v>
+        <v>-0.7978</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2527</v>
+        <v>-0.4214</v>
       </c>
       <c r="F32" t="n">
-        <v>0.61</v>
+        <v>0.4584</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.8627</v>
+        <v>-0.8798</v>
       </c>
       <c r="H32" t="n">
-        <v>0.61</v>
+        <v>0.4584</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3294</v>
+        <v>0.2574</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8627</v>
+        <v>-0.8798</v>
       </c>
       <c r="K32" t="n">
         <v>162</v>
@@ -1909,7 +1909,7 @@
         <v>135</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5333</v>
+        <v>-0.6224000000000001</v>
       </c>
       <c r="N32" t="n">
         <v>297</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3918</v>
+        <v>-0.4614</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1577</v>
+        <v>-0.1857</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8026</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3918</v>
+        <v>-0.4614</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3918</v>
+        <v>-0.4614</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3918</v>
+        <v>-0.4614</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3918</v>
+        <v>-0.4614</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3918</v>
+        <v>-0.4614</v>
       </c>
       <c r="N33" t="n">
         <v>151</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4349</v>
+        <v>-0.5713</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.175</v>
+        <v>-0.2299</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8222</v>
+        <v>-0.866</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4349</v>
+        <v>-0.5713</v>
       </c>
       <c r="F34" t="n">
-        <v>0.079</v>
+        <v>-0.0302</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.5139</v>
+        <v>-0.5411</v>
       </c>
       <c r="H34" t="n">
-        <v>0.079</v>
+        <v>-0.0302</v>
       </c>
       <c r="I34" t="n">
-        <v>0.079</v>
+        <v>-0.0302</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.5139</v>
+        <v>-0.5411</v>
       </c>
       <c r="K34" t="n">
         <v>162</v>
@@ -2001,7 +2001,7 @@
         <v>69</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4349</v>
+        <v>-0.5713</v>
       </c>
       <c r="N34" t="n">
         <v>231</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.592</v>
+        <v>-0.6899</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2382</v>
+        <v>-0.2776</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8937</v>
+        <v>-0.9201</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.592</v>
+        <v>-0.6899</v>
       </c>
       <c r="F35" t="n">
-        <v>0.408</v>
+        <v>0.3101</v>
       </c>
       <c r="G35" t="n">
         <v>-1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.408</v>
+        <v>0.3101</v>
       </c>
       <c r="I35" t="n">
-        <v>0.408</v>
+        <v>0.3101</v>
       </c>
       <c r="J35" t="n">
         <v>-1</v>
@@ -2047,7 +2047,7 @@
         <v>69</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5920000000000001</v>
+        <v>-0.6899</v>
       </c>
       <c r="N35" t="n">
         <v>231</v>
@@ -2056,185 +2056,185 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6947</v>
+        <v>-0.7174</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2795</v>
+        <v>-0.2887</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9404</v>
+        <v>-0.9326</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6947</v>
+        <v>-0.7174</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6947</v>
+        <v>-0.2863</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.4311</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6947</v>
+        <v>-0.2863</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6947</v>
+        <v>-0.2863</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.4311</v>
       </c>
       <c r="K36" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6947</v>
+        <v>-0.7174</v>
       </c>
       <c r="N36" t="n">
-        <v>154</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7322</v>
+        <v>-0.7861</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2946</v>
+        <v>-0.3163</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9575</v>
+        <v>-0.9639</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7322</v>
+        <v>-0.7861</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0552</v>
+        <v>-0.7861</v>
       </c>
       <c r="G37" t="n">
-        <v>0.323</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0552</v>
+        <v>-0.7861</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.5698</v>
+        <v>-0.7861</v>
       </c>
       <c r="J37" t="n">
-        <v>0.323</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L37" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.2468</v>
+        <v>-0.7861</v>
       </c>
       <c r="N37" t="n">
-        <v>227</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.7614</v>
+        <v>-0.8424</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3064</v>
+        <v>-0.339</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9708</v>
+        <v>-0.9895</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.7614</v>
+        <v>-0.8424</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.2793</v>
+        <v>-1.0823</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.4821</v>
+        <v>0.2399</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.2793</v>
+        <v>-1.0823</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2793</v>
+        <v>-0.6077</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.4821</v>
+        <v>0.2399</v>
       </c>
       <c r="K38" t="n">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="L38" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7614</v>
+        <v>-0.3678</v>
       </c>
       <c r="N38" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.7945</v>
+        <v>-0.8647</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3197</v>
+        <v>-0.3479</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9859</v>
+        <v>-0.9997</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.7945</v>
+        <v>-0.8647</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.7945</v>
+        <v>-0.8647</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.7945</v>
+        <v>-0.8647</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7945</v>
+        <v>-0.8647</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.7945</v>
+        <v>-0.8647</v>
       </c>
       <c r="N39" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.0081</v>
+        <v>-1.0698</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4056</v>
+        <v>-0.4305</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0831</v>
+        <v>-1.0931</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.0081</v>
+        <v>-1.0698</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.0081</v>
+        <v>-1.0698</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.0081</v>
+        <v>-1.0698</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.0081</v>
+        <v>-1.0698</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.0081</v>
+        <v>-1.0698</v>
       </c>
       <c r="N40" t="n">
         <v>151</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.146</v>
+        <v>-1.0742</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4611</v>
+        <v>-0.4322</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1459</v>
+        <v>-1.0951</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.146</v>
+        <v>-1.0742</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.146</v>
+        <v>-1.0742</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.146</v>
+        <v>-1.0742</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.146</v>
+        <v>-1.0742</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.146</v>
+        <v>-1.0742</v>
       </c>
       <c r="N41" t="n">
         <v>154</v>
@@ -2429,10 +2429,10 @@
         <v>1.4</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5195</v>
+        <v>0.4508</v>
       </c>
       <c r="J2" t="n">
-        <v>14.0265</v>
+        <v>12.1716</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.38</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4983</v>
+        <v>0.4306</v>
       </c>
       <c r="J3" t="n">
-        <v>13.4541</v>
+        <v>11.6262</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.37</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4877</v>
+        <v>0.4205</v>
       </c>
       <c r="J4" t="n">
-        <v>13.1679</v>
+        <v>11.3535</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0131</v>
+        <v>0.0067</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3537</v>
+        <v>0.1809</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.91</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1528</v>
+        <v>-0.1337</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.1256</v>
+        <v>-3.6099</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.07</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1695</v>
+        <v>0.1529</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5765</v>
+        <v>4.1283</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1152</v>
+        <v>0.0993</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1104</v>
+        <v>2.6811</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.91</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1271</v>
+        <v>-0.1108</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.4317</v>
+        <v>-2.9916</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3366</v>
+        <v>-0.3205</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.088200000000001</v>
+        <v>-8.653499999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.7</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3366</v>
+        <v>-0.3205</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.088200000000001</v>
+        <v>-8.653499999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.82</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1952</v>
+        <v>-0.1796</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.0992</v>
+        <v>-3.7716</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.78</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2371</v>
+        <v>-0.2228</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.9791</v>
+        <v>-4.6788</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.67</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3409</v>
+        <v>-0.3288</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.1589</v>
+        <v>-6.9048</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.64</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3666</v>
+        <v>-0.355</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.6986</v>
+        <v>-7.455</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.43</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5511</v>
+        <v>-0.5558</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.5731</v>
+        <v>-11.6718</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.78</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5415</v>
+        <v>1.5721</v>
       </c>
       <c r="J17" t="n">
-        <v>32.3715</v>
+        <v>33.0141</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.66</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3549</v>
+        <v>1.3919</v>
       </c>
       <c r="J18" t="n">
-        <v>28.4529</v>
+        <v>29.2299</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.56</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1863</v>
+        <v>1.2071</v>
       </c>
       <c r="J19" t="n">
-        <v>24.9123</v>
+        <v>25.3491</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.26</v>
       </c>
       <c r="I20" t="n">
-        <v>0.633</v>
+        <v>0.6105</v>
       </c>
       <c r="J20" t="n">
-        <v>13.293</v>
+        <v>12.8205</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5042</v>
+        <v>0.4754</v>
       </c>
       <c r="J21" t="n">
-        <v>10.5882</v>
+        <v>9.9834</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.98</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0061</v>
+        <v>0.0058</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1281</v>
+        <v>0.1218</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.86</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1637</v>
+        <v>-0.1481</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.4377</v>
+        <v>-3.1101</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.75</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2755</v>
+        <v>-0.2603</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.7855</v>
+        <v>-5.4663</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.63</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3828</v>
+        <v>-0.3705</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.0388</v>
+        <v>-7.7805</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.43</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5585</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.7285</v>
+        <v>-11.865</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.56</v>
       </c>
       <c r="I27" t="n">
-        <v>1.206</v>
+        <v>1.224</v>
       </c>
       <c r="J27" t="n">
-        <v>25.326</v>
+        <v>25.704</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.44</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9919</v>
+        <v>0.989</v>
       </c>
       <c r="J28" t="n">
-        <v>20.8299</v>
+        <v>20.769</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.37</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8646</v>
+        <v>0.8525</v>
       </c>
       <c r="J29" t="n">
-        <v>18.1566</v>
+        <v>17.9025</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.26</v>
       </c>
       <c r="I30" t="n">
-        <v>0.65</v>
+        <v>0.6263</v>
       </c>
       <c r="J30" t="n">
-        <v>13.65</v>
+        <v>13.1523</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.23</v>
       </c>
       <c r="I31" t="n">
-        <v>0.587</v>
+        <v>0.5606</v>
       </c>
       <c r="J31" t="n">
-        <v>12.327</v>
+        <v>11.7726</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.12</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2876</v>
+        <v>0.2383</v>
       </c>
       <c r="J32" t="n">
-        <v>7.19</v>
+        <v>5.9575</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.11</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2687</v>
+        <v>0.221</v>
       </c>
       <c r="J33" t="n">
-        <v>6.7175</v>
+        <v>5.525</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.03</v>
       </c>
       <c r="I34" t="n">
-        <v>0.098</v>
+        <v>0.0728</v>
       </c>
       <c r="J34" t="n">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1005</v>
+        <v>-0.0833</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.5125</v>
+        <v>-2.0825</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.89</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1598</v>
+        <v>-0.1396</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.995</v>
+        <v>-3.49</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.4</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8373</v>
+        <v>0.8215</v>
       </c>
       <c r="J37" t="n">
-        <v>20.9325</v>
+        <v>20.5375</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.33</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7333</v>
+        <v>0.7174</v>
       </c>
       <c r="J38" t="n">
-        <v>18.3325</v>
+        <v>17.935</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.04</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1543</v>
+        <v>0.1284</v>
       </c>
       <c r="J39" t="n">
-        <v>3.8575</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.99</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.0761</v>
+        <v>-0.0558</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.9025</v>
+        <v>-1.395</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.76</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6987</v>
+        <v>-0.6674</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.4675</v>
+        <v>-16.685</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.46</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5482</v>
+        <v>0.5118</v>
       </c>
       <c r="J42" t="n">
-        <v>15.8978</v>
+        <v>14.8422</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.42</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5173</v>
+        <v>0.4748</v>
       </c>
       <c r="J43" t="n">
-        <v>15.0017</v>
+        <v>13.7692</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.37</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4779</v>
+        <v>0.424</v>
       </c>
       <c r="J44" t="n">
-        <v>13.8591</v>
+        <v>12.296</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.06</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1112</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>3.2248</v>
+        <v>2.4389</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.6</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4501</v>
+        <v>-0.4477</v>
       </c>
       <c r="J46" t="n">
-        <v>-13.0529</v>
+        <v>-12.9833</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.14</v>
       </c>
       <c r="I47" t="n">
-        <v>0.256</v>
+        <v>0.2413</v>
       </c>
       <c r="J47" t="n">
-        <v>7.424</v>
+        <v>6.9977</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.12</v>
       </c>
       <c r="I48" t="n">
-        <v>0.227</v>
+        <v>0.2111</v>
       </c>
       <c r="J48" t="n">
-        <v>6.583</v>
+        <v>6.1219</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.08</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1656</v>
+        <v>0.1488</v>
       </c>
       <c r="J49" t="n">
-        <v>4.8024</v>
+        <v>4.3152</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.85</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.202</v>
+        <v>-0.1814</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.858</v>
+        <v>-5.2606</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2124</v>
+        <v>-0.1918</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.1596</v>
+        <v>-5.5622</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3282</v>
+        <v>0.2784</v>
       </c>
       <c r="J52" t="n">
-        <v>9.1896</v>
+        <v>7.7952</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.07</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2245</v>
+        <v>0.1822</v>
       </c>
       <c r="J53" t="n">
-        <v>6.286</v>
+        <v>5.1016</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.91</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1245</v>
+        <v>-0.1089</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.486</v>
+        <v>-3.0492</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.66</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3702</v>
+        <v>-0.3564</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.3656</v>
+        <v>-9.979200000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.52</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4939</v>
+        <v>-0.4929</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.8292</v>
+        <v>-13.8012</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.69</v>
       </c>
       <c r="I57" t="n">
-        <v>1.2115</v>
+        <v>1.2104</v>
       </c>
       <c r="J57" t="n">
-        <v>33.922</v>
+        <v>33.8912</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5488</v>
+        <v>0.5415</v>
       </c>
       <c r="J58" t="n">
-        <v>15.3664</v>
+        <v>15.162</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.12</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3615</v>
+        <v>0.3275</v>
       </c>
       <c r="J59" t="n">
-        <v>10.122</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0332</v>
+        <v>-0.0276</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.9296</v>
+        <v>-0.7728</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.96</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.205</v>
+        <v>-0.1706</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.74</v>
+        <v>-4.7768</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.88</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.0619</v>
       </c>
       <c r="J62" t="n">
-        <v>-1.5351</v>
+        <v>-1.0523</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.86</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1152</v>
+        <v>-0.0887</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.9584</v>
+        <v>-1.5079</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.37</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.5883</v>
+        <v>-0.5974</v>
       </c>
       <c r="J64" t="n">
-        <v>-10.0011</v>
+        <v>-10.1558</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.34</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.6151</v>
+        <v>-0.6283</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.4567</v>
+        <v>-10.6811</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.33</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6241</v>
+        <v>-0.6388</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.6097</v>
+        <v>-10.8596</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>2.21</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0077</v>
+        <v>0.9472</v>
       </c>
       <c r="J67" t="n">
-        <v>17.1309</v>
+        <v>16.1024</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.71</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6917</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="J68" t="n">
-        <v>11.7589</v>
+        <v>11.0279</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.4</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4777</v>
+        <v>0.4314</v>
       </c>
       <c r="J69" t="n">
-        <v>8.120900000000001</v>
+        <v>7.3338</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.33</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4173</v>
+        <v>0.3616</v>
       </c>
       <c r="J70" t="n">
-        <v>7.0941</v>
+        <v>6.1472</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.25</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3291</v>
+        <v>0.2779</v>
       </c>
       <c r="J71" t="n">
-        <v>5.5947</v>
+        <v>4.7243</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.41</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8585</v>
+        <v>0.8435</v>
       </c>
       <c r="J72" t="n">
-        <v>24.8965</v>
+        <v>24.4615</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.32</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7238</v>
+        <v>0.708</v>
       </c>
       <c r="J73" t="n">
-        <v>20.9902</v>
+        <v>20.532</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.08</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2745</v>
+        <v>0.2386</v>
       </c>
       <c r="J74" t="n">
-        <v>7.9605</v>
+        <v>6.9194</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.9</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3575</v>
+        <v>-0.3148</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.3675</v>
+        <v>-9.129200000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8666</v>
+        <v>-0.8495</v>
       </c>
       <c r="J76" t="n">
-        <v>-25.1314</v>
+        <v>-24.6355</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.11</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2791</v>
+        <v>0.23</v>
       </c>
       <c r="J77" t="n">
-        <v>8.0939</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2595</v>
+        <v>0.212</v>
       </c>
       <c r="J78" t="n">
-        <v>7.5255</v>
+        <v>6.148</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.1</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2595</v>
+        <v>0.212</v>
       </c>
       <c r="J79" t="n">
-        <v>7.5255</v>
+        <v>6.148</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.76</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2881</v>
+        <v>-0.2694</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.354900000000001</v>
+        <v>-7.8126</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.75</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2976</v>
+        <v>-0.2794</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.6304</v>
+        <v>-8.102600000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>1.2139</v>
+        <v>1.2109</v>
       </c>
       <c r="J82" t="n">
-        <v>24.278</v>
+        <v>24.218</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.45</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8637</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>17.274</v>
+        <v>17.026</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.44</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.8379</v>
       </c>
       <c r="J84" t="n">
-        <v>17.006</v>
+        <v>16.758</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.11</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3119</v>
+        <v>0.28</v>
       </c>
       <c r="J85" t="n">
-        <v>6.238</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.03</v>
       </c>
       <c r="I86" t="n">
-        <v>0.0793</v>
+        <v>0.0577</v>
       </c>
       <c r="J86" t="n">
-        <v>1.586</v>
+        <v>1.154</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.91</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.1109</v>
+        <v>-0.0963</v>
       </c>
       <c r="J87" t="n">
-        <v>-2.218</v>
+        <v>-1.926</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.88</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1463</v>
+        <v>-0.1309</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.926</v>
+        <v>-2.618</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.86</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1686</v>
+        <v>-0.1529</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.372</v>
+        <v>-3.058</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.6</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4133</v>
+        <v>-0.4029</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.266</v>
+        <v>-8.058</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.55</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4575</v>
+        <v>-0.4513</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.15</v>
+        <v>-9.026</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.34</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4452</v>
+        <v>0.3859</v>
       </c>
       <c r="J92" t="n">
-        <v>11.13</v>
+        <v>9.647500000000001</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.28</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3852</v>
+        <v>0.3264</v>
       </c>
       <c r="J93" t="n">
-        <v>9.630000000000001</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.26</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3636</v>
+        <v>0.3066</v>
       </c>
       <c r="J94" t="n">
-        <v>9.09</v>
+        <v>7.665</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.24</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3412</v>
+        <v>0.2863</v>
       </c>
       <c r="J95" t="n">
-        <v>8.529999999999999</v>
+        <v>7.1575</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.24</v>
       </c>
       <c r="I96" t="n">
-        <v>0.3412</v>
+        <v>0.2863</v>
       </c>
       <c r="J96" t="n">
-        <v>8.529999999999999</v>
+        <v>7.1575</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.0265</v>
+        <v>0.0246</v>
       </c>
       <c r="J97" t="n">
-        <v>0.6625</v>
+        <v>0.615</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.89</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1439</v>
+        <v>-0.128</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.5975</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.85</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1871</v>
+        <v>-0.1698</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.6775</v>
+        <v>-4.245</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3394</v>
+        <v>-0.3236</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.484999999999999</v>
+        <v>-8.09</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3394</v>
+        <v>-0.3236</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.484999999999999</v>
+        <v>-8.09</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.91</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.1048</v>
+        <v>-0.0896</v>
       </c>
       <c r="J102" t="n">
-        <v>-2.096</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.78</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.2467</v>
+        <v>-0.2315</v>
       </c>
       <c r="J103" t="n">
-        <v>-4.934</v>
+        <v>-4.63</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.73</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2933</v>
+        <v>-0.2783</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.866</v>
+        <v>-5.566</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3288</v>
+        <v>-0.3142</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.576</v>
+        <v>-6.284</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.53</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4712</v>
+        <v>-0.4663</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.423999999999999</v>
+        <v>-9.326000000000001</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.76</v>
       </c>
       <c r="I107" t="n">
-        <v>1.2536</v>
+        <v>1.2529</v>
       </c>
       <c r="J107" t="n">
-        <v>25.072</v>
+        <v>25.058</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.63</v>
       </c>
       <c r="I108" t="n">
-        <v>1.0913</v>
+        <v>1.0833</v>
       </c>
       <c r="J108" t="n">
-        <v>21.826</v>
+        <v>21.666</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.29</v>
       </c>
       <c r="I109" t="n">
-        <v>0.6371</v>
+        <v>0.6318</v>
       </c>
       <c r="J109" t="n">
-        <v>12.742</v>
+        <v>12.636</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.23</v>
       </c>
       <c r="I110" t="n">
-        <v>0.5451</v>
+        <v>0.5432</v>
       </c>
       <c r="J110" t="n">
-        <v>10.902</v>
+        <v>10.864</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.1</v>
       </c>
       <c r="I111" t="n">
-        <v>0.278</v>
+        <v>0.2458</v>
       </c>
       <c r="J111" t="n">
-        <v>5.56</v>
+        <v>4.916</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.17</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3912</v>
+        <v>0.3355</v>
       </c>
       <c r="J112" t="n">
-        <v>11.3448</v>
+        <v>9.7295</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1987</v>
+        <v>0.1574</v>
       </c>
       <c r="J113" t="n">
-        <v>5.7623</v>
+        <v>4.5646</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.02</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0789</v>
+        <v>0.056</v>
       </c>
       <c r="J114" t="n">
-        <v>2.2881</v>
+        <v>1.624</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.79</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2586</v>
+        <v>-0.2389</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.4994</v>
+        <v>-6.9281</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.75</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2972</v>
+        <v>-0.279</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.6188</v>
+        <v>-8.090999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.54</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0281</v>
+        <v>1.0176</v>
       </c>
       <c r="J117" t="n">
-        <v>29.8149</v>
+        <v>29.5104</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.16</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4568</v>
+        <v>0.4259</v>
       </c>
       <c r="J118" t="n">
-        <v>13.2472</v>
+        <v>12.3511</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.12</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3705</v>
+        <v>0.3337</v>
       </c>
       <c r="J119" t="n">
-        <v>10.7445</v>
+        <v>9.677300000000001</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.96</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1934</v>
+        <v>-0.1587</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.6086</v>
+        <v>-4.6023</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.89</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3946</v>
+        <v>-0.3522</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.4434</v>
+        <v>-10.2138</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.277</v>
+        <v>-0.2606</v>
       </c>
       <c r="J122" t="n">
-        <v>-4.432</v>
+        <v>-4.1696</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.66</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.3088</v>
+        <v>-0.2963</v>
       </c>
       <c r="J123" t="n">
-        <v>-4.9408</v>
+        <v>-4.7408</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.43</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.5239</v>
       </c>
       <c r="J124" t="n">
-        <v>-8.347200000000001</v>
+        <v>-8.382400000000001</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.42</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5305</v>
+        <v>-0.5333</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.488</v>
+        <v>-8.5328</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.2</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7318</v>
+        <v>-0.7668</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.7088</v>
+        <v>-12.2688</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>2.27</v>
       </c>
       <c r="I127" t="n">
-        <v>1.805</v>
+        <v>1.8528</v>
       </c>
       <c r="J127" t="n">
-        <v>28.88</v>
+        <v>29.6448</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.82</v>
       </c>
       <c r="I128" t="n">
-        <v>1.2949</v>
+        <v>1.2993</v>
       </c>
       <c r="J128" t="n">
-        <v>20.7184</v>
+        <v>20.7888</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.4</v>
       </c>
       <c r="I129" t="n">
-        <v>0.7749</v>
+        <v>0.7702</v>
       </c>
       <c r="J129" t="n">
-        <v>12.3984</v>
+        <v>12.3232</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.33</v>
       </c>
       <c r="I130" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6721</v>
       </c>
       <c r="J130" t="n">
-        <v>10.8144</v>
+        <v>10.7536</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.18</v>
       </c>
       <c r="I131" t="n">
-        <v>0.4408</v>
+        <v>0.4123</v>
       </c>
       <c r="J131" t="n">
-        <v>7.0528</v>
+        <v>6.5968</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.35</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4723</v>
+        <v>0.4165</v>
       </c>
       <c r="J132" t="n">
-        <v>12.2798</v>
+        <v>10.829</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.26</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3814</v>
+        <v>0.3193</v>
       </c>
       <c r="J133" t="n">
-        <v>9.916399999999999</v>
+        <v>8.3018</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.13</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2195</v>
+        <v>0.1739</v>
       </c>
       <c r="J134" t="n">
-        <v>5.707</v>
+        <v>4.5214</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1062</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="J135" t="n">
-        <v>-2.7612</v>
+        <v>-2.2984</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.76</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.299</v>
+        <v>-0.2816</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.774</v>
+        <v>-7.3216</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.09</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1812</v>
+        <v>0.1644</v>
       </c>
       <c r="J137" t="n">
-        <v>4.7112</v>
+        <v>4.2744</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1491</v>
+        <v>0.1325</v>
       </c>
       <c r="J138" t="n">
-        <v>3.8766</v>
+        <v>3.445</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0968</v>
+        <v>0.0822</v>
       </c>
       <c r="J139" t="n">
-        <v>2.5168</v>
+        <v>2.1372</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0003</v>
+        <v>-0.0001</v>
       </c>
       <c r="J140" t="n">
-        <v>-0.0078</v>
+        <v>-0.0026</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.84</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2126</v>
+        <v>-0.192</v>
       </c>
       <c r="J141" t="n">
-        <v>-5.5276</v>
+        <v>-4.992</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.14</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3284</v>
+        <v>0.2759</v>
       </c>
       <c r="J142" t="n">
-        <v>8.8668</v>
+        <v>7.4493</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.12</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2913</v>
+        <v>0.2414</v>
       </c>
       <c r="J143" t="n">
-        <v>7.8651</v>
+        <v>6.5178</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0859</v>
+        <v>-0.0703</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.3193</v>
+        <v>-1.8981</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0989</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.6703</v>
+        <v>-2.2167</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.84</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2117</v>
+        <v>-0.1911</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.7159</v>
+        <v>-5.1597</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.27</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.6198</v>
       </c>
       <c r="J147" t="n">
-        <v>17.0802</v>
+        <v>16.7346</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.24</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5858</v>
+        <v>0.5752</v>
       </c>
       <c r="J148" t="n">
-        <v>15.8166</v>
+        <v>15.5304</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.19</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4909</v>
       </c>
       <c r="J149" t="n">
-        <v>13.6485</v>
+        <v>13.2543</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.16</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4551</v>
+        <v>0.4248</v>
       </c>
       <c r="J150" t="n">
-        <v>12.2877</v>
+        <v>11.4696</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.9</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3715</v>
+        <v>-0.3296</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.0305</v>
+        <v>-8.8992</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.58</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7046</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="J152" t="n">
-        <v>20.4334</v>
+        <v>18.3454</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.54</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6646</v>
+        <v>0.5927</v>
       </c>
       <c r="J153" t="n">
-        <v>19.2734</v>
+        <v>17.1883</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.18</v>
       </c>
       <c r="I154" t="n">
-        <v>0.275</v>
+        <v>0.2254</v>
       </c>
       <c r="J154" t="n">
-        <v>7.975</v>
+        <v>6.5366</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.99</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0406</v>
+        <v>-0.0312</v>
       </c>
       <c r="J155" t="n">
-        <v>-1.1774</v>
+        <v>-0.9048</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.74</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3267</v>
+        <v>-0.3125</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.474299999999999</v>
+        <v>-9.0625</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.12</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3107</v>
+        <v>0.2598</v>
       </c>
       <c r="J157" t="n">
-        <v>9.010300000000001</v>
+        <v>7.5342</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.01</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0565</v>
+        <v>0.0386</v>
       </c>
       <c r="J158" t="n">
-        <v>1.6385</v>
+        <v>1.1194</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.9</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1401</v>
+        <v>-0.1222</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.0629</v>
+        <v>-3.5438</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.78</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2639</v>
+        <v>-0.2445</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.6531</v>
+        <v>-7.0905</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.76</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2832</v>
+        <v>-0.2644</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.2128</v>
+        <v>-7.6676</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.38</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5204</v>
+        <v>0.4516</v>
       </c>
       <c r="J162" t="n">
-        <v>14.0508</v>
+        <v>12.1932</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.14</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2344</v>
+        <v>0.1865</v>
       </c>
       <c r="J163" t="n">
-        <v>6.3288</v>
+        <v>5.0355</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.01</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0268</v>
+        <v>0.0177</v>
       </c>
       <c r="J164" t="n">
-        <v>0.7236</v>
+        <v>0.4779</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0781</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="J165" t="n">
-        <v>-2.1087</v>
+        <v>-1.6929</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.87</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1865</v>
+        <v>-0.1659</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.0355</v>
+        <v>-4.4793</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.28</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5553</v>
+        <v>0.4956</v>
       </c>
       <c r="J167" t="n">
-        <v>14.9931</v>
+        <v>13.3812</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.09</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2265</v>
+        <v>0.1835</v>
       </c>
       <c r="J168" t="n">
-        <v>6.1155</v>
+        <v>4.9545</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="J169" t="n">
-        <v>1.89</v>
+        <v>1.377</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1022</v>
+        <v>-0.0848</v>
       </c>
       <c r="J170" t="n">
-        <v>-2.7594</v>
+        <v>-2.2896</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.87</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1837</v>
+        <v>-0.1631</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.9599</v>
+        <v>-4.4037</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.9</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="J172" t="n">
-        <v>-1.8544</v>
+        <v>-1.4953</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.79</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2227</v>
+        <v>-0.2078</v>
       </c>
       <c r="J173" t="n">
-        <v>-4.2313</v>
+        <v>-3.9482</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.77</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2434</v>
+        <v>-0.2293</v>
       </c>
       <c r="J174" t="n">
-        <v>-4.6246</v>
+        <v>-4.3567</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.48</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5047</v>
+        <v>-0.5033</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.5893</v>
+        <v>-9.5627</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.3</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6619</v>
+        <v>-0.6851</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.5761</v>
+        <v>-13.0169</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>2.09</v>
       </c>
       <c r="I177" t="n">
-        <v>1.093</v>
+        <v>1.0539</v>
       </c>
       <c r="J177" t="n">
-        <v>20.767</v>
+        <v>20.0241</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.6</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6894</v>
+        <v>0.6197</v>
       </c>
       <c r="J178" t="n">
-        <v>13.0986</v>
+        <v>11.7743</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.47</v>
       </c>
       <c r="I179" t="n">
-        <v>0.5674</v>
+        <v>0.5019</v>
       </c>
       <c r="J179" t="n">
-        <v>10.7806</v>
+        <v>9.536099999999999</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.3</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3933</v>
+        <v>0.3375</v>
       </c>
       <c r="J180" t="n">
-        <v>7.4727</v>
+        <v>6.4125</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.92</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.158</v>
+        <v>-0.1423</v>
       </c>
       <c r="J181" t="n">
-        <v>-3.002</v>
+        <v>-2.7037</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.29</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6019</v>
+        <v>0.5455</v>
       </c>
       <c r="J182" t="n">
-        <v>16.2513</v>
+        <v>14.7285</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.15</v>
       </c>
       <c r="I183" t="n">
-        <v>0.3619</v>
+        <v>0.3078</v>
       </c>
       <c r="J183" t="n">
-        <v>9.7713</v>
+        <v>8.310600000000001</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.85</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1955</v>
+        <v>-0.1754</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.2785</v>
+        <v>-4.7358</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.75</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2947</v>
+        <v>-0.2764</v>
       </c>
       <c r="J185" t="n">
-        <v>-7.9569</v>
+        <v>-7.4628</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.63</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.405</v>
+        <v>-0.3946</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.935</v>
+        <v>-10.6542</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.43</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5583</v>
+        <v>0.488</v>
       </c>
       <c r="J187" t="n">
-        <v>15.0741</v>
+        <v>13.176</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.22</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3251</v>
+        <v>0.269</v>
       </c>
       <c r="J188" t="n">
-        <v>8.777699999999999</v>
+        <v>7.263</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.15</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2404</v>
+        <v>0.1939</v>
       </c>
       <c r="J189" t="n">
-        <v>6.4908</v>
+        <v>5.2353</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.1</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1733</v>
+        <v>0.1361</v>
       </c>
       <c r="J190" t="n">
-        <v>4.6791</v>
+        <v>3.6747</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.92</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.1371</v>
+        <v>-0.1181</v>
       </c>
       <c r="J191" t="n">
-        <v>-3.7017</v>
+        <v>-3.1887</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>0.93</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0921</v>
+        <v>-0.0785</v>
       </c>
       <c r="J192" t="n">
-        <v>-2.0262</v>
+        <v>-1.727</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.85</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1842</v>
+        <v>-0.1677</v>
       </c>
       <c r="J193" t="n">
-        <v>-4.0524</v>
+        <v>-3.6894</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.84</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1946</v>
+        <v>-0.1779</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.2812</v>
+        <v>-3.9138</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.72</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3087</v>
+        <v>-0.292</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.7914</v>
+        <v>-6.424</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.64</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3817</v>
+        <v>-0.3687</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.397399999999999</v>
+        <v>-8.1114</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.67</v>
       </c>
       <c r="I197" t="n">
-        <v>1.2942</v>
+        <v>1.3134</v>
       </c>
       <c r="J197" t="n">
-        <v>28.4724</v>
+        <v>28.8948</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.51</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0881</v>
+        <v>1.1009</v>
       </c>
       <c r="J198" t="n">
-        <v>23.9382</v>
+        <v>24.2198</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.48</v>
       </c>
       <c r="I199" t="n">
-        <v>1.0473</v>
+        <v>1.0561</v>
       </c>
       <c r="J199" t="n">
-        <v>23.0406</v>
+        <v>23.2342</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.2</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5218</v>
+        <v>0.493</v>
       </c>
       <c r="J200" t="n">
-        <v>11.4796</v>
+        <v>10.846</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.0618</v>
+        <v>-0.0587</v>
       </c>
       <c r="J201" t="n">
-        <v>-1.3596</v>
+        <v>-1.2914</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.6</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2192</v>
+        <v>1.2348</v>
       </c>
       <c r="J202" t="n">
-        <v>25.6032</v>
+        <v>25.9308</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.52</v>
       </c>
       <c r="I203" t="n">
-        <v>1.1135</v>
+        <v>1.126</v>
       </c>
       <c r="J203" t="n">
-        <v>23.3835</v>
+        <v>23.646</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.16</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4431</v>
+        <v>0.4113</v>
       </c>
       <c r="J204" t="n">
-        <v>9.305099999999999</v>
+        <v>8.6373</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.1</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2952</v>
+        <v>0.2637</v>
       </c>
       <c r="J205" t="n">
-        <v>6.1992</v>
+        <v>5.5377</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.08</v>
       </c>
       <c r="I206" t="n">
-        <v>0.2414</v>
+        <v>0.2112</v>
       </c>
       <c r="J206" t="n">
-        <v>5.0694</v>
+        <v>4.4352</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.02</v>
       </c>
       <c r="I207" t="n">
-        <v>0.1068</v>
+        <v>0.081</v>
       </c>
       <c r="J207" t="n">
-        <v>2.2428</v>
+        <v>1.701</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.92</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1102</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.3142</v>
+        <v>-2.0097</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.86</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1777</v>
+        <v>-0.1604</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.7317</v>
+        <v>-3.3684</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.76</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2753</v>
+        <v>-0.2571</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.7813</v>
+        <v>-5.3991</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.62</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4041</v>
+        <v>-0.393</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.4861</v>
+        <v>-8.253</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.53</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9091</v>
+        <v>0.8607</v>
       </c>
       <c r="J212" t="n">
-        <v>25.4548</v>
+        <v>24.0996</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.29</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5586</v>
+        <v>0.4989</v>
       </c>
       <c r="J213" t="n">
-        <v>15.6408</v>
+        <v>13.9692</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.05</v>
       </c>
       <c r="I214" t="n">
-        <v>0.138</v>
+        <v>0.1084</v>
       </c>
       <c r="J214" t="n">
-        <v>3.864</v>
+        <v>3.0352</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2508</v>
+        <v>-0.2313</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.0224</v>
+        <v>-6.4764</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.8</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2607</v>
+        <v>-0.2416</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.2996</v>
+        <v>-6.7648</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.53</v>
       </c>
       <c r="I217" t="n">
-        <v>0.6752</v>
+        <v>0.6047</v>
       </c>
       <c r="J217" t="n">
-        <v>18.9056</v>
+        <v>16.9316</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.2</v>
       </c>
       <c r="I218" t="n">
-        <v>0.308</v>
+        <v>0.2522</v>
       </c>
       <c r="J218" t="n">
-        <v>8.624000000000001</v>
+        <v>7.0616</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.04</v>
       </c>
       <c r="I219" t="n">
-        <v>0.0852</v>
+        <v>0.0623</v>
       </c>
       <c r="J219" t="n">
-        <v>2.3856</v>
+        <v>1.7444</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0322</v>
+        <v>-0.0233</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.9016</v>
+        <v>-0.6524</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.73</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3281</v>
+        <v>-0.3127</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.1868</v>
+        <v>-8.755599999999999</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.24</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5043</v>
+        <v>0.4455</v>
       </c>
       <c r="J222" t="n">
-        <v>15.129</v>
+        <v>13.365</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.15</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3492</v>
+        <v>0.2953</v>
       </c>
       <c r="J223" t="n">
-        <v>10.476</v>
+        <v>8.859</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.93</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1104</v>
+        <v>-0.0929</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.312</v>
+        <v>-2.787</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.93</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1104</v>
+        <v>-0.0929</v>
       </c>
       <c r="J225" t="n">
-        <v>-3.312</v>
+        <v>-2.787</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.68</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3647</v>
+        <v>-0.3512</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.941</v>
+        <v>-10.536</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.36</v>
       </c>
       <c r="I227" t="n">
-        <v>0.489</v>
+        <v>0.421</v>
       </c>
       <c r="J227" t="n">
-        <v>14.67</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.36</v>
       </c>
       <c r="I228" t="n">
-        <v>0.489</v>
+        <v>0.421</v>
       </c>
       <c r="J228" t="n">
-        <v>14.67</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.25</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3645</v>
+        <v>0.3041</v>
       </c>
       <c r="J229" t="n">
-        <v>10.935</v>
+        <v>9.122999999999999</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.85</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2122</v>
+        <v>-0.1921</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.366</v>
+        <v>-5.763</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2532</v>
+        <v>-0.2341</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.596</v>
+        <v>-7.023</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.63</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7211</v>
+        <v>0.6502</v>
       </c>
       <c r="J232" t="n">
-        <v>15.1431</v>
+        <v>13.6542</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.56</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6553</v>
+        <v>0.5856</v>
       </c>
       <c r="J233" t="n">
-        <v>13.7613</v>
+        <v>12.2976</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.53</v>
       </c>
       <c r="I234" t="n">
-        <v>0.6267</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="J234" t="n">
-        <v>13.1607</v>
+        <v>11.718</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.4</v>
       </c>
       <c r="I235" t="n">
-        <v>0.5012</v>
+        <v>0.4382</v>
       </c>
       <c r="J235" t="n">
-        <v>10.5252</v>
+        <v>9.202199999999999</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.06</v>
       </c>
       <c r="I236" t="n">
-        <v>0.0888</v>
+        <v>0.0638</v>
       </c>
       <c r="J236" t="n">
-        <v>1.8648</v>
+        <v>1.3398</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.85</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1706</v>
+        <v>-0.155</v>
       </c>
       <c r="J237" t="n">
-        <v>-3.5826</v>
+        <v>-3.255</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.8</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2237</v>
+        <v>-0.2087</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.6977</v>
+        <v>-4.3827</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.79</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2339</v>
+        <v>-0.219</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.9119</v>
+        <v>-4.599</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.65</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3623</v>
+        <v>-0.3494</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.6083</v>
+        <v>-7.3374</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.45</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5386</v>
+        <v>-0.542</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.3106</v>
+        <v>-11.382</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.55</v>
       </c>
       <c r="I242" t="n">
-        <v>0.6737</v>
+        <v>0.6016</v>
       </c>
       <c r="J242" t="n">
-        <v>16.8425</v>
+        <v>15.04</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.35</v>
       </c>
       <c r="I243" t="n">
-        <v>0.4664</v>
+        <v>0.4004</v>
       </c>
       <c r="J243" t="n">
-        <v>11.66</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.18</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2746</v>
+        <v>0.2252</v>
       </c>
       <c r="J244" t="n">
-        <v>6.865</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.04</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0745</v>
+        <v>0.0541</v>
       </c>
       <c r="J245" t="n">
-        <v>1.8625</v>
+        <v>1.3525</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.116</v>
+        <v>-0.0984</v>
       </c>
       <c r="J246" t="n">
-        <v>-2.9</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.03</v>
       </c>
       <c r="I247" t="n">
-        <v>0.13</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="J247" t="n">
-        <v>3.25</v>
+        <v>2.4875</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.91</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1241</v>
+        <v>-0.1086</v>
       </c>
       <c r="J248" t="n">
-        <v>-3.1025</v>
+        <v>-2.715</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.8</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2384</v>
+        <v>-0.2194</v>
       </c>
       <c r="J249" t="n">
-        <v>-5.96</v>
+        <v>-5.485</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.79</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2481</v>
+        <v>-0.2292</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.2025</v>
+        <v>-5.73</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.73</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3053</v>
+        <v>-0.2878</v>
       </c>
       <c r="J251" t="n">
-        <v>-7.6325</v>
+        <v>-7.195</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.65</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7648</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="J252" t="n">
-        <v>20.6496</v>
+        <v>18.711</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.23</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3309</v>
+        <v>0.2766</v>
       </c>
       <c r="J253" t="n">
-        <v>8.9343</v>
+        <v>7.4682</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.22</v>
       </c>
       <c r="I254" t="n">
-        <v>0.3194</v>
+        <v>0.2662</v>
       </c>
       <c r="J254" t="n">
-        <v>8.623799999999999</v>
+        <v>7.1874</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.11</v>
       </c>
       <c r="I255" t="n">
-        <v>0.1795</v>
+        <v>0.1424</v>
       </c>
       <c r="J255" t="n">
-        <v>4.8465</v>
+        <v>3.8448</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.06</v>
       </c>
       <c r="I256" t="n">
-        <v>0.1045</v>
+        <v>0.0786</v>
       </c>
       <c r="J256" t="n">
-        <v>2.8215</v>
+        <v>2.1222</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.8</v>
       </c>
       <c r="I257" t="n">
-        <v>1.2586</v>
+        <v>1.2654</v>
       </c>
       <c r="J257" t="n">
-        <v>33.9822</v>
+        <v>34.1658</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.85</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.196</v>
+        <v>-0.1758</v>
       </c>
       <c r="J258" t="n">
-        <v>-5.292</v>
+        <v>-4.7466</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.73</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3142</v>
+        <v>-0.2969</v>
       </c>
       <c r="J259" t="n">
-        <v>-8.4834</v>
+        <v>-8.016299999999999</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.68</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3605</v>
+        <v>-0.3462</v>
       </c>
       <c r="J260" t="n">
-        <v>-9.733499999999999</v>
+        <v>-9.3474</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.64</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3966</v>
+        <v>-0.3855</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.7082</v>
+        <v>-10.4085</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.73</v>
       </c>
       <c r="I262" t="n">
-        <v>0.8355</v>
+        <v>0.7648</v>
       </c>
       <c r="J262" t="n">
-        <v>20.8875</v>
+        <v>19.12</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.44</v>
       </c>
       <c r="I263" t="n">
-        <v>0.5523</v>
+        <v>0.4833</v>
       </c>
       <c r="J263" t="n">
-        <v>13.8075</v>
+        <v>12.0825</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.41</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5216</v>
+        <v>0.4539</v>
       </c>
       <c r="J264" t="n">
-        <v>13.04</v>
+        <v>11.3475</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.97</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.08</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="J265" t="n">
-        <v>-2</v>
+        <v>-1.655</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.88</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.1919</v>
+        <v>-0.1732</v>
       </c>
       <c r="J266" t="n">
-        <v>-4.7975</v>
+        <v>-4.33</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.15</v>
       </c>
       <c r="I267" t="n">
-        <v>0.391</v>
+        <v>0.3398</v>
       </c>
       <c r="J267" t="n">
-        <v>9.775</v>
+        <v>8.494999999999999</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.91</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.123</v>
+        <v>-0.1077</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.075</v>
+        <v>-2.6925</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.83</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2081</v>
+        <v>-0.1897</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.2025</v>
+        <v>-4.7425</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.82</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2179</v>
+        <v>-0.1994</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.4475</v>
+        <v>-4.985</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.5</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5098</v>
+        <v>-0.5107</v>
       </c>
       <c r="J271" t="n">
-        <v>-12.745</v>
+        <v>-12.7675</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.24</v>
       </c>
       <c r="I272" t="n">
-        <v>0.3569</v>
+        <v>0.2967</v>
       </c>
       <c r="J272" t="n">
-        <v>9.9932</v>
+        <v>8.307600000000001</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.2</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3084</v>
+        <v>0.2526</v>
       </c>
       <c r="J273" t="n">
-        <v>8.635199999999999</v>
+        <v>7.0728</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.05</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1027</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="J274" t="n">
-        <v>2.8756</v>
+        <v>2.1364</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.99</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.0319</v>
+        <v>-0.023</v>
       </c>
       <c r="J275" t="n">
-        <v>-0.8932</v>
+        <v>-0.644</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.99</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.0319</v>
+        <v>-0.023</v>
       </c>
       <c r="J276" t="n">
-        <v>-0.8932</v>
+        <v>-0.644</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.25</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5241</v>
+        <v>0.4654</v>
       </c>
       <c r="J277" t="n">
-        <v>14.6748</v>
+        <v>13.0312</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.14</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3336</v>
+        <v>0.2807</v>
       </c>
       <c r="J278" t="n">
-        <v>9.3408</v>
+        <v>7.8596</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.02</v>
       </c>
       <c r="I279" t="n">
-        <v>0.0767</v>
+        <v>0.0545</v>
       </c>
       <c r="J279" t="n">
-        <v>2.1476</v>
+        <v>1.526</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.84</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2095</v>
+        <v>-0.189</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.866</v>
+        <v>-5.292</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.62</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4174</v>
+        <v>-0.4087</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.6872</v>
+        <v>-11.4436</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.43</v>
       </c>
       <c r="I282" t="n">
-        <v>0.5775</v>
+        <v>0.5078</v>
       </c>
       <c r="J282" t="n">
-        <v>16.17</v>
+        <v>14.2184</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.07</v>
       </c>
       <c r="I283" t="n">
-        <v>0.1367</v>
+        <v>0.1032</v>
       </c>
       <c r="J283" t="n">
-        <v>3.8276</v>
+        <v>2.8896</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.01</v>
       </c>
       <c r="I284" t="n">
-        <v>0.0279</v>
+        <v>0.0185</v>
       </c>
       <c r="J284" t="n">
-        <v>0.7812</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.96</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.0772</v>
+        <v>-0.0619</v>
       </c>
       <c r="J285" t="n">
-        <v>-2.1616</v>
+        <v>-1.7332</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.83</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2275</v>
+        <v>-0.2072</v>
       </c>
       <c r="J286" t="n">
-        <v>-6.37</v>
+        <v>-5.8016</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.39</v>
       </c>
       <c r="I287" t="n">
-        <v>0.7229</v>
+        <v>0.666</v>
       </c>
       <c r="J287" t="n">
-        <v>20.2412</v>
+        <v>18.648</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.17</v>
       </c>
       <c r="I288" t="n">
-        <v>0.3729</v>
+        <v>0.3182</v>
       </c>
       <c r="J288" t="n">
-        <v>10.4412</v>
+        <v>8.909599999999999</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1026</v>
+        <v>-0.0851</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.8728</v>
+        <v>-2.3828</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.92</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1273</v>
+        <v>-0.1083</v>
       </c>
       <c r="J290" t="n">
-        <v>-3.5644</v>
+        <v>-3.0324</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.8</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2563</v>
+        <v>-0.2367</v>
       </c>
       <c r="J291" t="n">
-        <v>-7.1764</v>
+        <v>-6.6276</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.29</v>
       </c>
       <c r="I292" t="n">
-        <v>0.7369</v>
+        <v>0.727</v>
       </c>
       <c r="J292" t="n">
-        <v>16.9487</v>
+        <v>16.721</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.59</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.4121</v>
+        <v>-0.4023</v>
       </c>
       <c r="J293" t="n">
-        <v>-9.478300000000001</v>
+        <v>-9.2529</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.57</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.4298</v>
+        <v>-0.4212</v>
       </c>
       <c r="J294" t="n">
-        <v>-9.885400000000001</v>
+        <v>-9.6876</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.48</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.509</v>
+        <v>-0.5082</v>
       </c>
       <c r="J295" t="n">
-        <v>-11.707</v>
+        <v>-11.6886</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.47</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5177</v>
+        <v>-0.518</v>
       </c>
       <c r="J296" t="n">
-        <v>-11.9071</v>
+        <v>-11.914</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.87</v>
       </c>
       <c r="I297" t="n">
-        <v>0.9419</v>
+        <v>0.8748</v>
       </c>
       <c r="J297" t="n">
-        <v>21.6637</v>
+        <v>20.1204</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.52</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6192</v>
+        <v>0.5501</v>
       </c>
       <c r="J298" t="n">
-        <v>14.2416</v>
+        <v>12.6523</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.31</v>
       </c>
       <c r="I299" t="n">
-        <v>0.409</v>
+        <v>0.3513</v>
       </c>
       <c r="J299" t="n">
-        <v>9.407</v>
+        <v>8.0799</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.27</v>
       </c>
       <c r="I300" t="n">
-        <v>0.3648</v>
+        <v>0.3103</v>
       </c>
       <c r="J300" t="n">
-        <v>8.3904</v>
+        <v>7.1369</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>1.09</v>
       </c>
       <c r="I301" t="n">
-        <v>0.1371</v>
+        <v>0.1052</v>
       </c>
       <c r="J301" t="n">
-        <v>3.1533</v>
+        <v>2.4196</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.32</v>
       </c>
       <c r="I302" t="n">
-        <v>0.6194</v>
+        <v>0.5601</v>
       </c>
       <c r="J302" t="n">
-        <v>18.582</v>
+        <v>16.803</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.18</v>
       </c>
       <c r="I303" t="n">
-        <v>0.3921</v>
+        <v>0.3363</v>
       </c>
       <c r="J303" t="n">
-        <v>11.763</v>
+        <v>10.089</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.02</v>
       </c>
       <c r="I304" t="n">
-        <v>0.0706</v>
+        <v>0.0513</v>
       </c>
       <c r="J304" t="n">
-        <v>2.118</v>
+        <v>1.539</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.83</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2252</v>
+        <v>-0.2048</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.756</v>
+        <v>-6.144</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.82</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2354</v>
+        <v>-0.2152</v>
       </c>
       <c r="J306" t="n">
-        <v>-7.062</v>
+        <v>-6.456</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.2</v>
       </c>
       <c r="I307" t="n">
-        <v>0.3146</v>
+        <v>0.2576</v>
       </c>
       <c r="J307" t="n">
-        <v>9.438000000000001</v>
+        <v>7.728</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.12</v>
       </c>
       <c r="I308" t="n">
-        <v>0.21</v>
+        <v>0.1648</v>
       </c>
       <c r="J308" t="n">
-        <v>6.3</v>
+        <v>4.944</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.11</v>
       </c>
       <c r="I309" t="n">
-        <v>0.1961</v>
+        <v>0.1528</v>
       </c>
       <c r="J309" t="n">
-        <v>5.883</v>
+        <v>4.584</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.93</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1155</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.465</v>
+        <v>-2.913</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.88</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.1735</v>
+        <v>-0.153</v>
       </c>
       <c r="J311" t="n">
-        <v>-5.205</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.15</v>
       </c>
       <c r="I312" t="n">
-        <v>0.4166</v>
+        <v>0.3706</v>
       </c>
       <c r="J312" t="n">
-        <v>10.415</v>
+        <v>9.265000000000001</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.88</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.1494</v>
+        <v>-0.1338</v>
       </c>
       <c r="J313" t="n">
-        <v>-3.735</v>
+        <v>-3.345</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.76</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.27</v>
+        <v>-0.253</v>
       </c>
       <c r="J314" t="n">
-        <v>-6.75</v>
+        <v>-6.325</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.73</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2977</v>
+        <v>-0.2811</v>
       </c>
       <c r="J315" t="n">
-        <v>-7.4425</v>
+        <v>-7.0275</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.38</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6063</v>
+        <v>-0.6214</v>
       </c>
       <c r="J316" t="n">
-        <v>-15.1575</v>
+        <v>-15.535</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.55</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="J317" t="n">
-        <v>16.47</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.43</v>
       </c>
       <c r="I318" t="n">
-        <v>0.5392</v>
+        <v>0.4713</v>
       </c>
       <c r="J318" t="n">
-        <v>13.48</v>
+        <v>11.7825</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.38</v>
       </c>
       <c r="I319" t="n">
-        <v>0.488</v>
+        <v>0.4228</v>
       </c>
       <c r="J319" t="n">
-        <v>12.2</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.21</v>
       </c>
       <c r="I320" t="n">
-        <v>0.303</v>
+        <v>0.2525</v>
       </c>
       <c r="J320" t="n">
-        <v>7.575</v>
+        <v>6.3125</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>1</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.0227</v>
+        <v>-0.0206</v>
       </c>
       <c r="J321" t="n">
-        <v>-0.5675</v>
+        <v>-0.515</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>0.98</v>
       </c>
       <c r="I322" t="n">
-        <v>-0.031</v>
+        <v>-0.0237</v>
       </c>
       <c r="J322" t="n">
-        <v>-0.837</v>
+        <v>-0.6399</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>0.93</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.1015</v>
+        <v>-0.0871</v>
       </c>
       <c r="J323" t="n">
-        <v>-2.7405</v>
+        <v>-2.3517</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.9</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.137</v>
+        <v>-0.1205</v>
       </c>
       <c r="J324" t="n">
-        <v>-3.699</v>
+        <v>-3.2535</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.77</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2688</v>
+        <v>-0.25</v>
       </c>
       <c r="J325" t="n">
-        <v>-7.2576</v>
+        <v>-6.75</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.75</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2879</v>
+        <v>-0.2696</v>
       </c>
       <c r="J326" t="n">
-        <v>-7.7733</v>
+        <v>-7.2792</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.66</v>
       </c>
       <c r="I327" t="n">
-        <v>0.7731</v>
+        <v>0.7014</v>
       </c>
       <c r="J327" t="n">
-        <v>20.8737</v>
+        <v>18.9378</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.46</v>
       </c>
       <c r="I328" t="n">
-        <v>0.5756</v>
+        <v>0.5054</v>
       </c>
       <c r="J328" t="n">
-        <v>15.5412</v>
+        <v>13.6458</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.1</v>
       </c>
       <c r="I329" t="n">
-        <v>0.1646</v>
+        <v>0.1295</v>
       </c>
       <c r="J329" t="n">
-        <v>4.4442</v>
+        <v>3.4965</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.07</v>
       </c>
       <c r="I330" t="n">
-        <v>0.1197</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="J330" t="n">
-        <v>3.2319</v>
+        <v>2.4651</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>1.02</v>
       </c>
       <c r="I331" t="n">
-        <v>0.0313</v>
+        <v>0.0196</v>
       </c>
       <c r="J331" t="n">
-        <v>0.8451</v>
+        <v>0.5292</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.11</v>
       </c>
       <c r="I332" t="n">
-        <v>0.2805</v>
+        <v>0.2312</v>
       </c>
       <c r="J332" t="n">
-        <v>7.293</v>
+        <v>6.0112</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.1</v>
       </c>
       <c r="I333" t="n">
-        <v>0.2608</v>
+        <v>0.2132</v>
       </c>
       <c r="J333" t="n">
-        <v>6.7808</v>
+        <v>5.5432</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.09</v>
       </c>
       <c r="I334" t="n">
-        <v>0.2408</v>
+        <v>0.195</v>
       </c>
       <c r="J334" t="n">
-        <v>6.2608</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.96</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.0701</v>
+        <v>-0.0569</v>
       </c>
       <c r="J335" t="n">
-        <v>-1.8226</v>
+        <v>-1.4794</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.53</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.4943</v>
+        <v>-0.4946</v>
       </c>
       <c r="J336" t="n">
-        <v>-12.8518</v>
+        <v>-12.8596</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.5</v>
       </c>
       <c r="I337" t="n">
-        <v>0.6194</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="J337" t="n">
-        <v>16.1044</v>
+        <v>14.2454</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.24</v>
       </c>
       <c r="I338" t="n">
-        <v>0.343</v>
+        <v>0.2871</v>
       </c>
       <c r="J338" t="n">
-        <v>8.917999999999999</v>
+        <v>7.4646</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.2</v>
       </c>
       <c r="I339" t="n">
-        <v>0.2969</v>
+        <v>0.2456</v>
       </c>
       <c r="J339" t="n">
-        <v>7.7194</v>
+        <v>6.3856</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.14</v>
       </c>
       <c r="I340" t="n">
-        <v>0.2217</v>
+        <v>0.179</v>
       </c>
       <c r="J340" t="n">
-        <v>5.7642</v>
+        <v>4.654</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>1.11</v>
       </c>
       <c r="I341" t="n">
-        <v>0.181</v>
+        <v>0.1435</v>
       </c>
       <c r="J341" t="n">
-        <v>4.706</v>
+        <v>3.731</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.21</v>
       </c>
       <c r="I342" t="n">
-        <v>0.4661</v>
+        <v>0.4087</v>
       </c>
       <c r="J342" t="n">
-        <v>13.5169</v>
+        <v>11.8523</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.09</v>
       </c>
       <c r="I343" t="n">
-        <v>0.2443</v>
+        <v>0.1982</v>
       </c>
       <c r="J343" t="n">
-        <v>7.0847</v>
+        <v>5.7478</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.05</v>
       </c>
       <c r="I344" t="n">
-        <v>0.1579</v>
+        <v>0.1216</v>
       </c>
       <c r="J344" t="n">
-        <v>4.5791</v>
+        <v>3.5264</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.92</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1191</v>
+        <v>-0.1018</v>
       </c>
       <c r="J345" t="n">
-        <v>-3.4539</v>
+        <v>-2.9522</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.44</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.569</v>
+        <v>-0.5802</v>
       </c>
       <c r="J346" t="n">
-        <v>-16.501</v>
+        <v>-16.8258</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.45</v>
       </c>
       <c r="I347" t="n">
-        <v>0.5774</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="J347" t="n">
-        <v>16.7446</v>
+        <v>14.6914</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.29</v>
       </c>
       <c r="I348" t="n">
-        <v>0.4045</v>
+        <v>0.3419</v>
       </c>
       <c r="J348" t="n">
-        <v>11.7305</v>
+        <v>9.915100000000001</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.12</v>
       </c>
       <c r="I349" t="n">
-        <v>0.2001</v>
+        <v>0.1593</v>
       </c>
       <c r="J349" t="n">
-        <v>5.8029</v>
+        <v>4.6197</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>1.01</v>
       </c>
       <c r="I350" t="n">
-        <v>0.0167</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="J350" t="n">
-        <v>0.4843</v>
+        <v>0.2871</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>1.01</v>
       </c>
       <c r="I351" t="n">
-        <v>0.0167</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="J351" t="n">
-        <v>0.4843</v>
+        <v>0.2871</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.04</v>
       </c>
       <c r="I352" t="n">
-        <v>0.1723</v>
+        <v>0.139</v>
       </c>
       <c r="J352" t="n">
-        <v>4.3075</v>
+        <v>3.475</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>0.92</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.1052</v>
+        <v>-0.0911</v>
       </c>
       <c r="J353" t="n">
-        <v>-2.63</v>
+        <v>-2.2775</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>0.84</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.195</v>
+        <v>-0.1782</v>
       </c>
       <c r="J354" t="n">
-        <v>-4.875</v>
+        <v>-4.455</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>0.65</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.3731</v>
+        <v>-0.3596</v>
       </c>
       <c r="J355" t="n">
-        <v>-9.327500000000001</v>
+        <v>-8.99</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>0.55</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.462</v>
+        <v>-0.4566</v>
       </c>
       <c r="J356" t="n">
-        <v>-11.55</v>
+        <v>-11.415</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.69</v>
       </c>
       <c r="I357" t="n">
-        <v>0.7904</v>
+        <v>0.7187</v>
       </c>
       <c r="J357" t="n">
-        <v>19.76</v>
+        <v>17.9675</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>1.39</v>
       </c>
       <c r="I358" t="n">
-        <v>0.4969</v>
+        <v>0.4316</v>
       </c>
       <c r="J358" t="n">
-        <v>12.4225</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>1.38</v>
       </c>
       <c r="I359" t="n">
-        <v>0.4867</v>
+        <v>0.4219</v>
       </c>
       <c r="J359" t="n">
-        <v>12.1675</v>
+        <v>10.5475</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>1.15</v>
       </c>
       <c r="I360" t="n">
-        <v>0.2268</v>
+        <v>0.1842</v>
       </c>
       <c r="J360" t="n">
-        <v>5.67</v>
+        <v>4.605</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>1.05</v>
       </c>
       <c r="I361" t="n">
-        <v>0.081</v>
+        <v>0.0584</v>
       </c>
       <c r="J361" t="n">
-        <v>2.025</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.32</v>
       </c>
       <c r="I362" t="n">
-        <v>0.7353</v>
+        <v>0.7068</v>
       </c>
       <c r="J362" t="n">
-        <v>16.1766</v>
+        <v>15.5496</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.01</v>
       </c>
       <c r="I363" t="n">
-        <v>0.1024</v>
+        <v>0.0849</v>
       </c>
       <c r="J363" t="n">
-        <v>2.2528</v>
+        <v>1.8678</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.4482</v>
+        <v>-0.441</v>
       </c>
       <c r="J364" t="n">
-        <v>-9.8604</v>
+        <v>-9.702</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>0.55</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.457</v>
+        <v>-0.4507</v>
       </c>
       <c r="J365" t="n">
-        <v>-10.054</v>
+        <v>-9.9154</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.34</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.638</v>
+        <v>-0.6585</v>
       </c>
       <c r="J366" t="n">
-        <v>-14.036</v>
+        <v>-14.487</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.77</v>
       </c>
       <c r="I367" t="n">
-        <v>0.8502</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="J367" t="n">
-        <v>18.7044</v>
+        <v>17.1534</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>1.63</v>
       </c>
       <c r="I368" t="n">
-        <v>0.7215</v>
+        <v>0.6506</v>
       </c>
       <c r="J368" t="n">
-        <v>15.873</v>
+        <v>14.3132</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>1.45</v>
       </c>
       <c r="I369" t="n">
-        <v>0.5501</v>
+        <v>0.4844</v>
       </c>
       <c r="J369" t="n">
-        <v>12.1022</v>
+        <v>10.6568</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>1.41</v>
       </c>
       <c r="I370" t="n">
-        <v>0.5114</v>
+        <v>0.4477</v>
       </c>
       <c r="J370" t="n">
-        <v>11.2508</v>
+        <v>9.849399999999999</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.9</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.1788</v>
+        <v>-0.1621</v>
       </c>
       <c r="J371" t="n">
-        <v>-3.9336</v>
+        <v>-3.5662</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.24</v>
       </c>
       <c r="I372" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.449</v>
       </c>
       <c r="J372" t="n">
-        <v>14.2128</v>
+        <v>12.572</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>1.15</v>
       </c>
       <c r="I373" t="n">
-        <v>0.3519</v>
+        <v>0.2979</v>
       </c>
       <c r="J373" t="n">
-        <v>9.853199999999999</v>
+        <v>8.341200000000001</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>1.02</v>
       </c>
       <c r="I374" t="n">
-        <v>0.0767</v>
+        <v>0.0545</v>
       </c>
       <c r="J374" t="n">
-        <v>2.1476</v>
+        <v>1.526</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>0.84</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.2095</v>
+        <v>-0.189</v>
       </c>
       <c r="J375" t="n">
-        <v>-5.866</v>
+        <v>-5.292</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>0.62</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.4174</v>
+        <v>-0.4087</v>
       </c>
       <c r="J376" t="n">
-        <v>-11.6872</v>
+        <v>-11.4436</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>1.56</v>
       </c>
       <c r="I377" t="n">
-        <v>1.1898</v>
+        <v>1.2046</v>
       </c>
       <c r="J377" t="n">
-        <v>33.3144</v>
+        <v>33.7288</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>1.43</v>
       </c>
       <c r="I378" t="n">
-        <v>1.0046</v>
+        <v>1.0023</v>
       </c>
       <c r="J378" t="n">
-        <v>28.1288</v>
+        <v>28.0644</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>1.09</v>
       </c>
       <c r="I379" t="n">
-        <v>0.2864</v>
+        <v>0.2541</v>
       </c>
       <c r="J379" t="n">
-        <v>8.0192</v>
+        <v>7.1148</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>0.93</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.2943</v>
+        <v>-0.2546</v>
       </c>
       <c r="J380" t="n">
-        <v>-8.240399999999999</v>
+        <v>-7.1288</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>0.91</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3503</v>
+        <v>-0.3093</v>
       </c>
       <c r="J381" t="n">
-        <v>-9.808400000000001</v>
+        <v>-8.660399999999999</v>
       </c>
     </row>
     <row r="382">
@@ -17629,10 +17629,10 @@
         <v>1.25</v>
       </c>
       <c r="I382" t="n">
-        <v>0.6785</v>
+        <v>0.6437</v>
       </c>
       <c r="J382" t="n">
-        <v>16.9625</v>
+        <v>16.0925</v>
       </c>
     </row>
     <row r="383">
@@ -17669,10 +17669,10 @@
         <v>1.18</v>
       </c>
       <c r="I383" t="n">
-        <v>0.5221</v>
+        <v>0.4817</v>
       </c>
       <c r="J383" t="n">
-        <v>13.0525</v>
+        <v>12.0425</v>
       </c>
     </row>
     <row r="384">
@@ -17709,10 +17709,10 @@
         <v>1.06</v>
       </c>
       <c r="I384" t="n">
-        <v>0.2202</v>
+        <v>0.1875</v>
       </c>
       <c r="J384" t="n">
-        <v>5.505</v>
+        <v>4.6875</v>
       </c>
     </row>
     <row r="385">
@@ -17749,10 +17749,10 @@
         <v>0.98</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.1113</v>
+        <v>-0.0852</v>
       </c>
       <c r="J385" t="n">
-        <v>-2.7825</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="386">
@@ -17789,10 +17789,10 @@
         <v>0.88</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.4081</v>
+        <v>-0.3651</v>
       </c>
       <c r="J386" t="n">
-        <v>-10.2025</v>
+        <v>-9.1275</v>
       </c>
     </row>
     <row r="387">
@@ -17829,10 +17829,10 @@
         <v>1.72</v>
       </c>
       <c r="I387" t="n">
-        <v>1.1406</v>
+        <v>1.132</v>
       </c>
       <c r="J387" t="n">
-        <v>28.515</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="388">
@@ -17869,10 +17869,10 @@
         <v>1.14</v>
       </c>
       <c r="I388" t="n">
-        <v>0.3202</v>
+        <v>0.2688</v>
       </c>
       <c r="J388" t="n">
-        <v>8.005000000000001</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="389">
@@ -17909,10 +17909,10 @@
         <v>0.91</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.139</v>
+        <v>-0.1195</v>
       </c>
       <c r="J389" t="n">
-        <v>-3.475</v>
+        <v>-2.9875</v>
       </c>
     </row>
     <row r="390">
@@ -17949,10 +17949,10 @@
         <v>0.88</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.173</v>
+        <v>-0.1525</v>
       </c>
       <c r="J390" t="n">
-        <v>-4.325</v>
+        <v>-3.8125</v>
       </c>
     </row>
     <row r="391">
@@ -17989,10 +17989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.4751</v>
+        <v>-0.4739</v>
       </c>
       <c r="J391" t="n">
-        <v>-11.8775</v>
+        <v>-11.8475</v>
       </c>
     </row>
   </sheetData>
